--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,23 +482,29 @@
           <t>status</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>is_demo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>beispiel-001</t>
+          <t>demo-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beispielzeile entfernen</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
+          <t>Demo: Wie sich Frankfurt im Blick behalten laesst</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -507,20 +513,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Beispieltext durch eine gepruefte Meldung ersetzen.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Beispielmeldung zur Darstellung des Newsrooms. Vor dem Livegang durch eine recherchierte Meldung ersetzen.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dies ist kein aktueller Nachrichtenbericht. Die Zeile zeigt, wie Fakten, Einordnung und Quelle spaeter auf der Website erscheinen.</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Quelle eintragen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://example.com</t>
-        </is>
-      </c>
+          <t>DEMO-INHALT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>mittel</t>
@@ -529,12 +535,144 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Beispielbild</t>
+          <t>Demo-Inhalt</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>demo-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Demo: Ein Special Movement sachlich einordnen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beispiel fuer eine klar gekennzeichnete Meldung ohne Spekulationen oder unbestaetigte Ursachen.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nur bestaetigte Angaben wuerden im echten Betrieb veroeffentlicht. Externe Trackingdaten waeren dabei niemals die einzige Quelle.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DEMO-INHALT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mittel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Demo-Inhalt</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>demo-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Demo: Infrastruktur am Flughafen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Terminal 3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beispiel fuer ein dauerhaft relevantes Hintergrundthema rund um Frankfurt Airport.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Evergreen-Inhalte koennen an nachrichtenarmen Tagen genutzt werden, wenn sie quellenbasiert erstellt und korrekt belegt sind.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DEMO-INHALT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>niedrig</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Demo-Inhalt</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,8 +504,6 @@
           <t>Demo: Wie sich Frankfurt im Blick behalten laesst</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -526,13 +524,11 @@
           <t>DEMO-INHALT</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>mittel</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Demo-Inhalt</t>
@@ -565,8 +561,6 @@
           <t>Demo: Ein Special Movement sachlich einordnen</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -587,13 +581,11 @@
           <t>DEMO-INHALT</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>mittel</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Demo-Inhalt</t>
@@ -626,8 +618,6 @@
           <t>Demo: Infrastruktur am Flughafen</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Terminal 3</t>
@@ -648,13 +638,11 @@
           <t>DEMO-INHALT</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>niedrig</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Demo-Inhalt</t>
@@ -673,6 +661,67 @@
       <c r="O4" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>incident-geruch-pruefung</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pruefung: Geruch an Bord fuehrte zur Rueckkehr nach Frankfurt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notfall</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Redaktioneller Pruefeintrag: Der konkrete Vorfall muss vor einer Veroeffentlichung eindeutig ueber Datum, Flugnummer und belastbare Quelle zugeordnet werden.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bis zur eindeutigen Bestaetigung bleibt dieser Eintrag unsichtbar. Keine Ursache und keine weiteren Details werden abgeleitet.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Noch zu bestaetigen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mittel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pruefeintrag</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,42 +496,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>demo-001</t>
+          <t>lh573-geruch-brazzaville</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Demo: Wie sich Frankfurt im Blick behalten laesst</t>
-        </is>
-      </c>
+          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Frankfurt Airport</t>
+          <t>Special Movement</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Beispielmeldung zur Darstellung des Newsrooms. Vor dem Livegang durch eine recherchierte Meldung ersetzen.</t>
+          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dies ist kein aktueller Nachrichtenbericht. Die Zeile zeigt, wie Fakten, Einordnung und Quelle spaeter auf der Website erscheinen.</t>
+          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DEMO-INHALT</t>
+          <t>RTL.de</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mittel</t>
-        </is>
-      </c>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Demo-Inhalt</t>
+          <t>Symbolbild: Boeing 747-8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -546,49 +558,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>demo-002</t>
+          <t>fraport-juli-traffic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Demo: Ein Special Movement sachlich einordnen</t>
-        </is>
-      </c>
+          <t>Frankfurt Airport erreicht im Juli rund 6,2 Millionen Passagiere</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Special Movement</t>
+          <t>Frankfurt Airport</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Beispiel fuer eine klar gekennzeichnete Meldung ohne Spekulationen oder unbestaetigte Ursachen.</t>
+          <t>Die Passagierzahl am Flughafen Frankfurt lag im Juli 2026 rund 1,4 Prozent über dem Vorjahresmonat.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nur bestaetigte Angaben wuerden im echten Betrieb veroeffentlicht. Externe Trackingdaten waeren dabei niemals die einzige Quelle.</t>
+          <t>Nach den veröffentlichten Verkehrszahlen wurden im Juli rund 6,2 Millionen Passagiere gezählt. Gleichzeitig gingen die Flugbewegungen um 3,2 Prozent auf 41.286 Starts und Landungen zurück. Das Cargo-Aufkommen stieg um 0,9 Prozent auf 180.622 Tonnen.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DEMO-INHALT</t>
+          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://payloadasia.com/2026/08/fraport-reports-july-growth-frankfurt-passenger-traffic-cargo-volumes/</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mittel</t>
-        </is>
-      </c>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Demo-Inhalt</t>
+          <t>Flughafen Frankfurt: Verkehrszahlen Juli 2026</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -603,49 +627,61 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>demo-003</t>
+          <t>fraport-h1-traffic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Demo: Infrastruktur am Flughafen</t>
-        </is>
-      </c>
+          <t>Fraport hält Jahresausblick trotz schwächerem ersten Halbjahr</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terminal 3</t>
+          <t>Verkehrszahlen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beispiel fuer ein dauerhaft relevantes Hintergrundthema rund um Frankfurt Airport.</t>
+          <t>Im ersten Halbjahr 2026 nutzten rund 28,9 Millionen Passagiere den Flughafen Frankfurt, 0,8 Prozent weniger als im Vorjahreszeitraum.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evergreen-Inhalte koennen an nachrichtenarmen Tagen genutzt werden, wenn sie quellenbasiert erstellt und korrekt belegt sind.</t>
+          <t>Fraport führte die Entwicklung unter anderem auf Streiks bei Lufthansa und die geringere Nachfrage nach Verbindungen in den Nahen Osten zurück. Für das Gesamtjahr erwartet Fraport am Standort Frankfurt ungefähr das Passagierniveau von 2025. Die Angaben stammen aus der veröffentlichten Halbjahresauswertung.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DEMO-INHALT</t>
+          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://payloadasia.com/2026/07/fraport-maintains-2026-outlook-frankfurt-traffic-softens-first-half/</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>niedrig</t>
-        </is>
-      </c>
+          <t>mittel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Demo-Inhalt</t>
+          <t>Fraport Halbjahresauswertung 2026</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -659,67 +695,6 @@
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>incident-geruch-pruefung</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pruefung: Geruch an Bord fuehrte zur Rueckkehr nach Frankfurt</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Notfall</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Redaktioneller Pruefeintrag: Der konkrete Vorfall muss vor einer Veroeffentlichung eindeutig ueber Datum, Flugnummer und belastbare Quelle zugeordnet werden.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bis zur eindeutigen Bestaetigung bleibt dieser Eintrag unsichtbar. Keine Ursache und keine weiteren Details werden abgeleitet.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Noch zu bestaetigen</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mittel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Pruefeintrag</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -496,43 +496,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lh573-geruch-brazzaville</t>
+          <t>fraport-juli-traffic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
+          <t>Frankfurt Airport erreicht im Juli rund 6,2 Millionen Passagiere</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Special Movement</t>
+          <t>Frankfurt Airport</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
+          <t>Die Passagierzahl am Flughafen Frankfurt lag im Juli 2026 rund 1,4 Prozent über dem Vorjahresmonat.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
+          <t>Nach den veröffentlichten Verkehrszahlen wurden im Juli rund 6,2 Millionen Passagiere gezählt. Gleichzeitig gingen die Flugbewegungen um 3,2 Prozent auf 41.286 Starts und Landungen zurück. Das Cargo-Aufkommen stieg um 0,9 Prozent auf 180.622 Tonnen.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RTL.de</t>
+          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
+          <t>https://payloadasia.com/2026/08/fraport-reports-july-growth-frankfurt-passenger-traffic-cargo-volumes/</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -543,7 +543,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Symbolbild: Boeing 747-8</t>
+          <t>Flughafen Frankfurt: Verkehrszahlen Juli 2026</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -565,43 +565,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fraport-juli-traffic</t>
+          <t>lh573-geruch-brazzaville</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frankfurt Airport erreicht im Juli rund 6,2 Millionen Passagiere</t>
+          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Frankfurt Airport</t>
+          <t>Special Movement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Die Passagierzahl am Flughafen Frankfurt lag im Juli 2026 rund 1,4 Prozent über dem Vorjahresmonat.</t>
+          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nach den veröffentlichten Verkehrszahlen wurden im Juli rund 6,2 Millionen Passagiere gezählt. Gleichzeitig gingen die Flugbewegungen um 3,2 Prozent auf 41.286 Starts und Landungen zurück. Das Cargo-Aufkommen stieg um 0,9 Prozent auf 180.622 Tonnen.</t>
+          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
+          <t>RTL.de</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://payloadasia.com/2026/08/fraport-reports-july-growth-frankfurt-passenger-traffic-cargo-volumes/</t>
+          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Flughafen Frankfurt: Verkehrszahlen Juli 2026</t>
+          <t>Symbolbild: Boeing 747-8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,43 +565,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lh573-geruch-brazzaville</t>
+          <t>auto-dae28e3b4373</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
+          <t>Deutlich weniger Flüge am Frankfurter Flughafen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Special Movement</t>
+          <t>Frankfurt Airport</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
+          <t>Im Juli 2026 wurden am Flughafen Frankfurt rund 6,2 Millionen Passagiere gezählt, obwohl die Zahl der Starts und Landungen zurückging.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
+          <t>Nach den von Fraport veröffentlichten und von aero.de zusammengefassten Zahlen sanken die Flugbewegungen um 3,2 Prozent auf 41.286. Die Passagierzahl stieg dagegen um 1,4 Prozent. Als Gründe werden eine höhere Auslastung und der Einsatz größerer Flugzeuge genannt.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL.de</t>
+          <t>aero.de</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
+          <t>https://www.aero.de/news-53366/Deutlich-weniger-Fluege-am-Frankfurter-Flughafen.html</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -610,11 +610,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Symbolbild: Boeing 747-8</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>published</t>
@@ -622,7 +618,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -634,67 +630,266 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fraport-h1-traffic</t>
+          <t>auto-6a58b9d3aef5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fraport hält Jahresausblick trotz schwächerem ersten Halbjahr</t>
+          <t>Wachstum bei Lufthansa City Airlines geht trotz Schlichtung weiter</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Airlines</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lufthansa City Airlines soll ihr Flottenwachstum trotz der Schlichtungsvereinbarung zwischen Lufthansa und der Vereinigung Cockpit fortsetzen können.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH berichtet unter Berufung auf eine Mitteilung der Gewerkschaft Verdi, dass neue Flugzeuge und Wechsel aus dem Lufthansa-AOC weiterhin möglich sein sollen. Ein direkter operativer Effekt für Frankfurt ist in der Meldung nicht genannt; der Beitrag wird deshalb als mittel relevant eingeordnet.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/wachstum-bei-lufthansa-city-airlines-geht-trotz-schlichtung-weiter/kbrvm52</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mittel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>auto-e37a0f8cf765</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lufthansa und Vereinigung Cockpit vereinbaren Schlichtung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Airlines</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lufthansa und die Vereinigung Cockpit haben eine Vereinbarung für Schlichtung und Mediation offener Tarifthemen getroffen.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Laut aero.de sollen die Schlichtungen möglicherweise noch im August beginnen. Ein Abschluss des Gesamtverfahrens ist bis Ende Dezember 2026 vorgesehen. Die Meldung ist für Frankfurt relevant, weil Lufthansa am Standort ein zentrales Drehkreuz betreibt; konkrete Auswirkungen auf den Flugbetrieb sind damit nicht automatisch verbunden.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53344/Lufthansa-und-Vereinigung-Cockpit-vereinbaren-Schlichtung.html</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mittel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lh573-geruch-brazzaville</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RTL.de</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Symbolbild: Boeing 747-8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fraport-h1-traffic</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fraport hält Jahresausblick trotz schwächerem ersten Halbjahr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Verkehrszahlen</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Im ersten Halbjahr 2026 nutzten rund 28,9 Millionen Passagiere den Flughafen Frankfurt, 0,8 Prozent weniger als im Vorjahreszeitraum.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Fraport führte die Entwicklung unter anderem auf Streiks bei Lufthansa und die geringere Nachfrage nach Verbindungen in den Nahen Osten zurück. Für das Gesamtjahr erwartet Fraport am Standort Frankfurt ungefähr das Passagierniveau von 2025. Die Angaben stammen aus der veröffentlichten Halbjahresauswertung.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://payloadasia.com/2026/07/fraport-maintains-2026-outlook-frankfurt-traffic-softens-first-half/</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>mittel</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Fraport Halbjahresauswertung 2026</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,12 +496,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fraport-juli-traffic</t>
+          <t>auto-dae28e3b4373</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frankfurt Airport erreicht im Juli rund 6,2 Millionen Passagiere</t>
+          <t>Deutlich weniger Flüge am Frankfurter Flughafen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,22 +517,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Die Passagierzahl am Flughafen Frankfurt lag im Juli 2026 rund 1,4 Prozent über dem Vorjahresmonat.</t>
+          <t>Im Juli 2026 wurden am Flughafen Frankfurt rund 6,2 Millionen Passagiere gezählt, obwohl die Zahl der Starts und Landungen zurückging.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nach den veröffentlichten Verkehrszahlen wurden im Juli rund 6,2 Millionen Passagiere gezählt. Gleichzeitig gingen die Flugbewegungen um 3,2 Prozent auf 41.286 Starts und Landungen zurück. Das Cargo-Aufkommen stieg um 0,9 Prozent auf 180.622 Tonnen.</t>
+          <t>Nach den von Fraport veröffentlichten und von aero.de zusammengefassten Zahlen sanken die Flugbewegungen um 3,2 Prozent auf 41.286. Die Passagierzahl stieg dagegen um 1,4 Prozent. Als Gründe werden eine höhere Auslastung und der Einsatz größerer Flugzeuge genannt.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
+          <t>aero.de</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://payloadasia.com/2026/08/fraport-reports-july-growth-frankfurt-passenger-traffic-cargo-volumes/</t>
+          <t>https://www.aero.de/news-53366/Deutlich-weniger-Fluege-am-Frankfurter-Flughafen.html</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,11 +541,7 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Flughafen Frankfurt: Verkehrszahlen Juli 2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>published</t>
@@ -553,7 +549,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -565,12 +561,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>auto-dae28e3b4373</t>
+          <t>auto-6a58b9d3aef5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deutlich weniger Flüge am Frankfurter Flughafen</t>
+          <t>Wachstum bei Lufthansa City Airlines geht trotz Schlichtung weiter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -581,32 +577,32 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Frankfurt Airport</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Im Juli 2026 wurden am Flughafen Frankfurt rund 6,2 Millionen Passagiere gezählt, obwohl die Zahl der Starts und Landungen zurückging.</t>
+          <t>Lufthansa City Airlines soll ihr Flottenwachstum trotz der Schlichtungsvereinbarung zwischen Lufthansa und der Vereinigung Cockpit fortsetzen können.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nach den von Fraport veröffentlichten und von aero.de zusammengefassten Zahlen sanken die Flugbewegungen um 3,2 Prozent auf 41.286. Die Passagierzahl stieg dagegen um 1,4 Prozent. Als Gründe werden eine höhere Auslastung und der Einsatz größerer Flugzeuge genannt.</t>
+          <t>aeroTELEGRAPH berichtet unter Berufung auf eine Mitteilung der Gewerkschaft Verdi, dass neue Flugzeuge und Wechsel aus dem Lufthansa-AOC weiterhin möglich sein sollen. Ein direkter operativer Effekt für Frankfurt ist in der Meldung nicht genannt; der Beitrag wird deshalb als mittel relevant eingeordnet.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>aero.de</t>
+          <t>aeroTELEGRAPH</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.aero.de/news-53366/Deutlich-weniger-Fluege-am-Frankfurter-Flughafen.html</t>
+          <t>https://www.aerotelegraph.com/ticker/wachstum-bei-lufthansa-city-airlines-geht-trotz-schlichtung-weiter/kbrvm52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>hoch</t>
+          <t>mittel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,17 +626,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>auto-6a58b9d3aef5</t>
+          <t>auto-e37a0f8cf765</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wachstum bei Lufthansa City Airlines geht trotz Schlichtung weiter</t>
+          <t>Lufthansa und Vereinigung Cockpit vereinbaren Schlichtung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -651,22 +647,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lufthansa City Airlines soll ihr Flottenwachstum trotz der Schlichtungsvereinbarung zwischen Lufthansa und der Vereinigung Cockpit fortsetzen können.</t>
+          <t>Lufthansa und die Vereinigung Cockpit haben eine Vereinbarung für Schlichtung und Mediation offener Tarifthemen getroffen.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>aeroTELEGRAPH berichtet unter Berufung auf eine Mitteilung der Gewerkschaft Verdi, dass neue Flugzeuge und Wechsel aus dem Lufthansa-AOC weiterhin möglich sein sollen. Ein direkter operativer Effekt für Frankfurt ist in der Meldung nicht genannt; der Beitrag wird deshalb als mittel relevant eingeordnet.</t>
+          <t>Laut aero.de sollen die Schlichtungen möglicherweise noch im August beginnen. Ein Abschluss des Gesamtverfahrens ist bis Ende Dezember 2026 vorgesehen. Die Meldung ist für Frankfurt relevant, weil Lufthansa am Standort ein zentrales Drehkreuz betreibt; konkrete Auswirkungen auf den Flugbetrieb sind damit nicht automatisch verbunden.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>aeroTELEGRAPH</t>
+          <t>aero.de</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.aerotelegraph.com/ticker/wachstum-bei-lufthansa-city-airlines-geht-trotz-schlichtung-weiter/kbrvm52</t>
+          <t>https://www.aero.de/news-53344/Lufthansa-und-Vereinigung-Cockpit-vereinbaren-Schlichtung.html</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -695,52 +691,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>auto-e37a0f8cf765</t>
+          <t>lh573-geruch-brazzaville</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lufthansa und Vereinigung Cockpit vereinbaren Schlichtung</t>
+          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Special Movement</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lufthansa und die Vereinigung Cockpit haben eine Vereinbarung für Schlichtung und Mediation offener Tarifthemen getroffen.</t>
+          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Laut aero.de sollen die Schlichtungen möglicherweise noch im August beginnen. Ein Abschluss des Gesamtverfahrens ist bis Ende Dezember 2026 vorgesehen. Die Meldung ist für Frankfurt relevant, weil Lufthansa am Standort ein zentrales Drehkreuz betreibt; konkrete Auswirkungen auf den Flugbetrieb sind damit nicht automatisch verbunden.</t>
+          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>aero.de</t>
+          <t>RTL.de</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.aero.de/news-53344/Lufthansa-und-Vereinigung-Cockpit-vereinbaren-Schlichtung.html</t>
+          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mittel</t>
+          <t>hoch</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Symbolbild: Boeing 747-8</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>published</t>
@@ -748,7 +748,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -760,54 +760,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lh573-geruch-brazzaville</t>
+          <t>fraport-h1-traffic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lufthansa LH573 landet nach Geruch in der Kabine außerplanmäßig</t>
+          <t>Fraport hält Jahresausblick trotz schwächerem ersten Halbjahr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Special Movement</t>
+          <t>Verkehrszahlen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ein Lufthansa-Jumbo auf dem Weg von Johannesburg nach Frankfurt ist nach einem undefinierbaren Geruch in der Kabine sicher in Brazzaville zwischengelandet.</t>
+          <t>Im ersten Halbjahr 2026 nutzten rund 28,9 Millionen Passagiere den Flughafen Frankfurt, 0,8 Prozent weniger als im Vorjahreszeitraum.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lufthansa bestätigte gegenüber RTL, dass alle 363 Passagiere und die 16-köpfige Crew das Flugzeug sicher verlassen konnten. Die Boeing 747-8 blieb zunächst zur technischen Untersuchung in Brazzaville. Eine Ursache wurde in der vorliegenden Bestätigung nicht genannt.</t>
+          <t>Fraport führte die Entwicklung unter anderem auf Streiks bei Lufthansa und die geringere Nachfrage nach Verbindungen in den Nahen Osten zurück. Für das Gesamtjahr erwartet Fraport am Standort Frankfurt ungefähr das Passagierniveau von 2025. Die Angaben stammen aus der veröffentlichten Halbjahresauswertung.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RTL.de</t>
+          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.rtl.de/news/lufthansa-flug-lh573-sendet-notsignal-boeing-747-muss-sofort-landen-id31168621.html</t>
+          <t>https://payloadasia.com/2026/07/fraport-maintains-2026-outlook-frankfurt-traffic-softens-first-half/</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hoch</t>
+          <t>mittel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Symbolbild: Boeing 747-8</t>
+          <t>Fraport Halbjahresauswertung 2026</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -817,79 +817,10 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>fraport-h1-traffic</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fraport hält Jahresausblick trotz schwächerem ersten Halbjahr</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Verkehrszahlen</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Im ersten Halbjahr 2026 nutzten rund 28,9 Millionen Passagiere den Flughafen Frankfurt, 0,8 Prozent weniger als im Vorjahreszeitraum.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Fraport führte die Entwicklung unter anderem auf Streiks bei Lufthansa und die geringere Nachfrage nach Verbindungen in den Nahen Osten zurück. Für das Gesamtjahr erwartet Fraport am Standort Frankfurt ungefähr das Passagierniveau von 2025. Die Angaben stammen aus der veröffentlichten Halbjahresauswertung.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Fraport-Verkehrszahlen (berichtet von Payload Asia)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://payloadasia.com/2026/07/fraport-maintains-2026-outlook-frankfurt-traffic-softens-first-half/</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mittel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Fraport Halbjahresauswertung 2026</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="News" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -540,8 +539,6 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>published</t>
@@ -574,7 +571,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Airlines</t>
@@ -605,8 +601,6 @@
           <t>mittel</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>published</t>
@@ -639,7 +633,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Airlines</t>
@@ -670,8 +663,6 @@
           <t>mittel</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>published</t>
@@ -704,7 +695,6 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -735,7 +725,6 @@
           <t>hoch</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Symbolbild: Boeing 747-8</t>
@@ -773,7 +762,6 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Verkehrszahlen</t>
@@ -804,7 +792,6 @@
           <t>mittel</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Fraport Halbjahresauswertung 2026</t>
@@ -821,6 +808,1306 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>auto-db4bf840d1fc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Air France pausiert Paris - Salvador im Frühjahr 2027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Air France setzt ihre Nonstopverbindung zwischen Salvador da Bahia und Paris im Frühjahr 2027 vorübergehend aus. Zwischen dem 8. März und 22. Mai finden keine Direktflüge statt. Ab dem 24. Mai soll die Strecke wieder regulär bedient werden. Als Grund nennt Air France operative Gründe, wie das Portal Bahia Economica berichtet. Bereits gebuchte Passagiere werden während der Unterbrechung auf Gol-Flüge über São Paulo umgebucht.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-france-pausiert-paris-salvador-im-fruehjahr-2027/pmlsbbx</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>auto-463f30dc5cb7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Europas Kerosinkrise: Warum der Engpass bisher ausblieb – und das Risiko bleibt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>m Frühjahr schien ein Kerosinengpass unausweichlich: Straße von Hormuz blockiert, Lagerbestände niedrig, Nachfrage steigend. Doch der Markt reagierte erstaunlich schnell und zusätzliche Lieferungen aus den USA und Nigeria schlossen einen Großteil der Lücke. Entwarnung wäre trotzdem verfrüht.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/kolumnen/europas-kerosinkrise-warum-der-engpass-bisher-ausblieb-und-das-risiko-bleibt/mgx9tmm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>auto-526e6aab2205</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Airbus A350F: Erstauslieferung doch erst 2028?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AMSTERDAM - Der neue Airbus-Frachter A350F nimmt nach Planungen des Herstellers noch 2026 ein straffes Flugtestprogramm auf. Airbus arbeitet auf ein EIS Ende 2027 hin - und will A350F ab 2028 "in bedeutenden Stückzahlen" ausliefern. Nach einem Bericht droht dem Programm eine Verzögerung.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53367/Airbus-A350F-Erstauslieferung-doch-erst-2028.html</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>auto-ac0ef1288e45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Verdi sticht Detail aus Lufthansa-Schlichtung durch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa stoppt für eine Schlichtung mit der Vereinigung Cockpit die Flottenerosion in der Mainline. Die Entscheidung verzögert den laufenden Ausbau von Lufthansa City Airlines aber nicht - sagt Verdi. Lufthansa kann nach Lesart der Gewerkschaft weiterhin Lufthansa-Flugzeuge zu City Airlines rüberschieben.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53368/Verdi-sticht-Detail-aus-Lufthansa-Schlichtung-durch.html</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>auto-2a6324861234</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>"Weiteres Schrumpfen ist nicht in unserem Interesse"</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schlichtung zu Betriebsrenten, vorgezogene Vergütungsverhandlungen - und eine Mediation: Lufthansa und die Vereinigung Cockpit bohren im Spätsommer die dicken Bretter. Personalvorstand Dr. Michael Niggemann spricht im Interview über die Systematik, Themenkreise - und Ziele.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53352/Weiteres-Schrumpfen-ist-nicht-in-unserem-Interesse.html</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>auto-7e208b1e7ade</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo: Customs processes at Frankfurt Airport are being further digitized. - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixgFBVV95cUxPS1FNNVRuTFdoLUUwRTFub0FwS3hvYXRTZ0FuWmVzeWVvVDEyYWx2U01wRjVWMFphUWFYZzRadXJnTDctaXdxZzY2aUw4NnluSFFNZkptQ1ZORE9oMUg1UHVWbjNkZTBsOFBHR1JZaFJZWFUyV21MbTAtNjk5OU9hUUVKNmptZkVDWmN0cVhLUUpDT1dVSWJtUmpHWXUxakZSQzgzczZ2RS1xWnhvRmc0M3NNcUR1TDhUVWR6ZEo3LUEySVRlUmc?oc=5" target="_blank"&gt;Lufthansa Cargo: Customs processes at Frankfurt Airport are being further digitized.&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPS1FNNVRuTFdoLUUwRTFub0FwS3hvYXRTZ0FuWmVzeWVvVDEyYWx2U01wRjVWMFphUWFYZzRadXJnTDctaXdxZzY2aUw4NnluSFFNZkptQ1ZORE9oMUg1UHVWbjNkZTBsOFBHR1JZaFJZWFUyV21MbTAtNjk5OU9hUUVKNmptZkVDWmN0cVhLUUpDT1dVSWJtUmpHWXUxakZSQzgzczZ2RS1xWnhvRmc0M3NNcUR1TDhUVWR6ZEo3LUEySVRlUmc?oc=5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>auto-fdb1c2e6580e</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vietnam Airlines zieht ins Terminal 3 am Frankfurt Airport - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinwFBVV95cUxQb2w4SXlpenNNRUFMaEpFMHFzV2psM0ktQ3lhSjVwazhLUUxOU0wtOFhEci1tQVpuaG5vWWpHMlloT0lOVWkxeDB0dFh1MnlIcFN2ajVJTFNIOG1ocHRGb3I5aFpDc2RZS2NvSzFEYjgzOTUtRlJGOG5yRWlLMUtlYlVuUTBYNEVGRXIyU3dGUjdDNjAzSFBzMmNoSUgtWnM?oc=5" target="_blank"&gt;Vietnam Airlines zieht ins Terminal 3 am Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQb2w4SXlpenNNRUFMaEpFMHFzV2psM0ktQ3lhSjVwazhLUUxOU0wtOFhEci1tQVpuaG5vWWpHMlloT0lOVWkxeDB0dFh1MnlIcFN2ajVJTFNIOG1ocHRGb3I5aFpDc2RZS2NvSzFEYjgzOTUtRlJGOG5yRWlLMUtlYlVuUTBYNEVGRXIyU3dGUjdDNjAzSFBzMmNoSUgtWnM?oc=5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>auto-4df725a00fde</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Frankfurt Terminal 3 – Airlines, Lounges &amp; Anreise im Überblick - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibEFVX3lxTE13M0J0OTBpYXJHeU1ERmNxRUxvY3JZZC03M2dJSXNuUWMySnY2cjhzcDVlWllBbW1PRDBiT1kyNVdMRW0yY09yNkdQYTVheUh5cnozV3lES01WMWJIZFN2QnVjZTRqMDlKMXRfaQ?oc=5" target="_blank"&gt;Frankfurt Terminal 3 – Airlines, Lounges &amp; Anreise im Überblick&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE13M0J0OTBpYXJHeU1ERmNxRUxvY3JZZC03M2dJSXNuUWMySnY2cjhzcDVlWllBbW1PRDBiT1kyNVdMRW0yY09yNkdQYTVheUh5cnozV3lES01WMWJIZFN2QnVjZTRqMDlKMXRfaQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>auto-889aa2431620</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Terminal 3 am Flughafen Frankfurt: Alles über Airlines, Umstiege, Anfahrt - hessenschau.de</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi4wFBVV95cUxNZk9WOEpkMW9uSUp4MjctenhRYjFSTEdzdkVIMXpDWUNPVGpscEJjLXAxQ0sxcHZUVFJCM1o5RUJxaFpZWXdGNC1COHh2Snl2NjdNbnUxa0dOYXNnLVFRNm9PYmZjLVZYVHNWZW52MXc4YVIwT19qYzBHdWRqUVR5UjZ1dWlkb2s4OE93VERyRFZ3SnB4SjM3a0xmLW5Sb3hrUi0xQk55MTVGazlhbVpwTFhUckdHVFNCdzNVdzk1dEFMeE1qdUc5TnptVlF5YzM2WW5VZnJ4NUh0Q1NseWpyS1RNMA?oc=5" target="_blank"&gt;Terminal 3 am Flughafen Frankfurt: Alles über Airlines, Umstiege, Anfahrt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;hessenschau.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNZk9WOEpkMW9uSUp4MjctenhRYjFSTEdzdkVIMXpDWUNPVGpscEJjLXAxQ0sxcHZUVFJCM1o5RUJxaFpZWXdGNC1COHh2Snl2NjdNbnUxa0dOYXNnLVFRNm9PYmZjLVZYVHNWZW52MXc4YVIwT19qYzBHdWRqUVR5UjZ1dWlkb2s4OE93VERyRFZ3SnB4SjM3a0xmLW5Sb3hrUi0xQk55MTVGazlhbVpwTFhUckdHVFNCdzNVdzk1dEFMeE1qdUc5TnptVlF5YzM2WW5VZnJ4NUh0Q1NseWpyS1RNMA?oc=5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>auto-ed08e08b238f</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Air France und KLM umgezogen - Flughafen Frankfurt schließt T2 - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUzJBZ2duWTN3Y0FEX0ZZdldwa2lyVUpJRGVjUTNrTUtGenQtLTFaLTh6Q1ZPa0tvYTdKX2VyWXBDTkNBeVFjZmwtcXJYVmgtSktmc3poNFlZSksxaUZVVGQwZTdEdmNrVEM3Q3lvWEdmUFppT09pM0lKS3hUaWJ0RjkzMzVZdXFsUUJnajllZUNPRHNndWtsQS13QTFrVkZXdXJOa2VuTnJRZw?oc=5" target="_blank"&gt;Air France und KLM umgezogen - Flughafen Frankfurt schließt T2&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUzJBZ2duWTN3Y0FEX0ZZdldwa2lyVUpJRGVjUTNrTUtGenQtLTFaLTh6Q1ZPa0tvYTdKX2VyWXBDTkNBeVFjZmwtcXJYVmgtSktmc3poNFlZSksxaUZVVGQwZTdEdmNrVEM3Q3lvWEdmUFppT09pM0lKS3hUaWJ0RjkzMzVZdXFsUUJnajllZUNPRHNndWtsQS13QTFrVkZXdXJOa2VuTnJRZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>auto-b791912ff9e4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: Auch Air France und KLM wechseln ins Terminal 3 - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirgFBVV95cUxQQTFhWTBKV3VOem9OdGYtWXJ1SURoRG0zUHpyV3p3OWJtRXNVZUJIOVVrczgzcGQxSFpUZmIweTA4SkVMVlEzZmxpS2V1RURhZE90YUVzaDlOUTVtcy1EVXFCZ3NfUDVBNnlEOWFyTXBEdGdSamFUSlUzcUF4VmstZUd5RFFDZUhPWVBXcXBZRmNtWGprSU9zbW1ldVlSeE1JeG5OX0lKVWlJMlA4aVE?oc=5" target="_blank"&gt;Frankfurt Airport: Auch Air France und KLM wechseln ins Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQQTFhWTBKV3VOem9OdGYtWXJ1SURoRG0zUHpyV3p3OWJtRXNVZUJIOVVrczgzcGQxSFpUZmIweTA4SkVMVlEzZmxpS2V1RURhZE90YUVzaDlOUTVtcy1EVXFCZ3NfUDVBNnlEOWFyTXBEdGdSamFUSlUzcUF4VmstZUd5RFFDZUhPWVBXcXBZRmNtWGprSU9zbW1ldVlSeE1JeG5OX0lKVWlJMlA4aVE?oc=5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>auto-16614984fb1d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Aufgepasst – diese Airlines fliegen seit dem 5. Mai am neuen Terminal 3 ab - Main-Post</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVXdldWdGLTlRcVNYakFHTVdiV1l2QXIyNkR4bDJEX21GWHc0c3BYczV6S3I2VWRScXNYTGVLdU45MXhtN3FjZUNxbERlTHYxWGZCaVlNelE3OUFNU3BHQVFCYXEtRUdMMW1MUFdtZFZGY05teUVSaFkxUm9fdEZsN3BoeEhUdFVVcUd3dEcwUHBmbWxEcER2ZF94N2RGNDFkVktnbEZ1cFZ2M0dBc21WQzFjRlNvMF96ZGYzUUZzRDk1LWtOOXVLWWl4bTRRYXB2Wnc?oc=5" target="_blank"&gt;Flughafen Frankfurt: Aufgepasst – diese Airlines fliegen seit dem 5. Mai am neuen Terminal 3 ab&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Main-Post&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVXdldWdGLTlRcVNYakFHTVdiV1l2QXIyNkR4bDJEX21GWHc0c3BYczV6S3I2VWRScXNYTGVLdU45MXhtN3FjZUNxbERlTHYxWGZCaVlNelE3OUFNU3BHQVFCYXEtRUdMMW1MUFdtZFZGY05teUVSaFkxUm9fdEZsN3BoeEhUdFVVcUd3dEcwUHBmbWxEcER2ZF94N2RGNDFkVktnbEZ1cFZ2M0dBc21WQzFjRlNvMF96ZGYzUUZzRDk1LWtOOXVLWWl4bTRRYXB2Wnc?oc=5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>auto-7fdf8e34c1c3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fluggäste aufgepasst: Diese Airlines ziehen heute am Frankfurter Flughafen um - t-online – Frankfurt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1gFBVV95cUxNUjNzejVBeXh1RnV5cGNHNnlhUXJTb1N6MEppRXZGb1FBMHRjUHFTOTVGd2IxTlFCNUxiaGM5ZmJ5QUc4STZyQ1hEcV9sNWpFTzh6R19CNXBVTEpuTDRXNktxakRQenJ1dTVMQXRUNXE2d2NSdGhZUjBVOV9vTktaa3FUZnpuUkR4dFdqX0ItdXU3dVpmQ0kxRWFjMVhRWHVMRTRwVy1GWUdXZDNTTkdiU2praDR0SENYNVowM1ZUQWVsNkt2bmp0ak8tYWUxR0NGeEI5VzV3?oc=5" target="_blank"&gt;Fluggäste aufgepasst: Diese Airlines ziehen heute am Frankfurter Flughafen um&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;t-online – Frankfurt&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNUjNzejVBeXh1RnV5cGNHNnlhUXJTb1N6MEppRXZGb1FBMHRjUHFTOTVGd2IxTlFCNUxiaGM5ZmJ5QUc4STZyQ1hEcV9sNWpFTzh6R19CNXBVTEpuTDRXNktxakRQenJ1dTVMQXRUNXE2d2NSdGhZUjBVOV9vTktaa3FUZnpuUkR4dFdqX0ItdXU3dVpmQ0kxRWFjMVhRWHVMRTRwVy1GWUdXZDNTTkdiU2praDR0SENYNVowM1ZUQWVsNkt2bmp0ak8tYWUxR0NGeEI5VzV3?oc=5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>auto-49937618d284</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Terminal 3 in Frankfurt eröffnet: Was Reisende jetzt wissen müssen - reisen EXCLUSIV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMie0FVX3lxTE1NdVRoUTlZb0JIcmkwV0QtZUVPbGQ4amlGWHcwNlgzY29SRGlSd2JMam9xVjZpRzhENzRKamFoMk80eDdKdG5kLWJab2pTak9CdlliSDNkZjdER29RLWdIS0RVX3lYZU5zWWRKbGJncnZBem9mQi1zaGNWbw?oc=5" target="_blank"&gt;Terminal 3 in Frankfurt eröffnet: Was Reisende jetzt wissen müssen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;reisen EXCLUSIV&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1NdVRoUTlZb0JIcmkwV0QtZUVPbGQ4amlGWHcwNlgzY29SRGlSd2JMam9xVjZpRzhENzRKamFoMk80eDdKdG5kLWJab2pTak9CdlliSDNkZjdER29RLWdIS0RVX3lYZU5zWWRKbGJncnZBem9mQi1zaGNWbw?oc=5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>auto-640cee9e5121</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Terminal 3 am Flughafen Frankfurt: Fraport verrät kompletten Zeitplan für Airline-Umzüge - fnp.de</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiswFBVV95cUxPNGp4ck0wTHo4aExLajNwOUZLSEJJNjczLXZJTXFmVjZoV1REelB4bnV3bXdybHVKeXJISUFIanIzeVhuS1dsMDhoMmhIYUJzakxaRWRpaWpXZkNhYl81WjZiYXNXRjlZTnlzUWFHdy0xbWdCaTdNM3dQRTU2X1Q2THZSVGNIaUhSNmY0Mm85UVh6TWxzQ3A0SlNraXM2T2hONXdrZ2lwUm9NUVZ4MnU5OHpMcw?oc=5" target="_blank"&gt;Terminal 3 am Flughafen Frankfurt: Fraport verrät kompletten Zeitplan für Airline-Umzüge&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNGp4ck0wTHo4aExLajNwOUZLSEJJNjczLXZJTXFmVjZoV1REelB4bnV3bXdybHVKeXJISUFIanIzeVhuS1dsMDhoMmhIYUJzakxaRWRpaWpXZkNhYl81WjZiYXNXRjlZTnlzUWFHdy0xbWdCaTdNM3dQRTU2X1Q2THZSVGNIaUhSNmY0Mm85UVh6TWxzQ3A0SlNraXM2T2hONXdrZ2lwUm9NUVZ4MnU5OHpMcw?oc=5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>auto-0598012a45f7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A Milestone at FRA: the First Landing at Terminal 3 - Presseportal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiV0FVX3lxTE5STWZuUy1NUEJwMFBjTElYYl9HRE90TU1NUEQ1YnVuVXIwQmRPaks4ZGdQUnNRS1p6WW5lZG1jVnA5QURWQm5zWTBYYkFueV9JS3J1N0xfNA?oc=5" target="_blank"&gt;A Milestone at FRA: the First Landing at Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Presseportal&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5STWZuUy1NUEJwMFBjTElYYl9HRE90TU1NUEQ1YnVuVXIwQmRPaks4ZGdQUnNRS1p6WW5lZG1jVnA5QURWQm5zWTBYYkFueV9JS3J1N0xfNA?oc=5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>auto-e35d8143da11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Neue SkyTeam Lounge im Terminal 3 Frankfurt: Zugang, Ausstattung und Einschränkungen - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxNOTNETUJleS1FX0dZT1FJVHBZSWtqbFhCWTNpbnBqdEl4SVcydHFDbFQyYUVwMjE0LVpKb3ZVS0FJWGIzLWxvazBiem1mYldhZnFoWVVnMS1Ea3ZTU2VOWXNkMlAwZUoxUkllaXhtbFR0OU10NURjb2JLdW9UX3U1UjZ0dExrbjFiUVZOUjVoZ21DNkxhMUQtblJ6SnlLTDBfRF9OQnVreGxUXzEyaThB?oc=5" target="_blank"&gt;Neue SkyTeam Lounge im Terminal 3 Frankfurt: Zugang, Ausstattung und Einschränkungen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNOTNETUJleS1FX0dZT1FJVHBZSWtqbFhCWTNpbnBqdEl4SVcydHFDbFQyYUVwMjE0LVpKb3ZVS0FJWGIzLWxvazBiem1mYldhZnFoWVVnMS1Ea3ZTU2VOWXNkMlAwZUoxUkllaXhtbFR0OU10NURjb2JLdW9UX3U1UjZ0dExrbjFiUVZOUjVoZ21DNkxhMUQtblJ6SnlLTDBfRF9OQnVreGxUXzEyaThB?oc=5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>auto-913e97c6b478</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kurznachrichten: Streckenstart von Edelweiss, Air Corsica, Discover Airlines und Umzug von Air France am Airport Frankfurt - Airportzentrale</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTDY1U2VhOGVvcVp2dlcwY0gzb2hsSGFoZ1FuUWZWd2JrOGFaTjNDSFVHNTlJYS0tVW9DRDdLTElqNEtyU015emRWaVFBUXc2YUVXamM1ZW5CYzZDUjFVTlpIenBFcmVVdVNMMXZfaFZsNXBHMnIyYUJKbnhQMVBLUHJIQlVRMU8tal9UT1lLNU9XRUQtSWJKSkxpNEZTcnVVSEZMX0hlMW1EM0hEVVFBdnoxeVM1SW9XeFk4c21fRnJKc0Rwa3RhUmRnSy13U3RxdmtGUTB3bE9Db3RBRUdhNkxpNXUwZG9UOE5YRU53?oc=5" target="_blank"&gt;Kurznachrichten: Streckenstart von Edelweiss, Air Corsica, Discover Airlines und Umzug von Air France am Airport Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airportzentrale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTDY1U2VhOGVvcVp2dlcwY0gzb2hsSGFoZ1FuUWZWd2JrOGFaTjNDSFVHNTlJYS0tVW9DRDdLTElqNEtyU015emRWaVFBUXc2YUVXamM1ZW5CYzZDUjFVTlpIenBFcmVVdVNMMXZfaFZsNXBHMnIyYUJKbnhQMVBLUHJIQlVRMU8tal9UT1lLNU9XRUQtSWJKSkxpNEZTcnVVSEZMX0hlMW1EM0hEVVFBdnoxeVM1SW9XeFk4c21fRnJKc0Rwa3RhUmRnSy13U3RxdmtGUTB3bE9Db3RBRUdhNkxpNXUwZG9UOE5YRU53?oc=5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>auto-b9057e59b5cb</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Korean Air wechselt in das Terminal 3 - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiowFBVV95cUxNbl9pMWZIanJOV1R1Zzc0NElHOGtwQTNVT3NXa09tSTFuQkFRZlV3T2J0bEtVQWF5cU9sUUZ5c3FfM2RCUU5oLUtFMVhoZlNiYzlRZS1wUjlFMl9QZzFINTdSbTA1S21Za1ZDbmxvZHZMZEpmYW03SDBOY1ZiUXZNQjR4cjVNcW53d19fU0VKRGFlT3hkTndpYm1UVFVKX1h2dHpJ?oc=5" target="_blank"&gt;Flughafen Frankfurt: Korean Air wechselt in das Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbl9pMWZIanJOV1R1Zzc0NElHOGtwQTNVT3NXa09tSTFuQkFRZlV3T2J0bEtVQWF5cU9sUUZ5c3FfM2RCUU5oLUtFMVhoZlNiYzlRZS1wUjlFMl9QZzFINTdSbTA1S21Za1ZDbmxvZHZMZEpmYW03SDBOY1ZiUXZNQjR4cjVNcW53d19fU0VKRGFlT3hkTndpYm1UVFVKX1h2dHpJ?oc=5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>auto-3b4197a584d6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt präsentiert Sommerflugplan - Fliegerweb</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMingFBVV95cUxNS2JnYUVJb2pJSFd2QzZCbzFWb1NCZU5rUDR4UlYtQkJENUVXenlfWUtYUkdUWTl1bzFXR2tYdW5SN19tVzJPa3EzVWtjTWZLTk5vbDFsNVBXdXE4bG5USF9pWEpQclZuZlNyZkRoSXJWUzY2ZEI2OXhHdk9aNjdUbFBUaW5UX29BN1BlVEx2SUxCUTFVY1FFVGU0dGNXQQ?oc=5" target="_blank"&gt;Flughafen Frankfurt präsentiert Sommerflugplan&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fliegerweb&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNS2JnYUVJb2pJSFd2QzZCbzFWb1NCZU5rUDR4UlYtQkJENUVXenlfWUtYUkdUWTl1bzFXR2tYdW5SN19tVzJPa3EzVWtjTWZLTk5vbDFsNVBXdXE4bG5USF9pWEpQclZuZlNyZkRoSXJWUzY2ZEI2OXhHdk9aNjdUbFBUaW5UX29BN1BlVEx2SUxCUTFVY1FFVGU0dGNXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,7 +829,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -860,8 +859,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>review</t>
@@ -894,7 +891,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -925,8 +921,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>review</t>
@@ -959,7 +953,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -990,8 +983,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>review</t>
@@ -1024,7 +1015,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1055,8 +1045,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>review</t>
@@ -1089,7 +1077,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1120,8 +1107,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>review</t>
@@ -1154,7 +1139,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1185,8 +1169,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>review</t>
@@ -1219,7 +1201,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1250,8 +1231,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>review</t>
@@ -1284,7 +1263,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1315,8 +1293,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>review</t>
@@ -1349,7 +1325,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1380,8 +1355,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>review</t>
@@ -1414,7 +1387,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1445,8 +1417,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>review</t>
@@ -1479,7 +1449,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1510,8 +1479,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>review</t>
@@ -1544,7 +1511,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1575,8 +1541,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>review</t>
@@ -1609,7 +1573,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1640,8 +1603,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>review</t>
@@ -1674,7 +1635,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1705,8 +1665,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>review</t>
@@ -1739,7 +1697,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1770,8 +1727,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>review</t>
@@ -1804,7 +1759,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1835,8 +1789,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>review</t>
@@ -1869,7 +1821,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1900,8 +1851,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>review</t>
@@ -1934,7 +1883,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -1965,8 +1913,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>review</t>
@@ -1999,7 +1945,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2030,8 +1975,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>review</t>
@@ -2064,7 +2007,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2095,8 +2037,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>review</t>
@@ -2108,6 +2048,1306 @@
         </is>
       </c>
       <c r="O26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>auto-582d1e9fec70</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ehemalige Spirit-Zentrale für 93 Millionen Dollar verkauft</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Die frühere Unternehmenszentrale von Spirit Airlines in Dania Beach im US-Bundesstaat Florida ist für 93,25 Millionen Dollar verkauft worden. Käufer ist die in Boston ansässige Investmentgesellschaft Hill City Capital. Der Verkauf erfolgt rund 15 Wochen nach der Einstellung des Flugbetriebs von Spirit und ist Teil der Verwertung der früheren Infrastruktur der Fluggesellschaft.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ehemalige-spirit-zentrale-fuer-93-millionen-dollar-verkauft/e2me6nf</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>auto-e04e055d78f8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Europas neue Waffe gegen Waldbrände könnte aus Frankreich kommen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Europas Waldbrandsaisons werden immer verheerender, während viele Löschflugzeuge bereits Jahrzehnte im Einsatz stehen. Die EU hat deshalb neue Canadair 515 bei De Havilland bestellt. In Frankreich denkt Hynaero bereits einen Schritt weiter – mit einem größeren, schnelleren und von Grund auf neu entwickelten Amphibienflugzeug.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/europas-neue-waffe-gegen-waldbraende-koennte-aus-frankreich-kommen/drx93sp</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>auto-ddc525bfd036</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Flughafen Dallas/Fort Worth plant neue Waschstationen für muslimische Reisende</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Der Flughafen Dallas/Fort Worth prüft den Bau zusätzlicher Waschstationen für die rituelle islamische Gebetswaschung. In zwei bestehenden Toiletten im Terminal D sollen dafür jeweils eine Anlage für Männer und Frauen eingerichtet werden. Die geschätzten Kosten liegen bei 300.000 Dollar.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-dallasfort-worth-plant-neue-waschstationen-fuer-muslimische-reisende/qf28wf5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>auto-cfd903c8cbfb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pilatus eröffnet neues Composite-Zentrum im Kanton Nidwalden</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pilatus Aircraft hat am Stammsitz in Stans im Kanton Nidwalden ein neues Kompetenzzentrum für die Entwicklung und Fertigung von Composite-Bauteilen eröffnet. In das Gebäude namens Schwarzhorn investierte der Flugzeughersteller 100 Millionen Franken – laut Pilatus so viel wie noch nie zuvor in ein einzelnes Gebäude.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/pilatus-eroeffnet-neues-composite-zentrum-im-kanton-nidwalden/y7myh8c</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>auto-085e7b431f2b</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Boeing 777F von Lufthansa Cargo hängt in Shanghai fest</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die älteste Boeing 777F von Lufthansa Cargo steht nach einem Startabbruch seit über einer Woche in Shanghai. Nach Informationen von aero.de fiel an der D-ALFA ein Triebwerk aus. Lufthansa Cargo hatte gleich doppelt Pech - das Wetter in Shanghai hat eine Reparatur vor Ort verzögert.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53373/Boeing-777F-von-Lufthansa-Cargo-haengt-in-Shanghai-fest.html</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>auto-11ef7e8ebcc0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: Partnerschaft mit Bangalore International Airport - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisgFBVV95cUxPMWRJdl9kVF9LV2owMVJELTZQc3NIRVVHbDRwMU9IdThab2RCZ1YtWGx3bUNaQm1DZHltM2xCT0RpS2lLQ1ZST1BNeHRKSzFFSmtwTktKN1VDbVk1eUNjcUY1NmlsdEJRakxXVDBEeXdJc1RLSDJJd2djc0NBTUFTTHVtZFpSMmVPb21LNmN5QkhtNmx5dG02bEZ4emF0YXQwbVNUN1FKSVo3UlVENzBUV0hR?oc=5" target="_blank"&gt;Frankfurt Airport: Partnerschaft mit Bangalore International Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPMWRJdl9kVF9LV2owMVJELTZQc3NIRVVHbDRwMU9IdThab2RCZ1YtWGx3bUNaQm1DZHltM2xCT0RpS2lLQ1ZST1BNeHRKSzFFSmtwTktKN1VDbVk1eUNjcUY1NmlsdEJRakxXVDBEeXdJc1RLSDJJd2djc0NBTUFTTHVtZFpSMmVPb21LNmN5QkhtNmx5dG02bEZ4emF0YXQwbVNUN1FKSVo3UlVENzBUV0hR?oc=5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>auto-acf6ef5a95ea</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Condor zieht ins Terminal 3 Frankfurt – Umzug aber erst später geplant - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinAFBVV95cUxQdGZ0ZlJkS1pPSzRpN2NldEVqeUlCRTZWNWVwZ2VjMjF5X0VNSnZvaVBySVBVQWlIUktGSTE3TzUzVzJfQU1ndlVTS0RxdUFxQjVwRzdhZ0FWbi1McmtpYS1pTk1JcWl3VDJoUmxaVkx6bzdmcDNTa3VJV2wzem15MG9icW9FTjdJeTF0cjhkSE9tMVIxYVJlbHd4a2g?oc=5" target="_blank"&gt;Condor zieht ins Terminal 3 Frankfurt – Umzug aber erst später geplant&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdGZ0ZlJkS1pPSzRpN2NldEVqeUlCRTZWNWVwZ2VjMjF5X0VNSnZvaVBySVBVQWlIUktGSTE3TzUzVzJfQU1ndlVTS0RxdUFxQjVwRzdhZ0FWbi1McmtpYS1pTk1JcWl3VDJoUmxaVkx6bzdmcDNTa3VJV2wzem15MG9icW9FTjdJeTF0cjhkSE9tMVIxYVJlbHd4a2g?oc=5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>auto-557123a0c053</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo: First construction phase at Frankfurt Cargo Center completed - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivgFBVV95cUxQMHB3dHg0dFdPOEdFbFJNRndEWXpFcEVOZmQzWTRSMjhveElvTHBQY1VveWl1enJWNVh1SzZtcFZ2WXVVYjdQTlp0VUF1TzJ4WEd2TXFMUTF6N1dHRFNpUXZXSDNueDhKLWtfTVlGQnVsT2l3bHhKWnRBRThESVZ3WmozbUVEek1EZjhjZGtYZV9Zb0o2aDZhSDRCZkR3Qi1OSWpNc3B3OGVhU3ZZTElpWE1zbTN2eXRobm1uQ3VR?oc=5" target="_blank"&gt;Lufthansa Cargo: First construction phase at Frankfurt Cargo Center completed&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQMHB3dHg0dFdPOEdFbFJNRndEWXpFcEVOZmQzWTRSMjhveElvTHBQY1VveWl1enJWNVh1SzZtcFZ2WXVVYjdQTlp0VUF1TzJ4WEd2TXFMUTF6N1dHRFNpUXZXSDNueDhKLWtfTVlGQnVsT2l3bHhKWnRBRThESVZ3WmozbUVEek1EZjhjZGtYZV9Zb0o2aDZhSDRCZkR3Qi1OSWpNc3B3OGVhU3ZZTElpWE1zbTN2eXRobm1uQ3VR?oc=5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>auto-5fa2754c60d3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gewerkschaft droht mit Warnstreiks: Lufthansa holt City Airlines nach Frankfurt - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivwFBVV95cUxNUEtfZW9oMVowUGxCaTJOT3poMWpoRjZQeDNqSHlzMEh6a3NlRDYwRHAzUWoxVzY3a3VGbU1ON3JEZ0FLX2ozNkZ4QjMzS2FqTHhKNGNaVUVrNnVRX0I5bTlsdjZldXhvVGw5a3V5MTVnR2UxUmJCLWc2dW05THhvdW5GdDU3cy02Qm5xczVEYk1EMm1ZMXJCX01vcE9taWJmbzh0T2lLVm9UampLdkRLNG1mNUJERkxWMFg3Ym9wNA?oc=5" target="_blank"&gt;Gewerkschaft droht mit Warnstreiks: Lufthansa holt City Airlines nach Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNUEtfZW9oMVowUGxCaTJOT3poMWpoRjZQeDNqSHlzMEh6a3NlRDYwRHAzUWoxVzY3a3VGbU1ON3JEZ0FLX2ozNkZ4QjMzS2FqTHhKNGNaVUVrNnVRX0I5bTlsdjZldXhvVGw5a3V5MTVnR2UxUmJCLWc2dW05THhvdW5GdDU3cy02Qm5xczVEYk1EMm1ZMXJCX01vcE9taWJmbzh0T2lLVm9UampLdkRLNG1mNUJERkxWMFg3Ym9wNA?oc=5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>auto-cea258772552</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lufthansa City Airlines plant 16 neue Strecken ab Frankfurt und München - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMioAFBVV95cUxPa2tSRGh3RU9fenQySDFaR2hFNTBxTWh1VzRuZENtanQ0LWFLS2Y1XzMySG1GWXVWTkMxaktRVEduQ1VkZnRRLW1GNWN3V1EwZTI0bE40TTBfLWpxRERzQzFVVl9QbXBieC03N1BVQnYwdGt0UXNZVmhKNDJxcU5MaFltLTdKbTI2M1NwMVRWZUlmYXE3aWhxVHQzbEluSkxY?oc=5" target="_blank"&gt;Lufthansa City Airlines plant 16 neue Strecken ab Frankfurt und München&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPa2tSRGh3RU9fenQySDFaR2hFNTBxTWh1VzRuZENtanQ0LWFLS2Y1XzMySG1GWXVWTkMxaktRVEduQ1VkZnRRLW1GNWN3V1EwZTI0bE40TTBfLWpxRERzQzFVVl9QbXBieC03N1BVQnYwdGt0UXNZVmhKNDJxcU5MaFltLTdKbTI2M1NwMVRWZUlmYXE3aWhxVHQzbEluSkxY?oc=5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>auto-6b975d778137</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Linz Airport: Erste DAT-Maschine flog nach Frankfurt, internationale Route ist zurück - MeinBezirk.at</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixAFBVV95cUxPczRyeW0xVElhQzJGT2VHeUc1MWEtdWgzbnBBM0lfNGcwWXZWSVZTSGF5cEZhNEZXMjlCNUJMT1V4cFczdFZTOVp4U2p6VV8xTGZ1UjEtRVk3Zy1vcVBrNXNySWJrcTJEY0xnaHoyUFh4Z1B0aHR6bUIxbVZRaXZrcEVRLTZiY3JmU1V5OHFwTmZEb1ZYQmlIWTlSUmx6dFphaHNYVDlXUUlJVGdxRkN3MmwzUmszNWV3dDdPTU43M3VQMDBS?oc=5" target="_blank"&gt;Linz Airport: Erste DAT-Maschine flog nach Frankfurt, internationale Route ist zurück&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;MeinBezirk.at&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPczRyeW0xVElhQzJGT2VHeUc1MWEtdWgzbnBBM0lfNGcwWXZWSVZTSGF5cEZhNEZXMjlCNUJMT1V4cFczdFZTOVp4U2p6VV8xTGZ1UjEtRVk3Zy1vcVBrNXNySWJrcTJEY0xnaHoyUFh4Z1B0aHR6bUIxbVZRaXZrcEVRLTZiY3JmU1V5OHFwTmZEb1ZYQmlIWTlSUmx6dFphaHNYVDlXUUlJVGdxRkN3MmwzUmszNWV3dDdPTU43M3VQMDBS?oc=5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>auto-9e4d19a6d424</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines bekommt neuen Mega Hub | Größter Airport in Afrika für 110 Millionen Menschen - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwgFBVV95cUxONXpUMGFmWjhEQ2lXeElXT21DZW1HZG12SFRmbHF4akpLaGNWYjRmN3FoZ1BUWjM1VDh4LVNzazhFOVJOWUw3U0xxeXlDakIxbGxuUVY3N19PLUM5SDczRG5RZTJMV1JGUlBxa2FIS0ZiSlpPWkMtVXdndkh0aFd4aHJfZHpzbE11YUFzTW5LRGREWW9pZkk3NHlXM1ZibDNqem94WXUxZHdpM18tOFRXTEtsWmlMZ0p3VlU4X2dWV19kQQ?oc=5" target="_blank"&gt;Ethiopian Airlines bekommt neuen Mega Hub | Größter Airport in Afrika für 110 Millionen Menschen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxONXpUMGFmWjhEQ2lXeElXT21DZW1HZG12SFRmbHF4akpLaGNWYjRmN3FoZ1BUWjM1VDh4LVNzazhFOVJOWUw3U0xxeXlDakIxbGxuUVY3N19PLUM5SDczRG5RZTJMV1JGUlBxa2FIS0ZiSlpPWkMtVXdndkh0aFd4aHJfZHpzbE11YUFzTW5LRGREWW9pZkk3NHlXM1ZibDNqem94WXUxZHdpM18tOFRXTEtsWmlMZ0p3VlU4X2dWV19kQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>auto-6214941e5aa9</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Air China Streckenmeldung: Frankfurt-Route wird teilweise an den Beijing Daxing International verlegt - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiXEFVX3lxTE9lV0NxQldTSGFTcjk4czdGQjZuQTUtUFZfOS15a3JUd25SRkFGbVZTZjJJR2djZjFDSHZ1Q05BOTVsWVVPVWdGTHJPVTZlcUlmLXNiOGo0R3F2QTVy?oc=5" target="_blank"&gt;Air China Streckenmeldung: Frankfurt-Route wird teilweise an den Beijing Daxing International verlegt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9lV0NxQldTSGFTcjk4czdGQjZuQTUtUFZfOS15a3JUd25SRkFGbVZTZjJJR2djZjFDSHZ1Q05BOTVsWVVPVWdGTHJPVTZlcUlmLXNiOGo0R3F2QTVy?oc=5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>auto-6abd7d080a23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SkyTeam Lounges – Überblick, Zugang und neue Lounge in Frankfurt - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiWEFVX3lxTE5JVWlVQ0VUQlRSU29sajcyVE5KODNkT0owWXRDS0l4SVk5Q2NfTDdGMUNKQlY4ak1HUTNDc0F0QjFmSXhEWlhVWnFOeW9DbmtuZmsxV3FOVjc?oc=5" target="_blank"&gt;SkyTeam Lounges – Überblick, Zugang und neue Lounge in Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5JVWlVQ0VUQlRSU29sajcyVE5KODNkT0owWXRDS0l4SVk5Q2NfTDdGMUNKQlY4ak1HUTNDc0F0QjFmSXhEWlhVWnFOeW9DbmtuZmsxV3FOVjc?oc=5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>auto-4b7c58a1fa60</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Neue Airlines und Destinationen am Flughafen Frankfurt - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMioAFBVV95cUxObEFzYkI1dUhRQmVQbkhaVkptb1R1UEhkLVphY2libE8zTlQ5TlRYZDlDOGFGcGpnenF6UThyNXROVF9qb1JIUXBZbTZlbzFJTzNtclVpTWhQTkNXZFVManFrNFB5T3c5eXZwdldKM1BqeEJySkxqRkxEU0ZTa1k0ak1DaXhDQWxLcW12WUdHQ0UwS0FSUFF4aU9QeHFWT1No?oc=5" target="_blank"&gt;Neue Airlines und Destinationen am Flughafen Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxObEFzYkI1dUhRQmVQbkhaVkptb1R1UEhkLVphY2libE8zTlQ5TlRYZDlDOGFGcGpnenF6UThyNXROVF9qb1JIUXBZbTZlbzFJTzNtclVpTWhQTkNXZFVManFrNFB5T3c5eXZwdldKM1BqeEJySkxqRkxEU0ZTa1k0ak1DaXhDQWxLcW12WUdHQ0UwS0FSUFF4aU9QeHFWT1No?oc=5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>auto-a18b1f4d5476</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lufthansa verliert Exklusivität - Flughafen Frankfurt plant Terminal 3 mit Turkish Airlines und Condor - leadersnet.de</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipgFBVV95cUxPMWE3bkpTeHFEc2NyY2FaeGVGeEI1SXhDbG5KQXNLbDRqYlA5M3JPQmtpZGlLZlQ2dXQ0aWVLakpJYVNLTmVUVnNaVmNuN1Z0OGpwdll1dlFRSXJQMXVxTkpBY1FHbWE0V0dTV0lBUk5Pa2FKMDY2MF9wWS1wemdiZUZKVWY3VEdTSTdrVnczdkF6eE1EaUZaYURuTndUb0N2UGZPdGZ3?oc=5" target="_blank"&gt;Lufthansa verliert Exklusivität - Flughafen Frankfurt plant Terminal 3 mit Turkish Airlines und Condor&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;leadersnet.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPMWE3bkpTeHFEc2NyY2FaeGVGeEI1SXhDbG5KQXNLbDRqYlA5M3JPQmtpZGlLZlQ2dXQ0aWVLakpJYVNLTmVUVnNaVmNuN1Z0OGpwdll1dlFRSXJQMXVxTkpBY1FHbWE0V0dTV0lBUk5Pa2FKMDY2MF9wWS1wemdiZUZKVWY3VEdTSTdrVnczdkF6eE1EaUZaYURuTndUb0N2UGZPdGZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>auto-d20e5f3f4a80</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt präsentiert Sommerflugplan - Fliegerweb</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMingFBVV95cUxPMFVCdjI5M2VEeUxtRnpCQ3kwZ3hoYXFOa0o0RGM2MlRPLVBrSzZnRkxxa1FzOUROTWU1QkNmOFpYZkhsZVBOdXBLQ2RsVm1vY0lTanJEMEZ6VnRrWXlhWlJjZC03Y3hYQ1pab3VCeHhOanFjSm1GS0JXb2pKQjVrdW5DYkZQbVZsMnpscnNHcUZfTVZNalhMTlFyVzJNQQ?oc=5" target="_blank"&gt;Flughafen Frankfurt präsentiert Sommerflugplan&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fliegerweb&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMFVCdjI5M2VEeUxtRnpCQ3kwZ3hoYXFOa0o0RGM2MlRPLVBrSzZnRkxxa1FzOUROTWU1QkNmOFpYZkhsZVBOdXBLQ2RsVm1vY0lTanJEMEZ6VnRrWXlhWlJjZC03Y3hYQ1pab3VCeHhOanFjSm1GS0JXb2pKQjVrdW5DYkZQbVZsMnpscnNHcUZfTVZNalhMTlFyVzJNQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>auto-b4812d4d6aef</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Übersicht der Lounges am Flughafen Frankfurt - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMigAFBVV95cUxOVTAxc3JaYkh5UWpqWnZOdmVZUHJUQkRRQWFBRXBtM0pIMVU3bkoyVTVJSEhLZ2k2SlJmLWRlUmwwbHFaa0NIc0U0aDBURVdPcjdtNnBoZUZ5eWZkWFUtMTgtNFpNTl9Zb1ZwMjlMUEFDVEtMblpoYjBNSTFfRTNhVA?oc=5" target="_blank"&gt;Übersicht der Lounges am Flughafen Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVTAxc3JaYkh5UWpqWnZOdmVZUHJUQkRRQWFBRXBtM0pIMVU3bkoyVTVJSEhLZ2k2SlJmLWRlUmwwbHFaa0NIc0U0aDBURVdPcjdtNnBoZUZ5eWZkWFUtMTgtNFpNTl9Zb1ZwMjlMUEFDVEtMblpoYjBNSTFfRTNhVA?oc=5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>auto-959d5637856f</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winterflugplan 2024/25: Frankfurt bleibt Deutschlands wichtigstes Drehkreuz - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcGJod1dsUnNfV1VlMUdwYnIyZi0zMWZiT1VOSkRPWUJ0bE1ROWw4RF8zZlpDY3hLT0ZfNll1RGY3djBOWXVwNG1LWW9tZ0FEUHY3RXcwWGNOX21PY1phQk1rU0NLRDlqNEQ2ZGhxcTB3Y3I1N2NaYkVrOHpwT1g3Wi00VkxQbXZKOXBvdkVFT2k4WWVZcEkyUGRicFVyNmJuR1E2Ukd4UGZLZ01XY0tEdy1INF9XNFpn?oc=5" target="_blank"&gt;Winterflugplan 2024/25: Frankfurt bleibt Deutschlands wichtigstes Drehkreuz&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcGJod1dsUnNfV1VlMUdwYnIyZi0zMWZiT1VOSkRPWUJ0bE1ROWw4RF8zZlpDY3hLT0ZfNll1RGY3djBOWXVwNG1LWW9tZ0FEUHY3RXcwWGNOX21PY1phQk1rU0NLRDlqNEQ2ZGhxcTB3Y3I1N2NaYkVrOHpwT1g3Wi00VkxQbXZKOXBvdkVFT2k4WWVZcEkyUGRicFVyNmJuR1E2Ukd4UGZLZ01XY0tEdy1INF9XNFpn?oc=5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>auto-fc40670c1c0f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Korean Air kommt mit A380 nach Frankfurt - aboutTravel</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMigwFBVV95cUxOb0swTF9rN1M0ek1URFF5elBmbEM0ZUdmU0ZLRVdwTDJZVVBBUERPRk41YTltejVVZEE1YjM5bWNvdXpUY3owa2tmcHJMN0dlTVZseFluVS1KNHdfWWlLTVhBa3dycEdSYXRid3ZhSkRHYnp5bnVodHlRdWdHenJ4dV9xVQ?oc=5" target="_blank"&gt;Korean Air kommt mit A380 nach Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aboutTravel&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOb0swTF9rN1M0ek1URFF5elBmbEM0ZUdmU0ZLRVdwTDJZVVBBUERPRk41YTltejVVZEE1YjM5bWNvdXpUY3owa2tmcHJMN0dlTVZseFluVS1KNHdfWWlLTVhBa3dycEdSYXRid3ZhSkRHYnp5bnVodHlRdWdHenJ4dV9xVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2069,7 +2069,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2100,8 +2099,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>review</t>
@@ -2134,7 +2131,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2165,8 +2161,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>review</t>
@@ -2199,7 +2193,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2230,8 +2223,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>review</t>
@@ -2264,7 +2255,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2295,8 +2285,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>review</t>
@@ -2329,7 +2317,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2360,8 +2347,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>review</t>
@@ -2394,7 +2379,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2425,8 +2409,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>review</t>
@@ -2459,7 +2441,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2490,8 +2471,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>review</t>
@@ -2524,7 +2503,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2555,8 +2533,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>review</t>
@@ -2589,7 +2565,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2620,8 +2595,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>review</t>
@@ -2654,7 +2627,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2685,8 +2657,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>review</t>
@@ -2719,7 +2689,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2750,8 +2719,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>review</t>
@@ -2784,7 +2751,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2815,8 +2781,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>review</t>
@@ -2849,7 +2813,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2880,8 +2843,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>review</t>
@@ -2914,7 +2875,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -2945,8 +2905,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>review</t>
@@ -2979,7 +2937,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3010,8 +2967,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>review</t>
@@ -3044,7 +2999,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3075,8 +3029,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>review</t>
@@ -3109,7 +3061,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3140,8 +3091,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>review</t>
@@ -3174,7 +3123,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3205,8 +3153,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>review</t>
@@ -3239,7 +3185,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3270,8 +3215,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>review</t>
@@ -3304,7 +3247,6 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3335,8 +3277,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>review</t>
@@ -3348,6 +3288,1306 @@
         </is>
       </c>
       <c r="O46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>auto-56c9147d9778</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Flughafen Weeze baut neues Ankunftsterminal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Der Flughafen Weeze erweitert wegen steigender Passagierzahlen und eines wachsenden Streckenangebots seine Infrastruktur. Am Freitag (14. August) erfolgte der Spatenstich für ein neues Ankunftsterminal, das bis Mitte 2027 fertiggestellt werden soll. Auf knapp 5000 Quadratmetern entsteht ein zweigeschossiges Gebäude. Die rund 3900 Quadratmeter große Passagierhalle erhält getrennte Ankunftsbereiche für Reisende aus dem Schengen- und Non-Schengen-Raum sowie einen Wartebereich für Abholer. Auch Zoll und Bundespolizei erhalten dort Flächen. Im Obergeschoss entstehen auf rund 1200 Quadratmetern Büros für die Flughafenverwaltung.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-weeze-baut-neues-ankunftsterminal/kd3xfle</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>auto-c38a6d963ca7</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Massive Flugausfälle bei Easyjet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PARIS - Wegen eines Streiks des Kabinenpersonals fallen an diesem Wochenende zahlreiche Easyjet-Flüge in Frankreich aus. Französischen Medien zufolge wurden mehr als 100 Verbindungen gestrichen.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53380/Massive-Flugausfaelle-bei-Easyjet.html</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>auto-43842d403c36</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Qatar Airways plant zwei Lounges im Frankfurter Terminal 3 - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBvZFV6dEg2TXZBUngtS1pPdHRWRGk1X3RUVF84d2xwVWg0dGNrVDdvbWNtZFpOeFVrb05HdndZdk1OeVdvbEwzTGNXY1VPb3VLcXJRNU9PODBMeDNicUZRZ1pBZDVYWEU?oc=5" target="_blank"&gt;Qatar Airways plant zwei Lounges im Frankfurter Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBvZFV6dEg2TXZBUngtS1pPdHRWRGk1X3RUVF84d2xwVWg0dGNrVDdvbWNtZFpOeFVrb05HdndZdk1OeVdvbEwzTGNXY1VPb3VLcXJRNU9PODBMeDNicUZRZ1pBZDVYWEU?oc=5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>auto-f4d2bb972933</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DHL Global Forwarding: New Air Freight Hub at Frankfurt Airport - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqwFBVV95cUxOdzZUWHRuMkZ3TGZWZk14Y1VKbGNUUHlLdTFBY1UwbDlPT1d6OV9SbjJjcHk0dVJCZDNSOEZlQWJfRVEwQzF5WkFUajFERFhCcjF4SUZSeDdUR2Q4RF9iZXdDRzdsT0NqMkdyYjdrblFFSjZ4ZkNGVnJnMUFKZzgza0ZfWGwxV1lQdEMzVkJDdExPMmlKdFA3bGpCZkx5RkdnVWtPaXNja1RxQzQ?oc=5" target="_blank"&gt;DHL Global Forwarding: New Air Freight Hub at Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOdzZUWHRuMkZ3TGZWZk14Y1VKbGNUUHlLdTFBY1UwbDlPT1d6OV9SbjJjcHk0dVJCZDNSOEZlQWJfRVEwQzF5WkFUajFERFhCcjF4SUZSeDdUR2Q4RF9iZXdDRzdsT0NqMkdyYjdrblFFSjZ4ZkNGVnJnMUFKZzgza0ZfWGwxV1lQdEMzVkJDdExPMmlKdFA3bGpCZkx5RkdnVWtPaXNja1RxQzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>auto-ba29fc164c5f</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Der Winter zieht auch am Flughafen Frankfurt neue Airlines an - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikgFBVV95cUxNcXRmdno5ZE5Gci1fV2xlbFVlSGZUQm52U29tMGFOMVVpNGJSZGJSSzd1ZFNHR2FKdFQ5TUt1ZVdLZF84a1VZT3IwLTJPdTQzMjZsYzNhdDgyX0ZqbHNpRmVJS3BCZ0Q5dE9sazZkYzI3clpMc0VkblBrWjJ3T0xRMkRJaXlfd1FHOF91NzRBLU9TUQ?oc=5" target="_blank"&gt;Der Winter zieht auch am Flughafen Frankfurt neue Airlines an&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNcXRmdno5ZE5Gci1fV2xlbFVlSGZUQm52U29tMGFOMVVpNGJSZGJSSzd1ZFNHR2FKdFQ5TUt1ZVdLZF84a1VZT3IwLTJPdTQzMjZsYzNhdDgyX0ZqbHNpRmVJS3BCZ0Q5dE9sazZkYzI3clpMc0VkblBrWjJ3T0xRMkRJaXlfd1FHOF91NzRBLU9TUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>auto-58ea035d66c3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Am Frankfurt Airport: AHS fertigt südkoreanischen Billigflieger ab - fvw.de</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisAFBVV95cUxQRU03a082a3VoVVVmSVpqNUVNeGdqZmpqNC1YN2NtU3I0SGRVRXpGMkZpek1Ba2V6cFM2NThyanZuelA2eFZ1bFhUX3NQM3dxZUpiNnlBLWJ4bWw0bWI3MnJIalAwRkVVdnJMZGRwaGtPUFZYTEJvNFV2NFRIMVR5QWJEeDBoS2p0NG53QVNaLVp1RmY5SURqOVZPWmdPWm1aSTB2WlNQYUxhUTY5ek9fbg?oc=5" target="_blank"&gt;Am Frankfurt Airport: AHS fertigt südkoreanischen Billigflieger ab&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQRU03a082a3VoVVVmSVpqNUVNeGdqZmpqNC1YN2NtU3I0SGRVRXpGMkZpek1Ba2V6cFM2NThyanZuelA2eFZ1bFhUX3NQM3dxZUpiNnlBLWJ4bWw0bWI3MnJIalAwRkVVdnJMZGRwaGtPUFZYTEJvNFV2NFRIMVR5QWJEeDBoS2p0NG53QVNaLVp1RmY5SURqOVZPWmdPWm1aSTB2WlNQYUxhUTY5ek9fbg?oc=5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>auto-cd7d7859afbd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Keine Spezialrabatte: Ryanairs ungewisse Rückkehr zum Flughafen Frankfurt - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxPOGZEb09vUTYwckRPcDk0NWJ1X2pnNnF3VGtTUDVWQ1BOYllKVGFEVk05Vl9LcER6SVd1ZkpPTTlwb0kyUHdJcmRjWjJHTmdKemxfY1FBQV80RlF5ZWdYeUdmMVdUQWo1ZG51TEp5RkhvWXhvUFBhMmlJU3Q2YUZDM3BJcmxxSHdsLXJhdnRJLVpQT1JFV0VmSXNDaEw0RGRNaVE?oc=5" target="_blank"&gt;Keine Spezialrabatte: Ryanairs ungewisse Rückkehr zum Flughafen Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPOGZEb09vUTYwckRPcDk0NWJ1X2pnNnF3VGtTUDVWQ1BOYllKVGFEVk05Vl9LcER6SVd1ZkpPTTlwb0kyUHdJcmRjWjJHTmdKemxfY1FBQV80RlF5ZWdYeUdmMVdUQWo1ZG51TEp5RkhvWXhvUFBhMmlJU3Q2YUZDM3BJcmxxSHdsLXJhdnRJLVpQT1JFV0VmSXNDaEw0RGRNaVE?oc=5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>auto-a867cefdb7b4</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nippon Cargo Airlines kehrt mit Boeing 747-8 F nach Frankfurt zurück - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxNRkxOeVJmRDRsTHJValhZT1dWQXFuNnpiY051WXZOZDVDbkJPZVJlNFpENmhyeV9wTDF2Z0M2eXU1clZGOTEtR1hnRUdYaGdPUjZXb0dDSG51a3BjNEUtSWFCRjRGQmY2eW1RMFZ5VXRfY295Skd6bm9sd3A5bVYwOHpNLURQU1dYT19NSTc5TnJMT084VElzOXROWXpxRExQRHl1V2JYYUNqcWlteEJ0VmdFZGQ?oc=5" target="_blank"&gt;Nippon Cargo Airlines kehrt mit Boeing 747-8 F nach Frankfurt zurück&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRkxOeVJmRDRsTHJValhZT1dWQXFuNnpiY051WXZOZDVDbkJPZVJlNFpENmhyeV9wTDF2Z0M2eXU1clZGOTEtR1hnRUdYaGdPUjZXb0dDSG51a3BjNEUtSWFCRjRGQmY2eW1RMFZ5VXRfY295Skd6bm9sd3A5bVYwOHpNLURQU1dYT19NSTc5TnJMT084VElzOXROWXpxRExQRHl1V2JYYUNqcWlteEJ0VmdFZGQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>auto-af7b95806391</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mit Discover von Frankfurt nach Kittilä - Fliegerweb</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilAFBVV95cUxOUk55VTFpbWJWeUhzYlBTWWU2Vk9DZW9LRXFjSW5HZDR6U3pQLU5XNW5QdHdzVERhdG1iVjQ3aGhiMTV5UXRMczBrdzhDY0pGMkFzdDFLZS12TXFnNGFxeV9XVDdqSVlnUmFFUEZySHRGSng0bUlJNVdXbGZITE11Q2tBRUdlcnA1TXlGMGh5cFdMOUFQ?oc=5" target="_blank"&gt;Mit Discover von Frankfurt nach Kittilä&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fliegerweb&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOUk55VTFpbWJWeUhzYlBTWWU2Vk9DZW9LRXFjSW5HZDR6U3pQLU5XNW5QdHdzVERhdG1iVjQ3aGhiMTV5UXRMczBrdzhDY0pGMkFzdDFLZS12TXFnNGFxeV9XVDdqSVlnUmFFUEZySHRGSng0bUlJNVdXbGZITE11Q2tBRUdlcnA1TXlGMGh5cFdMOUFQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>auto-dd01e1e5cd62</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Aufgepasst bei der Buchung: Singapore Airlines zieht mal wieder den Airbus A380 von Frankfurt-Flügen ab - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiygFBVV95cUxNN1dIWHJwLWpLRUU4azVCQnRZaTZpMDVTeC1uQjd4VC1KbkVReW1SV0htclcxc0pXbzVZaDlBYktRdnJnQy1HeElhVGdCUFROLVdjLXBVQXVhdmhmajYzR0E1eTFYd3pfcHJ0Q1MxQVl4VEpIaThHQXp1aE5kVE1Md3FCN3ljTkpaRGRERVJqR0RXNFFKVFRoUTFjaUVaekpSVkZnQlBRZDEzbnhDbDdCb1BHcnU2LURqWnQ3QzVLUVRGYmtXZVhSLWJR?oc=5" target="_blank"&gt;Aufgepasst bei der Buchung: Singapore Airlines zieht mal wieder den Airbus A380 von Frankfurt-Flügen ab&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNN1dIWHJwLWpLRUU4azVCQnRZaTZpMDVTeC1uQjd4VC1KbkVReW1SV0htclcxc0pXbzVZaDlBYktRdnJnQy1HeElhVGdCUFROLVdjLXBVQXVhdmhmajYzR0E1eTFYd3pfcHJ0Q1MxQVl4VEpIaThHQXp1aE5kVE1Md3FCN3ljTkpaRGRERVJqR0RXNFFKVFRoUTFjaUVaekpSVkZnQlBRZDEzbnhDbDdCb1BHcnU2LURqWnQ3QzVLUVRGYmtXZVhSLWJR?oc=5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>auto-664e12561e4b</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Air China holt die Boeing 747-8 nach Frankfurt zurück - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSEg3djFEenBKU2ZuV2pJSzRza0pLRUktTllqem5pYkhqT0RBTFhhaHlkXzdRbWNGTnBVSHBPcWcxRXV6ckd2ZVZMWUhfSjJRbFU2UGdUN1hfdnpGN3FpUTNSTUFMalpmelVvR0ZHR3dHa1BteDNrNTVyODd4YW5VQnh3WFZZa1dJ?oc=5" target="_blank"&gt;Air China holt die Boeing 747-8 nach Frankfurt zurück&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSEg3djFEenBKU2ZuV2pJSzRza0pLRUktTllqem5pYkhqT0RBTFhhaHlkXzdRbWNGTnBVSHBPcWcxRXV6ckd2ZVZMWUhfSjJRbFU2UGdUN1hfdnpGN3FpUTNSTUFMalpmelVvR0ZHR3dHa1BteDNrNTVyODd4YW5VQnh3WFZZa1dJ?oc=5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>auto-bc1cafca6e56</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Winterflugplan 2025/26: Warum Air Astana die Abflugzeiten in FRA ändert - fvw.de</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivAFBVV95cUxPVldBX0M3SHpCYVRZUEZ6UVprTkR1c2d3QTB2QmFvWXJiYllmZkY1UlRjYXBYNGFIVVJkWnJPLUU3dU00eGV5a0EyU041Y0xpb3VxU0N0aFlCUVEzUmplR25fTDIzQkJkdFRHWUN5V2dETVdiQkFia3Bub1Rqb19RRl9tQjBEamhyYmk4X0RQOWlIN2ZEUE92dWRoTDU4MFBGQXBXcHNTS1p4cUFWU2I0UUxFOWRSRDFhZ2pKdw?oc=5" target="_blank"&gt;Winterflugplan 2025/26: Warum Air Astana die Abflugzeiten in FRA ändert&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVldBX0M3SHpCYVRZUEZ6UVprTkR1c2d3QTB2QmFvWXJiYllmZkY1UlRjYXBYNGFIVVJkWnJPLUU3dU00eGV5a0EyU041Y0xpb3VxU0N0aFlCUVEzUmplR25fTDIzQkJkdFRHWUN5V2dETVdiQkFia3Bub1Rqb19RRl9tQjBEamhyYmk4X0RQOWlIN2ZEUE92dWRoTDU4MFBGQXBXcHNTS1p4cUFWU2I0UUxFOWRSRDFhZ2pKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>auto-1f33ea88e494</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Discover Airlines erweitert im Sommer 2025 das Skandinavien-Angebot - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimgFBVV95cUxPejlmRS1Qc1QzNnJ6REZmT2R1Z3U2ckp0a0s1bTZIM0l4WnNuMjhTQmdkcEszS1I1NEhTMGhRM1R3ZGxINlZvRmp4a2k1LUVidm56LVo5eS13NWxfakx3d04xa08yZE4zQjZBSlNYTl9jRUk1OWVJcHR4SzZJWXp5UFlvRUQwSzFpUV9UWDd1bUpZanZEMzc5TEN3?oc=5" target="_blank"&gt;Discover Airlines erweitert im Sommer 2025 das Skandinavien-Angebot&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPejlmRS1Qc1QzNnJ6REZmT2R1Z3U2ckp0a0s1bTZIM0l4WnNuMjhTQmdkcEszS1I1NEhTMGhRM1R3ZGxINlZvRmp4a2k1LUVidm56LVo5eS13NWxfakx3d04xa08yZE4zQjZBSlNYTl9jRUk1OWVJcHR4SzZJWXp5UFlvRUQwSzFpUV9UWDd1bUpZanZEMzc5TEN3?oc=5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>auto-ff02d9a9433f</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Review: Air Canada Maple Leaf Lounge Frankfurt - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMif0FVX3lxTFA4NzJURnlyalRwRFFTTlZIdzJweDdXalVLVWoteElabkpaeXFrUW9GRy1ycEdmX1hGOGJoRWF6SVFEZWhKb0gzbldtVGNwN3hqRE5UOGttLXpCVE9GbjhieFlkMUowckUwbHpiUWprQWg4OC0yYTlCLUZHSFFLRU0?oc=5" target="_blank"&gt;Review: Air Canada Maple Leaf Lounge Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFA4NzJURnlyalRwRFFTTlZIdzJweDdXalVLVWoteElabkpaeXFrUW9GRy1ycEdmX1hGOGJoRWF6SVFEZWhKb0gzbldtVGNwN3hqRE5UOGttLXpCVE9GbjhieFlkMUowckUwbHpiUWprQWg4OC0yYTlCLUZHSFFLRU0?oc=5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>auto-17ac385d482b</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Coronavirus epidemic hurts Frankfurt Airport - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilgFBVV95cUxOdlJDcndGaUJINDkwRUNHeWRtS0hvV1RFLUt4ZW4xbHNjRjlpei0tUGJIZnlReGRUc3BUUDlMYTVYU3Z6emlFdEVCSTduVkZtUHZJQWVlWlU4bmI4Wjd6bFNYc2trZ1lrVUpidG5ZN1FPYkxIMG5CbWRDX3hRWXh0SHdROTI5MzlFWWVVVnVCVWx4TlROZXc?oc=5" target="_blank"&gt;Coronavirus epidemic hurts Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdlJDcndGaUJINDkwRUNHeWRtS0hvV1RFLUt4ZW4xbHNjRjlpei0tUGJIZnlReGRUc3BUUDlMYTVYU3Z6emlFdEVCSTduVkZtUHZJQWVlWlU4bmI4Wjd6bFNYc2trZ1lrVUpidG5ZN1FPYkxIMG5CbWRDX3hRWXh0SHdROTI5MzlFWWVVVnVCVWx4TlROZXc?oc=5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>auto-b414231cb15e</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kurzer Abstecher: Discover Airlines streicht Flüge nach Tulum - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikgFBVV95cUxNR25tdDVyUktQdzBKaU9yNllnZlpfTzM1NzZ0ZFZMRlhwV3lrRzEzZXkxNlhQR3VLQ1pfMWIzd1FncEVnOHhUY0ZtcDh3b2lBb3pMbzNtYUZFUlNtTzUwa3E5MEhnV3ZRSldMcUxGYm9yUEUxdlgzVEExQ2dMOVBGbGRKVGluci1HTWZMdHhIRWFtZw?oc=5" target="_blank"&gt;Kurzer Abstecher: Discover Airlines streicht Flüge nach Tulum&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNR25tdDVyUktQdzBKaU9yNllnZlpfTzM1NzZ0ZFZMRlhwV3lrRzEzZXkxNlhQR3VLQ1pfMWIzd1FncEVnOHhUY0ZtcDh3b2lBb3pMbzNtYUZFUlNtTzUwa3E5MEhnV3ZRSldMcUxGYm9yUEUxdlgzVEExQ2dMOVBGbGRKVGluci1HTWZMdHhIRWFtZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>auto-851080776676</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Singapore Airlines streicht zwei Flüge der fünften Freiheit aus dem Flugplan - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqAFBVV95cUxNV2IwYkRGSEZmRFgwQzY1cnhxTXhYNFpUQlFLT0l3MmphaEFkcnFXRzZ1YU10THBtNnlqQmEyQ2E4OXNpWkEydF9NckRDUjlWelQzTkZyUTF6bmdEU21fdVNzb2FTdVplLUR3UFdhWl9EXy1HQnRfbWNsWVR6QW0taTF4SHdZa3NYVzVmcjZHX1V5SjQ4ejAzbHYyVTVLLU5xTTNMbXlkaTA?oc=5" target="_blank"&gt;Singapore Airlines streicht zwei Flüge der fünften Freiheit aus dem Flugplan&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNV2IwYkRGSEZmRFgwQzY1cnhxTXhYNFpUQlFLT0l3MmphaEFkcnFXRzZ1YU10THBtNnlqQmEyQ2E4OXNpWkEydF9NckRDUjlWelQzTkZyUTF6bmdEU21fdVNzb2FTdVplLUR3UFdhWl9EXy1HQnRfbWNsWVR6QW0taTF4SHdZa3NYVzVmcjZHX1V5SjQ4ejAzbHYyVTVLLU5xTTNMbXlkaTA?oc=5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>auto-31e7b84062f4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Langstreckenkomfort auf der Kurzstrecke: Discover Airlines fliegt mit A330 nach Mallorca - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxPSzJBYWkxZ3E4aXlERFBHR1plZ0t0MzktZGYtZUotRWdwM1g2c2J4a0xuRVN1Q09HOXBTc3dVVlpxZEY3RXM1bnNqS2xMM2dPS01GRTZEU0doMW4teHZRRU5ZZDNFRGgyLVFUMXVTd3RleWt0ZDZkTEppVHNhbFBiNE1nNFlJSk5uMEZNY3VMejVpTEgwSS1HQ09HemFKU0tCMThSMERaVk92dm43WmJmYjRxVVo?oc=5" target="_blank"&gt;Langstreckenkomfort auf der Kurzstrecke: Discover Airlines fliegt mit A330 nach Mallorca&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPSzJBYWkxZ3E4aXlERFBHR1plZ0t0MzktZGYtZUotRWdwM1g2c2J4a0xuRVN1Q09HOXBTc3dVVlpxZEY3RXM1bnNqS2xMM2dPS01GRTZEU0doMW4teHZRRU5ZZDNFRGgyLVFUMXVTd3RleWt0ZDZkTEppVHNhbFBiNE1nNFlJSk5uMEZNY3VMejVpTEgwSS1HQ09HemFKU0tCMThSMERaVk92dm43WmJmYjRxVVo?oc=5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>auto-9b315e6288df</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Einmalig: Condor fliegt Düsseldorf–Frankfurt mit Langstreckenjet - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilgFBVV95cUxNb1UyWDd0amplY0RZYXdRTFI4VUxyUlhDLTE0S2Z4Y2VJd1VxTHhobzZ1dEk2dVVoVzR6QkNrb25XOEE0a1g1SnRVLW5WZGhndDVubGxXNS1YOVdRcFdrU3MwVkNCcVlQWjY0ZWd5YW9OOHpNNUkzQmNvTXhLaGdsZGNRa1FNcy03TkY1ZEwzOGxDU1lJSGc?oc=5" target="_blank"&gt;Einmalig: Condor fliegt Düsseldorf–Frankfurt mit Langstreckenjet&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNb1UyWDd0amplY0RZYXdRTFI4VUxyUlhDLTE0S2Z4Y2VJd1VxTHhobzZ1dEk2dVVoVzR6QkNrb25XOEE0a1g1SnRVLW5WZGhndDVubGxXNS1YOVdRcFdrU3MwVkNCcVlQWjY0ZWd5YW9OOHpNNUkzQmNvTXhLaGdsZGNRa1FNcy03TkY1ZEwzOGxDU1lJSGc?oc=5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>auto-0861a1668b88</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Discover Airlines fährt Nordamerika-Programm runter - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMihgFBVV95cUxQTkM3V1RpcUhaNVZGdXFWUHJucGF2U2R1dFB6eHoyV3pmV3dONFlnTHBOU2wwN05BVGJkUzBYc3dIX2R1blZWRHZiT05pRXpSS0ltbWxUQjV0bnI5LTYtWUVjekU3YmFRX290aHdiV2QzQjVvNTJRd1l3aXhMQkV5RkFuQUxkQQ?oc=5" target="_blank"&gt;Discover Airlines fährt Nordamerika-Programm runter&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQTkM3V1RpcUhaNVZGdXFWUHJucGF2U2R1dFB6eHoyV3pmV3dONFlnTHBOU2wwN05BVGJkUzBYc3dIX2R1blZWRHZiT05pRXpSS0ltbWxUQjV0bnI5LTYtWUVjekU3YmFRX290aHdiV2QzQjVvNTJRd1l3aXhMQkV5RkFuQUxkQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3309,7 +3309,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3340,8 +3339,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>review</t>
@@ -3374,7 +3371,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3405,8 +3401,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>review</t>
@@ -3439,7 +3433,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3470,8 +3463,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>review</t>
@@ -3504,7 +3495,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3535,8 +3525,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>review</t>
@@ -3569,7 +3557,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3600,8 +3587,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>review</t>
@@ -3634,7 +3619,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3665,8 +3649,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>review</t>
@@ -3699,7 +3681,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3730,8 +3711,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>review</t>
@@ -3764,7 +3743,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3795,8 +3773,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>review</t>
@@ -3829,7 +3805,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3860,8 +3835,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>review</t>
@@ -3894,7 +3867,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3925,8 +3897,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>review</t>
@@ -3959,7 +3929,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -3990,8 +3959,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>review</t>
@@ -4024,7 +3991,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4055,8 +4021,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>review</t>
@@ -4089,7 +4053,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4120,8 +4083,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>review</t>
@@ -4154,7 +4115,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4185,8 +4145,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>review</t>
@@ -4219,7 +4177,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4250,8 +4207,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>review</t>
@@ -4284,7 +4239,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4315,8 +4269,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>review</t>
@@ -4349,7 +4301,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4380,8 +4331,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>review</t>
@@ -4414,7 +4363,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4445,8 +4393,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>review</t>
@@ -4479,7 +4425,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4510,8 +4455,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>review</t>
@@ -4544,7 +4487,6 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4575,8 +4517,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>review</t>
@@ -4588,6 +4528,1306 @@
         </is>
       </c>
       <c r="O66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>auto-31bcf447b497</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ASL Airlines Australia erhält vier zusätzliche Boeing 737-800 BCF</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ASL Aviation Holdings baut die Flotte seiner australischen Tochter ASL Airlines Australia aus. Bis Ende 2026 sollen vier zu Frachtern umgebaute Boeing 737-800 BCF hinzukommen. Der erste soll im September nach Australien überführt werden und wenige Wochen später den Betrieb aufnehmen. Die Einsatzplanung für alle vier zusätzlichen Frachter wird derzeit noch abgeschlossen, berichtet das Portal Cargo Facts.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/asl-airlines-australia-erhaelt-vier-zusaetzliche-boeing-737-800-bcf/0kbyg79</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>auto-089ecd6b3c81</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Umbau zum Frachter der ersten Boeing 777 für Ethiopian Airlines hat begonnen</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Die erste für Ethiopian Airlines bestimmte Boeing 777-300 ER ist zur Umrüstung in Israel eingetroffen. Der16 Jahre Jet mit der Seriennummer 38285 flog zuvor als SU-GDM für Egypt Air und gehört dem Leasingunternehmen Aercap. Israel Aerospace Industries IAI wird den ehemaligen Passagierjet in Tel Aviv zum Frachter umbauen, berichtetd as Portal News Aero. Ethiopian hatte im März 2026 mit AerCap Leasingverträge für zwei 777-300 ERSF vereinbart und soll damit erster Betreiber des Musters in Afrika werden.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/umbau-zum-frachter-der-ersten-boeing-777-fuer-ethiopian-airlines-hat-begonnen/xm4cy8z</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>auto-8114288687f3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Embraer erwägt neue Endmontagelinien auch in den USA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Embraer prüft angesichts der hohen Nachfrage den Aufbau zusätzlicher Flugzeug-Endmontagelinien in Indien und den USA. Wie Konzernchef Francisco Gomes Neto erklärte, laufen mit Indien Gespräche über eine Fertigung des Militärtransporters KC-390. Später könnte dort möglicherweise auch die Montage von Verkehrsflugzeugen hinzukommen, berichtet die Zeitung &lt;a href="https://oglobo.globo.com/economia/negocios/noticia/2026/08/10/embraer-estuda-ampliar-capacidade-de-producao-global-com-linhas-de-montagem-nos-eua-e-india-diz-ceo-da-empresa.ghtml" id="56ebf127-ce74-485d-a69d-a180f91ccc04" data-link-role-code="target_blank"&gt;O Globo&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/embraer-erwaegt-neue-endmontagelinien-auch-in-den-usa/8s2hmfq</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>auto-51c4ce3a8b9a</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Paris-Charles de Gaulle Airport: Air France seit 30 Jahren am Drehkreuz CDG - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiugFBVV95cUxPQTVPTnk5X1dhdmZuY2F6WmdhRnlqRnVKNGRacDAzaTdFR2kxSjhSSzhoOFM0MVROdTJtUlhRMU5vY05jaDkwaHVOYlBIWUJWVU13bUl0Q0FsZHFiRWU1RHNES2ZudFVHZkJVMFAxSzZSZVBma0c2cTl2bXhKMFA3ak1XQzU4Z3A3aF9rdnM2c2RsQ3dUUzZmaWhxdm1EMDMyVkdNSmhMWlJoS1c5RVZBdUNrTE5DMVp5Mmc?oc=5" target="_blank"&gt;Paris-Charles de Gaulle Airport: Air France seit 30 Jahren am Drehkreuz CDG&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQTVPTnk5X1dhdmZuY2F6WmdhRnlqRnVKNGRacDAzaTdFR2kxSjhSSzhoOFM0MVROdTJtUlhRMU5vY05jaDkwaHVOYlBIWUJWVU13bUl0Q0FsZHFiRWU1RHNES2ZudFVHZkJVMFAxSzZSZVBma0c2cTl2bXhKMFA3ak1XQzU4Z3A3aF9rdnM2c2RsQ3dUUzZmaWhxdm1EMDMyVkdNSmhMWlJoS1c5RVZBdUNrTE5DMVp5Mmc?oc=5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>auto-e5b373b19a9f</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brussels Airlines setzt Airbus A330 einmalig zwischen Frankfurt und Brüssel ein - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqwFBVV95cUxNR3ItU3ZVOUUxcDJJT0tkNlJrbTBGS3oyYm1iRjBsM1ZpOEUtSE1LaUpPMjFTd0dJcG9LRE1IYUNCbVZNNGp4S3BiZUdzMzZzUmM3a0wzTWx0d3JLc0xaQ1NBbEdTMDhkOXFlYzUxTVRqRHlWN2x2SDNuV1hxWkhTWFBqU19lSm5UMHBkbWtDeHFXQ2p1dzJDT1lHdEZnRXRhaE92dHNKRkJYYjg?oc=5" target="_blank"&gt;Brussels Airlines setzt Airbus A330 einmalig zwischen Frankfurt und Brüssel ein&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNR3ItU3ZVOUUxcDJJT0tkNlJrbTBGS3oyYm1iRjBsM1ZpOEUtSE1LaUpPMjFTd0dJcG9LRE1IYUNCbVZNNGp4S3BiZUdzMzZzUmM3a0wzTWx0d3JLc0xaQ1NBbEdTMDhkOXFlYzUxTVRqRHlWN2x2SDNuV1hxWkhTWFBqU19lSm5UMHBkbWtDeHFXQ2p1dzJDT1lHdEZnRXRhaE92dHNKRkJYYjg?oc=5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>auto-cf60daf2f792</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Thai Airways ersetzt A350 in Frankfurt mit 777 - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxOS3hFUFg1Mi15RUM3eENqei1tSFRra21MX1RFSVRCSkN4ZFhDdzFBR0RXOHVNMlZYQ1ZLYkJ0ODNlR2FKSk9qRjAxQ2UzakZFQXh5MkRZdHlzRXZSTkdsLVBKYjZlb3ducDBKLVRsYnBvYVJ0MnJHMXR4ZWJYQ2l3TDg0aW1jc2kzT3BILXJhMjNXZjZoX25aaQ?oc=5" target="_blank"&gt;Thai Airways ersetzt A350 in Frankfurt mit 777&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOS3hFUFg1Mi15RUM3eENqei1tSFRra21MX1RFSVRCSkN4ZFhDdzFBR0RXOHVNMlZYQ1ZLYkJ0ODNlR2FKSk9qRjAxQ2UzakZFQXh5MkRZdHlzRXZSTkdsLVBKYjZlb3ducDBKLVRsYnBvYVJ0MnJHMXR4ZWJYQ2l3TDg0aW1jc2kzT3BILXJhMjNXZjZoX25aaQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>auto-29481876de77</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Review: Turkish Airlines Business Lounge New Istanbul Airport - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikAFBVV95cUxOb1RtRXlWZUJOQkJlS1kwNWdfanFNaEtrbjlNMG1MNE5HQ05uQ3F6c2RBaVZWQS1pY001TDZTT3pHbHBjSnlvXzBEZlVOQXhoTnVmMXoxY0ZGU3JYR0VESHFMYU1QRGVTLVdHRXEzY1liY2NMWDhxRjZQSWRsOVlNYV9Ed2ZUdXFlaFkyR01jUTc?oc=5" target="_blank"&gt;Review: Turkish Airlines Business Lounge New Istanbul Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOb1RtRXlWZUJOQkJlS1kwNWdfanFNaEtrbjlNMG1MNE5HQ05uQ3F6c2RBaVZWQS1pY001TDZTT3pHbHBjSnlvXzBEZlVOQXhoTnVmMXoxY0ZGU3JYR0VESHFMYU1QRGVTLVdHRXEzY1liY2NMWDhxRjZQSWRsOVlNYV9Ed2ZUdXFlaFkyR01jUTc?oc=5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>auto-a84d81ba130f</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kuriose Flüge durch die Coronakrise: Honolulu - Frankfurt, Lufthansa in Neuseeeland &amp; weitere - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE1pQ0dVQnFZMFRjOHNtT0gtTVB4NG9FOHhjeGxKUXoyMkNhWjJsZFNCSUhuUmw0blpyMS05anE2ZWhOaXFaNkpHT3lYd2xmcHZ4UEhyRG8yWUo0SDItTG1aT3EyVndyZHZWN3hEWkVR?oc=5" target="_blank"&gt;Kuriose Flüge durch die Coronakrise: Honolulu - Frankfurt, Lufthansa in Neuseeeland &amp; weitere&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1pQ0dVQnFZMFRjOHNtT0gtTVB4NG9FOHhjeGxKUXoyMkNhWjJsZFNCSUhuUmw0blpyMS05anE2ZWhOaXFaNkpHT3lYd2xmcHZ4UEhyRG8yWUo0SDItTG1aT3EyVndyZHZWN3hEWkVR?oc=5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>auto-84fe73d83fa8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Review: China Airlines Premium Economy B777-300ER von Frankfurt nach Taipeh - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiowFBVV95cUxPOFdGZmxzM1RDV0ZTNFBRSjhfMHJzd3BFN1FLRnZvSGZDN3NHMjJKaGtkOTZoNXFLcE52VkVzTm1FSi1lU2tRWmcwd2x4YnZTaDQydDVUdUR1SWtIYjBLSW9TWjc3c3pvMXVWdWJMeV9sUDM2SnlUVGpTcHNvdkZNTDVYS0U0WjJSOXQ2VXo5Um5UdW4tbzNuemJiVXVFVkFCQk9J?oc=5" target="_blank"&gt;Review: China Airlines Premium Economy B777-300ER von Frankfurt nach Taipeh&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPOFdGZmxzM1RDV0ZTNFBRSjhfMHJzd3BFN1FLRnZvSGZDN3NHMjJKaGtkOTZoNXFLcE52VkVzTm1FSi1lU2tRWmcwd2x4YnZTaDQydDVUdUR1SWtIYjBLSW9TWjc3c3pvMXVWdWJMeV9sUDM2SnlUVGpTcHNvdkZNTDVYS0U0WjJSOXQ2VXo5Um5UdW4tbzNuemJiVXVFVkFCQk9J?oc=5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>auto-e0eb1f3104f0</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Review: Turkish Airlines Domestic Lounge Istanbul Airport - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiwFBVV95cUxORDRGVVF3NlJOTzE4MXQ3S3Z1c3k2QlNNbEhEcXh0VVVLWlRPZDk0STIwckp2bHdYQmdKb21oZHE3dkZ1WjRoeTlWY2xYUl9UcThLOW4yVURkcDBIcWtCcWkzUElfT3VpaWRkbWdSRksxaG9wR0haQjJkN0NDalp3djgzdU9RRjZteks0?oc=5" target="_blank"&gt;Review: Turkish Airlines Domestic Lounge Istanbul Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORDRGVVF3NlJOTzE4MXQ3S3Z1c3k2QlNNbEhEcXh0VVVLWlRPZDk0STIwckp2bHdYQmdKb21oZHE3dkZ1WjRoeTlWY2xYUl9UcThLOW4yVURkcDBIcWtCcWkzUElfT3VpaWRkbWdSRksxaG9wR0haQjJkN0NDalp3djgzdU9RRjZteks0?oc=5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>auto-8c1b230b2eba</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Air China startet Frankfurt-Chengdu - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMigAFBVV95cUxPTGtkbFdfeUV3VjlIRWxpcjBXRWgzS0NNTThRNXlpcEl5R2lYZDg1emlPa0l0NTBudHJCTGxvVGVsTWw3RmlWVUNJcDFwVDlaeVhjT3dFLTJEN1RVcTM1c2xiLVdjY2pQUlBjNmFJMzhYcFhJRWN3Q0J3XzFxUTNPXw?oc=5" target="_blank"&gt;Air China startet Frankfurt-Chengdu&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPTGtkbFdfeUV3VjlIRWxpcjBXRWgzS0NNTThRNXlpcEl5R2lYZDg1emlPa0l0NTBudHJCTGxvVGVsTWw3RmlWVUNJcDFwVDlaeVhjT3dFLTJEN1RVcTM1c2xiLVdjY2pQUlBjNmFJMzhYcFhJRWN3Q0J3XzFxUTNPXw?oc=5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>auto-13dbd031527f</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Man nearly sucked out of 'detached' window on Ryanair flight - France 24</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxPT3RISXdIRHdBblpXc0w1aHJHOTduWHhXWnhhVFVtcmJQQkVsckZaX21FMVdZTmUxYmEyVW1QZEdzTVFHWG1jZl9DWklNclBIT3NLMXVDNHBBanJUVXBLbUJwY0hhQ196XzZHWUtJQ1B5NGlNeG51ZGNWVzJiX1dvcXVMWnFGd2FObWdGRkVZWTZ2SGMyd0U1RGFHUmgzczlYMk5pSg?oc=5" target="_blank"&gt;Man nearly sucked out of 'detached' window on Ryanair flight&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;France 24&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPT3RISXdIRHdBblpXc0w1aHJHOTduWHhXWnhhVFVtcmJQQkVsckZaX21FMVdZTmUxYmEyVW1QZEdzTVFHWG1jZl9DWklNclBIT3NLMXVDNHBBanJUVXBLbUJwY0hhQ196XzZHWUtJQ1B5NGlNeG51ZGNWVzJiX1dvcXVMWnFGd2FObWdGRkVZWTZ2SGMyd0U1RGFHUmgzczlYMk5pSg?oc=5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>auto-0713e960088e</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>One of Delta’s oldest active passenger aircraft finally landed in Portugal after initial planned diversion to Iceland - airlive</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZGpVbGRxb2FOY25paFNJVzU5cF82N1FTUDBKeUFNVnJBZjg2YzN1eUVvN0I5a0I0aVpnYUp4cUJ4bzc2OFp6UVZWcnF0a0hNdEFFTWlxc25QdVZvME5xYWo4QWFpNU9RMFdoOHA3U2dvUl9XWHMza1I1ZUstS1ZyMTBBb1ZBSEFTcFV4QXNDbjFLOVJhYlJ2TXdRMGZER2JEN2owOVdGTUd3eXEzUUI2Ynk1X0VmdU0zN01GUHJnQ0liODJMWmt1Vy1fSHRrME03VWIyOWwyYkRxdDJncVg3VlNzajQ0SkljRjR3b3pn?oc=5" target="_blank"&gt;One of Delta’s oldest active passenger aircraft finally landed in Portugal after initial planned diversion to Iceland&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZGpVbGRxb2FOY25paFNJVzU5cF82N1FTUDBKeUFNVnJBZjg2YzN1eUVvN0I5a0I0aVpnYUp4cUJ4bzc2OFp6UVZWcnF0a0hNdEFFTWlxc25QdVZvME5xYWo4QWFpNU9RMFdoOHA3U2dvUl9XWHMza1I1ZUstS1ZyMTBBb1ZBSEFTcFV4QXNDbjFLOVJhYlJ2TXdRMGZER2JEN2owOVdGTUd3eXEzUUI2Ynk1X0VmdU0zN01GUHJnQ0liODJMWmt1Vy1fSHRrME03VWIyOWwyYkRxdDJncVg3VlNzajQ0SkljRjR3b3pn?oc=5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>auto-497803338520</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Delta flight from Copenhagen to JFK diverted to Paris and declared emergency for priority landing - airlive</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi3AFBVV95cUxOLU5pbkx3Qmx3QTBHSFZDaDVkU1daVG90VGdBMkRwdklKT2VxRFJnNUtYcDBIaF83Qk1Rbmt4MjU3Z0hlM2ZVdlNuRkJWeXhZZktSVGFJRmJobjE0WjZTSW5yeEFPWVo3anRjUlJBcG42Nlp2REJOVFZnS3JtdDliVWQzbWo1c3VLUWdzN2JDeUNlSzZkNzF2Sk16SkpuLTB4QWRFOHNGNW10WjcyeEFraUNPcTBLQTVhbDhFN0YyZzROM2JFeEdLTTFCTVExbnNUR1B0YlEwaDdHdHZD?oc=5" target="_blank"&gt;Delta flight from Copenhagen to JFK diverted to Paris and declared emergency for priority landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOLU5pbkx3Qmx3QTBHSFZDaDVkU1daVG90VGdBMkRwdklKT2VxRFJnNUtYcDBIaF83Qk1Rbmt4MjU3Z0hlM2ZVdlNuRkJWeXhZZktSVGFJRmJobjE0WjZTSW5yeEFPWVo3anRjUlJBcG42Nlp2REJOVFZnS3JtdDliVWQzbWo1c3VLUWdzN2JDeUNlSzZkNzF2Sk16SkpuLTB4QWRFOHNGNW10WjcyeEFraUNPcTBLQTVhbDhFN0YyZzROM2JFeEdLTTFCTVExbnNUR1B0YlEwaDdHdHZD?oc=5</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>auto-3e0351c67080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Air France flight AF158 to DFW turned around over Atlantic, crew declaring an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiywFBVV95cUxPM0Z5UTBBY0lZTnNoNWhnbjQ5ZVZpOXExeFNIQXVCUi1YNGNDakUzYzAySzR3NW91d0VDSjRQM2RBRGUyRGVWTWlTa0pucVg4d04zZmdzSkpUbjJ3QTRZOXUzOE5Tb0NuU3RrWHN4QUhyTnpjdHBidHoxNDJETkpZUVBEaDlvckh3SDZ5bF9SbVVLbW12T1JuUVBlY0g1VXAwUWxwRVp0SS1Tc0lnTlBZa0VfTVBnWU1uaWdsZElRaXhsck9raEhxV0dDSQ?oc=5" target="_blank"&gt;Air France flight AF158 to DFW turned around over Atlantic, crew declaring an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPM0Z5UTBBY0lZTnNoNWhnbjQ5ZVZpOXExeFNIQXVCUi1YNGNDakUzYzAySzR3NW91d0VDSjRQM2RBRGUyRGVWTWlTa0pucVg4d04zZmdzSkpUbjJ3QTRZOXUzOE5Tb0NuU3RrWHN4QUhyTnpjdHBidHoxNDJETkpZUVBEaDlvckh3SDZ5bF9SbVVLbW12T1JuUVBlY0g1VXAwUWxwRVp0SS1Tc0lnTlBZa0VfTVBnWU1uaWdsZElRaXhsck9raEhxV0dDSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>auto-09080464cb09</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Air France flight AF1750 to Copenhagen declared an emergency and just diverted to Amsterdam - airlive</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizgFBVV95cUxPeXN3RFJBMFJKQmxNMGptc1ZzT3VLOVF5SU1zb1RjVXExb203MTFldHN6RmhXdlhhd0pPb08tN3pFdkJiSnhtMG91TE1aR25sSGRzT0t6RU80LXZaTmNmdFZDMWVybE9hcjRQZnFsT3NLVExLZ0NYUEVuSENvSUZEckhjQ1VmajFuLWY2am8xVXYzSmJiNzFYVjVrNF9TZlkzRFNTSjZKMTRlR0pzZUtva2xPMUIxVDEyT3ZiTTJ4WkUyajNKalR4RDl6aVRMUQ?oc=5" target="_blank"&gt;Air France flight AF1750 to Copenhagen declared an emergency and just diverted to Amsterdam&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPeXN3RFJBMFJKQmxNMGptc1ZzT3VLOVF5SU1zb1RjVXExb203MTFldHN6RmhXdlhhd0pPb08tN3pFdkJiSnhtMG91TE1aR25sSGRzT0t6RU80LXZaTmNmdFZDMWVybE9hcjRQZnFsT3NLVExLZ0NYUEVuSENvSUZEckhjQ1VmajFuLWY2am8xVXYzSmJiNzFYVjVrNF9TZlkzRFNTSjZKMTRlR0pzZUtva2xPMUIxVDEyT3ZiTTJ4WkUyajNKalR4RDl6aVRMUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>auto-8d0af21399a3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Delta A330 Makes Emergency Landing After Mid-Air Engine Fire Triggers Cabin “Blackout” - Simple Flying</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiAFBVV95cUxObnVxZmRoaGNyMGUyckE0bjF3NV83ZnlKQ0FGYjhSaTRJb1ZFcV84a0ZwMmNPa3N1X2hMc3VpOGFrZjBEcWphMVA5d2ItT3F3NDJ3OXNjdWpkeG1pNndnODYyM2cxbDlYcWdyMURodE84SS03UkNNQmhrN3ptRmFicGtaQnFiRlVS?oc=5" target="_blank"&gt;Delta A330 Makes Emergency Landing After Mid-Air Engine Fire Triggers Cabin “Blackout”&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Simple Flying&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObnVxZmRoaGNyMGUyckE0bjF3NV83ZnlKQ0FGYjhSaTRJb1ZFcV84a0ZwMmNPa3N1X2hMc3VpOGFrZjBEcWphMVA5d2ItT3F3NDJ3OXNjdWpkeG1pNndnODYyM2cxbDlYcWdyMURodE84SS03UkNNQmhrN3ptRmFicGtaQnFiRlVS?oc=5</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>auto-ab536bc1f514</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Turkish Airlines plane makes emergency landing in Spain after threat - Euronews.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiugFBVV95cUxNeXI3YlUtQzdZc1lPS0IzTkx5UnV5YjVjV19WSXRvX3VEbGMwRWtGcDNzcTA4OFpzWExnNHlINmNRV3NUZzYySFB6MFBVblRwRk8xaUNIcEZfS0I2MGJfVV9BOHBxT0tldDh6THZua3JMVEpZNkVDeVlNenk5ZHJCaTRGNjdoTE91ekhrNzc2THdpQkpnZEVadXpySmlLM2tZLVZzekNyemVmVkstSnJzcDBLMzdoSEQweXc?oc=5" target="_blank"&gt;Turkish Airlines plane makes emergency landing in Spain after threat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Euronews.com&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNeXI3YlUtQzdZc1lPS0IzTkx5UnV5YjVjV19WSXRvX3VEbGMwRWtGcDNzcTA4OFpzWExnNHlINmNRV3NUZzYySFB6MFBVblRwRk8xaUNIcEZfS0I2MGJfVV9BOHBxT0tldDh6THZua3JMVEpZNkVDeVlNenk5ZHJCaTRGNjdoTE91ekhrNzc2THdpQkpnZEVadXpySmlLM2tZLVZzekNyemVmVkstSnJzcDBLMzdoSEQweXc?oc=5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>auto-6838fb0f1b1d</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Air France flight makes emergency landing in Germany after technical issue - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxPVDVDdGNyZDRnTXBfYUVSNmRCekZTVU1Fd3dDYVAwaWxkTXpzalRKQkhzQmdLNmRBU01HNjdpQmp1VTVSajlmcDJRb1NFTUhzUXBIdVh1WGVFamxVdUdWc2ZqVzgwb2xmaWoyeXRsMUFleWdxYm1LSmN0V0pOazhwYmxCa0pDdm9DbUR4TGk1N3A5TGVSVVhLUzdqX0h1ZWVEVVhPQ0Zhcy1vSkkwQTlGLVdWSW4?oc=5" target="_blank"&gt;Air France flight makes emergency landing in Germany after technical issue&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Anadolu Ajansı&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPVDVDdGNyZDRnTXBfYUVSNmRCekZTVU1Fd3dDYVAwaWxkTXpzalRKQkhzQmdLNmRBU01HNjdpQmp1VTVSajlmcDJRb1NFTUhzUXBIdVh1WGVFamxVdUdWc2ZqVzgwb2xmaWoyeXRsMUFleWdxYm1LSmN0V0pOazhwYmxCa0pDdm9DbUR4TGk1N3A5TGVSVVhLUzdqX0h1ZWVEVVhPQ0Zhcy1vSkkwQTlGLVdWSW4?oc=5</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>auto-b5614127e249</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Turkish Airlines TK6 declared an emergency over The Netherlands and just diverted to Amsterdam - airlive</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZlNDWjdoZjNOSVNLdGhRRGZydnNxaWw5NEJPLUl4eEU1VHRzR1hjb1l2OW1LbGZ3QmwxODY3ZTBHdnJaMmE5c3JGWEgzWjUzcmZQcVY1Z0RuM1RoNUtLXy1oR19mWjJKX1pWcS14TkpyU1J6dnFBc3UwZTkwc0g5VXZodVp4Zk5kcjJIRFdwNzZtVHV5UlhrR0VtR3p5a3VBRE9aZl8tZ3FvR1RGamJkZGZFRlR4T21EVTFwV0pPQkZLenMtRkY2em5xTmtwWFZKT1E?oc=5" target="_blank"&gt;Turkish Airlines TK6 declared an emergency over The Netherlands and just diverted to Amsterdam&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZlNDWjdoZjNOSVNLdGhRRGZydnNxaWw5NEJPLUl4eEU1VHRzR1hjb1l2OW1LbGZ3QmwxODY3ZTBHdnJaMmE5c3JGWEgzWjUzcmZQcVY1Z0RuM1RoNUtLXy1oR19mWjJKX1pWcS14TkpyU1J6dnFBc3UwZTkwc0g5VXZodVp4Zk5kcjJIRFdwNzZtVHV5UlhrR0VtR3p5a3VBRE9aZl8tZ3FvR1RGamJkZGZFRlR4T21EVTFwV0pPQkZLenMtRkY2em5xTmtwWFZKT1E?oc=5</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4549,7 +4549,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4580,8 +4579,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>review</t>
@@ -4614,7 +4611,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4645,8 +4641,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>review</t>
@@ -4679,7 +4673,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4710,8 +4703,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>review</t>
@@ -4744,7 +4735,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4775,8 +4765,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>review</t>
@@ -4809,7 +4797,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4840,8 +4827,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>review</t>
@@ -4874,7 +4859,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4905,8 +4889,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>review</t>
@@ -4939,7 +4921,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -4970,8 +4951,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>review</t>
@@ -5004,7 +4983,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5035,8 +5013,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>review</t>
@@ -5069,7 +5045,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5100,8 +5075,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>review</t>
@@ -5134,7 +5107,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5165,8 +5137,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>review</t>
@@ -5199,7 +5169,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5230,8 +5199,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>review</t>
@@ -5264,7 +5231,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5295,8 +5261,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>review</t>
@@ -5329,7 +5293,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -5360,8 +5323,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>review</t>
@@ -5394,7 +5355,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -5425,8 +5385,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>review</t>
@@ -5459,7 +5417,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5490,8 +5447,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>review</t>
@@ -5524,7 +5479,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -5555,8 +5509,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>review</t>
@@ -5589,7 +5541,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -5620,8 +5571,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>review</t>
@@ -5654,7 +5603,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -5685,8 +5633,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>review</t>
@@ -5719,7 +5665,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -5750,8 +5695,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>review</t>
@@ -5784,7 +5727,6 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -5815,8 +5757,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>review</t>
@@ -5828,6 +5768,1306 @@
         </is>
       </c>
       <c r="O86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>auto-9b5fca87c98e</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Bolivien will mindestens zehn Embraer-Jets für Boliviana de Aviación leasen</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Die bolivianische Regierung plant eine Erneuerung der Flotte der staatlichen Fluggesellschaft. Vorgesehen ist das Leasing von mindestens zehn Exemplaren des brasilianischen Herstellers Embraer. Welches Modell für Boliviana de Aviación infrage kommt, wurde noch nicht bekannt gegeben.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/bolivien-will-mindestens-zehn-embraer-jets-fuer-boliviana-de-aviacion-leasen/9f2e1zb</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>auto-bee907c8a253</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Vier Mitarbeiter am Flughafen Amsterdam festgenommen</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Im Zuge von Ermittlungen wegen Drogenschmuggels über den Flughafen Amsterdam-Schiphol sind vier Mitarbeiter eines Frachtabfertigungsunternehmens festgenommen worden. Die Männer im Alter von 34, 38, 46 und 48 Jahren wurden am 11. August verhaftet. Die Ermittler prüfen, ob logistische Abläufe am Flughafen für die Einfuhr von Drogen missbraucht wurden, so das Portal &lt;a href="https://nos.nl/artikel/2626712-vier-medewerkers-luchtvracht-schiphol-aangehouden-voor-drugssmokkel" id="60a4c2d5-2efe-4a3f-9770-01a142862cbe" data-link-role-code="target_blank"&gt;NOS&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/vier-mitarbeiter-am-flughafen-amsterdam-festgenommen/kbhrnm4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>auto-a6c9f6fc3321</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Living Legends of Aviation Europe zeichnet neue Mitglieder aus</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Die Living Legends of Aviation Europe nehmen bei ihrer diesjährigen Veranstaltung am 5. September am Wolfgangsee fünf neue Mitglieder auf. Ausgezeichnet werden die Piloten Siegfried Blacky Schwarz und Raimund Riedmann, der französische Astronaut und Pilot Thomas Pesquet, Air-Car-Entwickler Stefan Klein sowie Hubschrauberunternehmer Hans J. Ostler. Weitere Preise gehen unter anderem an Jet-Aviation-Chef Jeremie Caillet, Dassault-Aviation-Chef Éric Trappier und Isar-Aerospace-Mitgründer Daniel Metzler. Der französische Testpilot Didier Delsalle wird für seine Hubschrauberlandung auf dem Gipfel des Mount Everest im Jahr 2005 geehrt. Auch die Wingsuit-Piloten Marco Fürst und Marco Waltenspiel erhalten eine Auszeichnung.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/living-legends-of-aviation-europe-zeichnet-neue-mitglieder-aus/nhmt6hl</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>auto-92062f1cee7e</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Allegiant kündigt neun neue Strecken an</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Allegiant baut ihr US-Streckennetz im Frühjahr 2027 um neun Nonstopverbindungen aus. Sieben davon werden nur während der besonders nachfragestarken Frühlingsmonate angeboten. Ab Boston fliegt die Airline nach Orlando-Sanford, Punta Gorda und St. Pete-Clearwater, ab Providence nach Fort Lauderdale, Orlando-Sanford und Sarasota. Hinzu kommt eine Verbindung zwischen Portsmouth und Fort Lauderdale. Außerdem startet Allegiant eine saisonale Strecke von Grand Forks nach Orlando-Sanford. Ganzjährig wird ab dem 12. Februar 2027 zwischen Cincinnati und Orlando geflogen. Die neuen Verbindungen starten überwiegend im Februar 2027.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/allegiant-kuendigt-neun-neue-strecken-an/vfzg4ww</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>auto-70f166158591</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Eve Air Mobility will Evtol-Infrastruktur in Thailand mit lokalem Partner entwickeln</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Eve Air Mobility und das thailändische Luftfahrt- und Ingenieurunternehmen RV Connex haben eine Absichtserklärung zur Entwicklung von Advanced Air Mobility in Thailand unterzeichnet. Im Mittelpunkt steht die Ausarbeitung regulatorischer und betrieblicher Grundlagen für den künftigen Einsatz neuer Luftverkehrskonzepte. Gemeinsam wollen die Unternehmen unter anderem mögliche Betriebsszenarien, Sicherheitsanforderungen, Luftraumregeln und den Infrastrukturbedarf untersuchen. Dabei sollen internationale Standards mit den Anforderungen des thailändischen Marktes verbunden werden. RV Connex will dazu auch mit Behörden, Hochschulen und weiteren Unternehmen zusammenarbeiten.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/eve-air-mobility-will-evtol-infrastruktur-in-thailand-mit-lokalem-partner-entwickeln/zfl1v96</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>auto-6ec8f23d9d33</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Neues Zentrum soll Drohnenabwehr voranbringen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>COCHSTEDT - Drohnen können Flughäfen und andere wichtige Infrastruktur gefährden - oder sogar für Angriffe eingesetzt werden. Wie sich solche Fluggeräte besser erkennen und abwehren lassen, soll künftig in Sachsen-Anhalt erforscht werden.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53398/Neues-Zentrum-soll-Drohnenabwehr-voranbringen.html</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>auto-d7e2d632ef62</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Das umfasst die temporäre Flottenzusage von Lufthansa</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schlichter und Mediatoren vermitteln zwischen Lufthansa und Piloten - Konzern und Vereinigung Cockpit (VC) suchen einen Neustart. Lufthansa stoppt für den Zeitraum der Verhandlungen die schleichende Erosion der Mainline - Lufthansa und Lufthansa Cargo sollen nicht unter 285 Flugzeuge fallen.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53395/Das-umfasst-die-temporaere-Flottenzusage-von-Lufthansa.html</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>auto-5167fe3b32cd</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Manchester-bound flight carrying 230 people makes emergency landing in Russia - Metro.co.uk</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxQVDFrVG1EcHJfSVNmdjdaa2N3dmxFYm90cmFIR09OWncwQTFTY1p1bFFPSGlXS3RWUl9JZ0taOGNKZWV5NmpkRmFoZW5Pd09pc1RuZEJ6blhhZ29uQU5zeUgxRHg1QVRBaVRjNWZaR0h2bEpnZ2RtMnlwcGQ0cnpsMktYZXZuQTR2emxVQUpXN2xFMmM1NWRPYlNhdkxwQ0NUWk9SaU10R0RpMEp2aHI2blJjY1V3d9IBuwFBVV95cUxOSk0xRXlwLXZZVFRYUlo1RjNNX2x5aDBsQWlwOFBqVzV2RVkxOWJPT1J3anRFbGk5T21xOTZwcXpmRENhQ3dmNURGc2NwRm5PM21ycDhuSVRHSmlqdnlQb0JKclhrSTU2TW9XN211VVB6V2gwdEZRZGh5dVdzMUM1VlFwNVJmelRyNFpOV2VmcjJwOS1MQ0dRWTZOOHhycXhmTk43WkZxLUJCSmVDRWxha01KZTI4ZW9QY0k4?oc=5" target="_blank"&gt;Manchester-bound flight carrying 230 people makes emergency landing in Russia&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Metro.co.uk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVDFrVG1EcHJfSVNmdjdaa2N3dmxFYm90cmFIR09OWncwQTFTY1p1bFFPSGlXS3RWUl9JZ0taOGNKZWV5NmpkRmFoZW5Pd09pc1RuZEJ6blhhZ29uQU5zeUgxRHg1QVRBaVRjNWZaR0h2bEpnZ2RtMnlwcGQ0cnpsMktYZXZuQTR2emxVQUpXN2xFMmM1NWRPYlNhdkxwQ0NUWk9SaU10R0RpMEp2aHI2blJjY1V3d9IBuwFBVV95cUxOSk0xRXlwLXZZVFRYUlo1RjNNX2x5aDBsQWlwOFBqVzV2RVkxOWJPT1J3anRFbGk5T21xOTZwcXpmRENhQ3dmNURGc2NwRm5PM21ycDhuSVRHSmlqdnlQb0JKclhrSTU2TW9XN211VVB6V2gwdEZRZGh5dVdzMUM1VlFwNVJmelRyNFpOV2VmcjJwOS1MQ0dRWTZOOHhycXhmTk43WkZxLUJCSmVDRWxha01KZTI4ZW9QY0k4?oc=5</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>auto-0390db6fc012</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alaska Airlines Boeing 787-9 is declaring an emergency off France coast, after U-turn over UK - airlive.net</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizwFBVV95cUxPaTY1ZTFSYXZOWmVQajY0OHJtaDJpNUpxWm50V1hRaEJKZ2gtMFZySG4tT0ZxNUlrTTN3YjMyWExVOVVybFBudmhXMjRqSlRwN3NGVW5KbDFReDVwbVBlZFUyQlRTTm15c1FRRnN1Qmtxam5fS3ExSm9OUEJ0ZVNvMDBmajhLYjNwUFV6bUI0cnZlMkxxX1lINkdBYlU2SEVkLU9HQ3VEUDNrWWRraHhudFFmS0JsNXhLLVhiUG1tTU9LWllUX01ubXZJeGpMMjg?oc=5" target="_blank"&gt;Alaska Airlines Boeing 787-9 is declaring an emergency off France coast, after U-turn over UK&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaTY1ZTFSYXZOWmVQajY0OHJtaDJpNUpxWm50V1hRaEJKZ2gtMFZySG4tT0ZxNUlrTTN3YjMyWExVOVVybFBudmhXMjRqSlRwN3NGVW5KbDFReDVwbVBlZFUyQlRTTm15c1FRRnN1Qmtxam5fS3ExSm9OUEJ0ZVNvMDBmajhLYjNwUFV6bUI0cnZlMkxxX1lINkdBYlU2SEVkLU9HQ3VEUDNrWWRraHhudFFmS0JsNXhLLVhiUG1tTU9LWllUX01ubXZJeGpMMjg?oc=5</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>auto-07287b8e327f</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Airbus issues major A320 recall after flight control incident - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxOLVBoWnBUeThKd3dGczBKdUdyck9uTjJodXlESXB3dVlOaHhjalA4dDF1UDJCb0t0OVQzamhpQ05UWDdKWWFON3NBVnpiek5SbFpucl9XMGNYNVpLc3BtZGNCU284YmFJTjlWWmRxNS1TcFAtZHJ5T3VEcVlOT3ZnRDdsVlR6WkxyUldSQU9vRGJ5YWZCb0hxWXhsQ1Qtd2ZJQU5pTVVlWDM0Z9IBrwFBVV95cUxPa2NNa2pRZUNNSk4yd3AzM0czVUk5X0gtWUNiaGNaWDVWeFJvcGMtaHJGV1Itcko5cjRkMFRrbmVsRm9QQ1lnRi1zWENrU25lOHpqSDlOTHFlNmVzOERBeEpuS090TTdXWmgxWTAxNnphV1pVYWlnc01ZempPQjRCeGZacUt2MWo5MXE0RERpZHBIYm5vT0x6UkRVdUlDVjQxRUUwb0E4RTN6QmtQOFZZ?oc=5" target="_blank"&gt;Airbus issues major A320 recall after flight control incident&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Al Jazeera&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOLVBoWnBUeThKd3dGczBKdUdyck9uTjJodXlESXB3dVlOaHhjalA4dDF1UDJCb0t0OVQzamhpQ05UWDdKWWFON3NBVnpiek5SbFpucl9XMGNYNVpLc3BtZGNCU284YmFJTjlWWmRxNS1TcFAtZHJ5T3VEcVlOT3ZnRDdsVlR6WkxyUldSQU9vRGJ5YWZCb0hxWXhsQ1Qtd2ZJQU5pTVVlWDM0Z9IBrwFBVV95cUxPa2NNa2pRZUNNSk4yd3AzM0czVUk5X0gtWUNiaGNaWDVWeFJvcGMtaHJGV1Itcko5cjRkMFRrbmVsRm9QQ1lnRi1zWENrU25lOHpqSDlOTHFlNmVzOERBeEpuS090TTdXWmgxWTAxNnphV1pVYWlnc01ZempPQjRCeGZacUt2MWo5MXE0RERpZHBIYm5vT0x6UkRVdUlDVjQxRUUwb0E4RTN6QmtQOFZZ?oc=5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>auto-b50e490d0c83</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>A Gulfstream G200 has crashed during emergency landing in Dominican Republic, killing two crew members - airlive.net</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWWE4OXdaT1lsUGRWZ3RWbkVfV0pjdmR4a0YybkZnYkFxd2M1bGN1UkM4ZTczN3c0bF9UeUpieENDRW9IRkZJRklTRy1nM1o1TWlKNzZEaC16LTctMG9BcGZLeXdxZTM1endqM2kyTG1Ia1RVajZOamQyLWRsVjBYd201dVowamUwRURreENMUjdyaEhsZVZUUjZMLWlfZzJzcFNxNkZJdFNUb25nbm9TeURlSDhjNjVHbVlHRG1NcldlcjdlQXJmYU00dmloU0NFRlktbjlJbHNxdw?oc=5" target="_blank"&gt;A Gulfstream G200 has crashed during emergency landing in Dominican Republic, killing two crew members&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWWE4OXdaT1lsUGRWZ3RWbkVfV0pjdmR4a0YybkZnYkFxd2M1bGN1UkM4ZTczN3c0bF9UeUpieENDRW9IRkZJRklTRy1nM1o1TWlKNzZEaC16LTctMG9BcGZLeXdxZTM1endqM2kyTG1Ia1RVajZOamQyLWRsVjBYd201dVowamUwRURreENMUjdyaEhsZVZUUjZMLWlfZzJzcFNxNkZJdFNUb25nbm9TeURlSDhjNjVHbVlHRG1NcldlcjdlQXJmYU00dmloU0NFRlktbjlJbHNxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>auto-a0a10730c855</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Air France A350 was stuck on runway for 25 minutes after emergency landing in Munich - airlive.net</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixAFBVV95cUxOczJwOThORlVBOUhjSXM3R3d0TWtKbGJiZW16VVNpNmRHUjZSVFhuQjUxcFpCZHJYTl9KU1FXS3Joa3pDZ1hLR2hNakdhd0ppVHpldUhaaV9XUUJlaVlGd05XQy16WGhpM1gxN0xkZlE1eU1TbkhWQ0h1WFNMeUNRWU9oS0s0SXRiYU5DQnZNVFRSQURBRHY5OEF1c3EzTkZ4RFVxNWwzbFdWRk9RVTZOZGtUem4yTlczZW10MlMxTDdRV1Vj?oc=5" target="_blank"&gt;Air France A350 was stuck on runway for 25 minutes after emergency landing in Munich&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOczJwOThORlVBOUhjSXM3R3d0TWtKbGJiZW16VVNpNmRHUjZSVFhuQjUxcFpCZHJYTl9KU1FXS3Joa3pDZ1hLR2hNakdhd0ppVHpldUhaaV9XUUJlaVlGd05XQy16WGhpM1gxN0xkZlE1eU1TbkhWQ0h1WFNMeUNRWU9oS0s0SXRiYU5DQnZNVFRSQURBRHY5OEF1c3EzTkZ4RFVxNWwzbFdWRk9RVTZOZGtUem4yTlczZW10MlMxTDdRV1Vj?oc=5</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>auto-985e03462e60</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>United Airlines Flight UA969 Emergency Landing Triggers Massive Transatlantic Travel Chaos From Amsterdam to San Francisco: Latest Airline News and Aviation Updates - Nomad Lawyer</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilwFBVV95cUxQRC1ZaWNtVDFWRUU0dWxxT2pkUFZmcUs5ZDBkbkVWQ3B5UWR0T000WWNQOUNMcHFxbnVKdWhwZGgtZm9xTHFGc0sxYUoteWFHRjRSQVduRWlBc2Nta2tsTVNIYzRLX3BKc2h6M3dFSTI5UkVEaHlXVUJBNS1Ua0Z2ZVdrdUlwalR1TWl3V0haUlpjVHFseHlj?oc=5" target="_blank"&gt;United Airlines Flight UA969 Emergency Landing Triggers Massive Transatlantic Travel Chaos From Amsterdam to San Francisco: Latest Airline News and Aviation Updates&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Nomad Lawyer&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQRC1ZaWNtVDFWRUU0dWxxT2pkUFZmcUs5ZDBkbkVWQ3B5UWR0T000WWNQOUNMcHFxbnVKdWhwZGgtZm9xTHFGc0sxYUoteWFHRjRSQVduRWlBc2Nta2tsTVNIYzRLX3BKc2h6M3dFSTI5UkVEaHlXVUJBNS1Ua0Z2ZVdrdUlwalR1TWl3V0haUlpjVHFseHlj?oc=5</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>auto-9c06fe978a8a</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TUI flight BY7614 just declared an emergency over France, now diverting to Gatwick - airlive.net</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirwFBVV95cUxQUHFQZWVnQUxzaGM5elBRbVFXMm1Vb093UXkwaERMTlZHcEpJN2RPQXU5NVdSUkE4NkF4Y18yaTVkM3dlTk5ZQ2MyOTZoaUlTelI5U0lKWFZVa254RlRWbGN3UVlFaFp2bUp6YVNXdHN5bklDcFlFLXYyUGdVVU1seGltN2RRYjM2bVVFVV9hcHplcHlINVpvbW9TUFM2QzhmbW1wYjVlbHZLR1pBdW4w?oc=5" target="_blank"&gt;TUI flight BY7614 just declared an emergency over France, now diverting to Gatwick&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUHFQZWVnQUxzaGM5elBRbVFXMm1Vb093UXkwaERMTlZHcEpJN2RPQXU5NVdSUkE4NkF4Y18yaTVkM3dlTk5ZQ2MyOTZoaUlTelI5U0lKWFZVa254RlRWbGN3UVlFaFp2bUp6YVNXdHN5bklDcFlFLXYyUGdVVU1seGltN2RRYjM2bVVFVV9hcHplcHlINVpvbW9TUFM2QzhmbW1wYjVlbHZLR1pBdW4w?oc=5</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>auto-a669404324a6</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Chaos in Palma de Mallorca: Air Europa Flight Suffers Incident - The Aviation Hub</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilgFBVV95cUxQSlZEVFFBRmdEdjBsaDUwM0JaYWJxZlNseHRvUUlEaFNjMnpBT0pNcTRiYUJfWGp1M25DWkVWZGswLW5Wc29TaFQ1YlVEX05fZUZSd2x0a2JLNklrUkpudjdJNzFneDZFalJXQk1Waks0Y1doQVJiRDdrWVhJUXQwd0tsUEcwRndNamxZMExpcVNJZ1Z3VFE?oc=5" target="_blank"&gt;Chaos in Palma de Mallorca: Air Europa Flight Suffers Incident&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Aviation Hub&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQSlZEVFFBRmdEdjBsaDUwM0JaYWJxZlNseHRvUUlEaFNjMnpBT0pNcTRiYUJfWGp1M25DWkVWZGswLW5Wc29TaFQ1YlVEX05fZUZSd2x0a2JLNklrUkpudjdJNzFneDZFalJXQk1Waks0Y1doQVJiRDdrWVhJUXQwd0tsUEcwRndNamxZMExpcVNJZ1Z3VFE?oc=5</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>auto-d72a6a33c27e</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Double Trouble: Air France and Iberia Battle Smoke And Fumes in Separate European Incidents - Simple Flying</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMihwFBVV95cUxQU0tuc0ZucGZoQjNKMWE0TzZUTF9WLXFqREJuaV8waHh3NHpQYVZud2lpVnpBQWxjdE1UdVFMcnpTNTVLaFZDQkEzZGFYZXZrUm1XaUFyYWp6aEMtdkUwa1h2NmxVMldRbVlsaWViUHJobUZSSmxjNFdERnlpU2o0NWF3bFIzSk0?oc=5" target="_blank"&gt;Double Trouble: Air France and Iberia Battle Smoke And Fumes in Separate European Incidents&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Simple Flying&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQU0tuc0ZucGZoQjNKMWE0TzZUTF9WLXFqREJuaV8waHh3NHpQYVZud2lpVnpBQWxjdE1UdVFMcnpTNTVLaFZDQkEzZGFYZXZrUm1XaUFyYWp6aEMtdkUwa1h2NmxVMldRbVlsaWViUHJobUZSSmxjNFdERnlpU2o0NWF3bFIzSk0?oc=5</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>auto-bdf5e30004e1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pedro Sánchez's plane makes an emergency landing in Ankara (Turkey) due to a technical problem - Demócrata</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixAFBVV95cUxNNjllT013cElZRHV4dWQ2aUVtOV9BcE9lc1ZsSG9fTE9hUlZYOUJQYWFTQUlZSHNYWk5xZFJKOTdKZjdhbEt5R3RQWXQ4RXdLNHNnN3llVlNEUFM1SmFKeDZDV2JuQndldUNNWkRoaGxRVU9OT1M2VUtPX2QzbmJ4WXpoWjl6ZFBPM3kwdUN1VU1DWEhyXzgwYUlsZHFheF9BdDZaSnBHbm4wNVF1OUs4NG9PaGhDdUw2WmxQUGZ2dUx6Y21l0gHKAUFVX3lxTE8zQ1RsVDVNQm8xeWlqU0ZBUzdtZngyU0RqaTA0ai1tOUl5d2h2N2RHUHZFcXE2M1N1WXlGOTZZMWNwWWYtenpkb0k0N3pkMzM3bk1fUk9vVEdZVi0zN2hwU3I3TkJJeGJGckNOMUlTVXdrcE9WVzNtRXhvZWk3UHgyYmtwblZWRzVPSXdJNTAySk5pS1ZMT3NGVzIyOE5HRXV5OTZKZ1F5MGxjY2VFSXQwYWpGOHFpakY0VElrcUVvWHd5UmJSVWlmVHc?oc=5" target="_blank"&gt;Pedro Sánchez's plane makes an emergency landing in Ankara (Turkey) due to a technical problem&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Demócrata&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNjllT013cElZRHV4dWQ2aUVtOV9BcE9lc1ZsSG9fTE9hUlZYOUJQYWFTQUlZSHNYWk5xZFJKOTdKZjdhbEt5R3RQWXQ4RXdLNHNnN3llVlNEUFM1SmFKeDZDV2JuQndldUNNWkRoaGxRVU9OT1M2VUtPX2QzbmJ4WXpoWjl6ZFBPM3kwdUN1VU1DWEhyXzgwYUlsZHFheF9BdDZaSnBHbm4wNVF1OUs4NG9PaGhDdUw2WmxQUGZ2dUx6Y21l0gHKAUFVX3lxTE8zQ1RsVDVNQm8xeWlqU0ZBUzdtZngyU0RqaTA0ai1tOUl5d2h2N2RHUHZFcXE2M1N1WXlGOTZZMWNwWWYtenpkb0k0N3pkMzM3bk1fUk9vVEdZVi0zN2hwU3I3TkJJeGJGckNOMUlTVXdrcE9WVzNtRXhvZWk3UHgyYmtwblZWRzVPSXdJNTAySk5pS1ZMT3NGVzIyOE5HRXV5OTZKZ1F5MGxjY2VFSXQwYWpGOHFpakY0VElrcUVvWHd5UmJSVWlmVHc?oc=5</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>auto-67af3de44657</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>A passenger died on board Brussels Airlines flight to Spain, prompting emergency landing in Toulouse - airlive.net</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1wFBVV95cUxPd3RfNWhBT29qWHdNV1AxOXE3R1JjM3NlcGowX1hmeWF4TzlJRUJkaElncklqR01VQzBvVWFaeHM3MFBGV3ZCTUxkRC15Z3VzVlliVEw0bEJ4NHVBOVlUWko0TFJYU0dVYUgzQm5sT3JINUtXNjRCYXc0b1NycGlBakZEVW9nMjlJczVpdTNvejktVVIxNjhFd1IzaDdxMnRrcmU1dVVRcWV3YnNFTGRXc0hHU3lLZ3pZNmNjQU5fT01HYWdkenlnMWZzUXM5akZLS21vbjVaWQ?oc=5" target="_blank"&gt;A passenger died on board Brussels Airlines flight to Spain, prompting emergency landing in Toulouse&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPd3RfNWhBT29qWHdNV1AxOXE3R1JjM3NlcGowX1hmeWF4TzlJRUJkaElncklqR01VQzBvVWFaeHM3MFBGV3ZCTUxkRC15Z3VzVlliVEw0bEJ4NHVBOVlUWko0TFJYU0dVYUgzQm5sT3JINUtXNjRCYXc0b1NycGlBakZEVW9nMjlJczVpdTNvejktVVIxNjhFd1IzaDdxMnRrcmU1dVVRcWV3YnNFTGRXc0hHU3lLZ3pZNmNjQU5fT01HYWdkenlnMWZzUXM5akZLS21vbjVaWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>auto-b116553d8806</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>'Flight from hell': Six fall ill on British Airways flight from London to Egypt; forces emergency landing - The Times of India</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikwJBVV95cUxNMWxWdlVFd2pFU3Z0WDNCN0tDb3U3QjJRTHBiV1RyN1p5TmVlSDdjY1F0N3d2OGdwZHJETzBidVJlR0c5ME1xN3dXT2wtRElGbzU1LVdpOHhiM2ZXcF9HMHpJV0lNeUFidXpxVHBDcG5ZNFFQRGpHQ1dsTmV5ZkxRWXdfMGFPMzU0OTBTcW4xb2JValpWTGVvWGU2NVF2ZnBEbWFZOF93TUQ4ZUlzQUtMU3Jpal96SGRvTTAwQ05xMzdGQ2FuSng2S3drSW1KYlY4Y1RMWGZzU0s1S3FQMVVaVmEzRUZFRFl6S2tJQTdXSVdDd3k5MlRKNmpvc2VOenktV29KZ0tmZG12MVdJUEFhWmVPSdIBmAJBVV95cUxNMDAyOTloN3V3YXYyclp6WXhQMlJ0LWM5cFF6aHFsVE9lc3RZQldZbG1sNzc0aWJOSm0xQldWNFlXS2l4UlAzbUVaV2k1Tl9fVi02MUMyRzFBT25fNHZucTZBcnNxZFZNSllVeXZCUkd0MFBSVlZ3YVZzVklrcEtqcklfbXBfMnBMS01oQXFqUEFpSHBLbmlPU2dVSlhTUEtia2tManIyZW9oc3ZINEdyMXRjTDhHRUF2Uks3VV9oQkJfOHNadjJTcUlhZmVJazBfRjZjbV95aklmbGF2UmxOVzJ1a0tKZHdmS0JRN2JhTDRnS01WRldIQnZaVV9TSDBnampUeG8yU2hVLWNZUG1WdXYwNjlBZ05S?oc=5" target="_blank"&gt;'Flight from hell': Six fall ill on British Airways flight from London to Egypt; forces emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Times of India&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNMWxWdlVFd2pFU3Z0WDNCN0tDb3U3QjJRTHBiV1RyN1p5TmVlSDdjY1F0N3d2OGdwZHJETzBidVJlR0c5ME1xN3dXT2wtRElGbzU1LVdpOHhiM2ZXcF9HMHpJV0lNeUFidXpxVHBDcG5ZNFFQRGpHQ1dsTmV5ZkxRWXdfMGFPMzU0OTBTcW4xb2JValpWTGVvWGU2NVF2ZnBEbWFZOF93TUQ4ZUlzQUtMU3Jpal96SGRvTTAwQ05xMzdGQ2FuSng2S3drSW1KYlY4Y1RMWGZzU0s1S3FQMVVaVmEzRUZFRFl6S2tJQTdXSVdDd3k5MlRKNmpvc2VOenktV29KZ0tmZG12MVdJUEFhWmVPSdIBmAJBVV95cUxNMDAyOTloN3V3YXYyclp6WXhQMlJ0LWM5cFF6aHFsVE9lc3RZQldZbG1sNzc0aWJOSm0xQldWNFlXS2l4UlAzbUVaV2k1Tl9fVi02MUMyRzFBT25fNHZucTZBcnNxZFZNSllVeXZCUkd0MFBSVlZ3YVZzVklrcEtqcklfbXBfMnBMS01oQXFqUEFpSHBLbmlPU2dVSlhTUEtia2tManIyZW9oc3ZINEdyMXRjTDhHRUF2Uks3VV9oQkJfOHNadjJTcUlhZmVJazBfRjZjbV95aklmbGF2UmxOVzJ1a0tKZHdmS0JRN2JhTDRnS01WRldIQnZaVV9TSDBnampUeG8yU2hVLWNZUG1WdXYwNjlBZ05S?oc=5</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>auto-dc808273bab5</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Milan-London flight diverted to Paris as passenger starts 'eating' passport, another tries to flush it do - The Times of India</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiwJBVV95cUxQdWVXYjF2VVhmNF9jRUhOM0tocjc1WV94NGJ5QVRteXRZVEhib3R6bEtoN1lzUTZTb1djVU9oaUFYYTRpckRYeXpkMFpBTVpIeEdTaDd4UUI4S2ZoVUxLaDdkdjh4VzV1VkREeFJIdUpBX0JEUXVNejRMTVFfcjYwcTZYZFpEb2JhZFVwZFRsb2Z0YmNiSmZ4WDhSU0dBU2pkSHIxakZJUXdCcDRpajJsOWNKSGNfanZmZ1Y5WFBEdXRmTU82eWJPUkxfX0FsZ3BxR3VLOWdlcVF4MHFQZTZPYVVVcFRqLVZURzU4YmpsUGFobGdvNjFGb1NJbWQyZkN0RDVHNWtHdjBUZmfSAZACQVVfeXFMUDVVVDd3Q1F2endpeHZGY3dmWmxhTlRtZVVKTVVzVlNCV2s5UlNWMHNEMl91SGRmNHgtYTE0RWNqaEdUbjYwV0hDMnJsXzFFaV9HVy1CREhVa3dGQUpCOWM1dTRVV2ZCNHpvaHFKX2FiSkFFckdJcXlCd2JCZ2Y0NzRsd2RIZ0VIVGtzQ0tPcFJLemJtc2tZbUtSMHVkLWptNEgtX1hZR2lvQlR0VG0zNjU5MExtTndoN1N2ek9NbkNzU2hvcnN2NzZDcFJOd3huU2hubnJZRWJfNEx4aDNxTlEyRzdvdlNyYTF0NHlHazVQUVhockFfcEJJVjZ4MlZ2ZW1faFNpWEZUcjdkT2JwZHY?oc=5" target="_blank"&gt;Milan-London flight diverted to Paris as passenger starts 'eating' passport, another tries to flush it do&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Times of India&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQdWVXYjF2VVhmNF9jRUhOM0tocjc1WV94NGJ5QVRteXRZVEhib3R6bEtoN1lzUTZTb1djVU9oaUFYYTRpckRYeXpkMFpBTVpIeEdTaDd4UUI4S2ZoVUxLaDdkdjh4VzV1VkREeFJIdUpBX0JEUXVNejRMTVFfcjYwcTZYZFpEb2JhZFVwZFRsb2Z0YmNiSmZ4WDhSU0dBU2pkSHIxakZJUXdCcDRpajJsOWNKSGNfanZmZ1Y5WFBEdXRmTU82eWJPUkxfX0FsZ3BxR3VLOWdlcVF4MHFQZTZPYVVVcFRqLVZURzU4YmpsUGFobGdvNjFGb1NJbWQyZkN0RDVHNWtHdjBUZmfSAZACQVVfeXFMUDVVVDd3Q1F2endpeHZGY3dmWmxhTlRtZVVKTVVzVlNCV2s5UlNWMHNEMl91SGRmNHgtYTE0RWNqaEdUbjYwV0hDMnJsXzFFaV9HVy1CREhVa3dGQUpCOWM1dTRVV2ZCNHpvaHFKX2FiSkFFckdJcXlCd2JCZ2Y0NzRsd2RIZ0VIVGtzQ0tPcFJLemJtc2tZbUtSMHVkLWptNEgtX1hZR2lvQlR0VG0zNjU5MExtTndoN1N2ek9NbkNzU2hvcnN2NzZDcFJOd3huU2hubnJZRWJfNEx4aDNxTlEyRzdvdlNyYTF0NHlHazVQUVhockFfcEJJVjZ4MlZ2ZW1faFNpWEZUcjdkT2JwZHY?oc=5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5789,7 +5789,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5820,8 +5819,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>review</t>
@@ -5854,7 +5851,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -5885,8 +5881,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>review</t>
@@ -5919,7 +5913,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -5950,8 +5943,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>review</t>
@@ -5984,7 +5975,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6015,8 +6005,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>review</t>
@@ -6049,7 +6037,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6080,8 +6067,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>review</t>
@@ -6114,7 +6099,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6145,8 +6129,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>review</t>
@@ -6179,7 +6161,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6210,8 +6191,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>review</t>
@@ -6244,7 +6223,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6275,8 +6253,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>review</t>
@@ -6309,7 +6285,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6340,8 +6315,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>review</t>
@@ -6374,7 +6347,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6405,8 +6377,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>review</t>
@@ -6439,7 +6409,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6470,8 +6439,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>review</t>
@@ -6504,7 +6471,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -6535,8 +6501,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>review</t>
@@ -6569,7 +6533,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -6600,8 +6563,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>review</t>
@@ -6634,7 +6595,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -6665,8 +6625,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>review</t>
@@ -6699,7 +6657,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6730,8 +6687,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>review</t>
@@ -6764,7 +6719,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -6795,8 +6749,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>review</t>
@@ -6829,7 +6781,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6860,8 +6811,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>review</t>
@@ -6894,7 +6843,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6925,8 +6873,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>review</t>
@@ -6959,7 +6905,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -6990,8 +6935,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>review</t>
@@ -7024,7 +6967,6 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7055,8 +6997,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>review</t>
@@ -7068,6 +7008,591 @@
         </is>
       </c>
       <c r="O106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>auto-ca1d5123b8ff</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Piloten: Drohnen an Flughäfen nicht vorschnell abschießen</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Nach dem Drohnenvorfall am Flughafen Leipzig/Halle verlangt der Pilotenverband Vereinigung Cockpit (VC) Standards, um derartige Ereignisse einheitlich erkennen und bewerten zu können.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53406/Piloten-Drohnen-an-Flughaefen-nicht-vorschnell-abschiessen.html</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>auto-e19f33dbe4d9</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ab April zu den Azoren: Sata Azores Airlines nimmt Frankfurt-Flüge wieder auf - fvw.de</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivgFBVV95cUxPRWM2T1lxYlNia1RkZk84SUdBRzgzVFE5UDMwUEZVcUpQZE1wUHBSVHltc3E3ZFNDRnNFVTVxN1dtLXFuQ09xazZMVURfcHFNdmRQMEcwZVNHTWRLaWJLR3dqc3JiRjVBQ0NfUktXV2JUY1NydnM2cnNVcUxRMUczMUdSWk1Jb19NaExXVGI1VmJZNTdpbl9YSUpQRWFkb0Y0MEhxRThMejhSTFJZOXIta2g3OHBGRkR1c1pUVVZn?oc=5" target="_blank"&gt;Ab April zu den Azoren: Sata Azores Airlines nimmt Frankfurt-Flüge wieder auf&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPRWM2T1lxYlNia1RkZk84SUdBRzgzVFE5UDMwUEZVcUpQZE1wUHBSVHltc3E3ZFNDRnNFVTVxN1dtLXFuQ09xazZMVURfcHFNdmRQMEcwZVNHTWRLaWJLR3dqc3JiRjVBQ0NfUktXV2JUY1NydnM2cnNVcUxRMUczMUdSWk1Jb19NaExXVGI1VmJZNTdpbl9YSUpQRWFkb0Y0MEhxRThMejhSTFJZOXIta2g3OHBGRkR1c1pUVVZn?oc=5</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>auto-1aa2131ef00b</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Review: Oman Air Business Class Boeing 787-8 Frankfurt nach Muscat - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikAFBVV95cUxQVHZYUmhTUFQxVEgxX2dYUHVGdFZvRDJMd2VtMnN0VnhIeHNoV21PR2tZeUFQQ1RQcUdpNHNaUF9KRXlfOXJ2UDZVclNxalItUDNfWHhjRXhMRElfemVxU0l3TmpLZ0xucGN0b3JpR2xtZzE0SzZqNXhsdUhLV085SGhrM1d0TEdsanFDbWU2Um4?oc=5" target="_blank"&gt;Review: Oman Air Business Class Boeing 787-8 Frankfurt nach Muscat&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQVHZYUmhTUFQxVEgxX2dYUHVGdFZvRDJMd2VtMnN0VnhIeHNoV21PR2tZeUFQQ1RQcUdpNHNaUF9KRXlfOXJ2UDZVclNxalItUDNfWHhjRXhMRElfemVxU0l3TmpLZ0xucGN0b3JpR2xtZzE0SzZqNXhsdUhLV085SGhrM1d0TEdsanFDbWU2Um4?oc=5</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>auto-6f4ce60c5738</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Delta flight DL22 to Munich has declared an emergency during the night and diverted to Ireland - airlive</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQVJvYTRVT0xwaVg3YVM4UGh4RmU3SXdKckxYMUFycmpkd20zY0UxOHRwbmdmdWhOamhRYjFIcndEandZRUR5TDRnUnZPS21ERXdURFpRQ3g1NFRFTFlNMHI2aUVmbnEzV1BZdFN2Sjl1dmtQUG1mRWVwTnVqYmoyZjJsOHBSN2xCLXRZUkpVNXk5Sm9iWUpaSkNiNEN5S2lwV2dBa2gzVjI3YmMxVHB2X096dC1ORGlzMG9KaTktUjNiUUhnRmc0UkJ0eVBuaTJUbkE?oc=5" target="_blank"&gt;Delta flight DL22 to Munich has declared an emergency during the night and diverted to Ireland&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOQVJvYTRVT0xwaVg3YVM4UGh4RmU3SXdKckxYMUFycmpkd20zY0UxOHRwbmdmdWhOamhRYjFIcndEandZRUR5TDRnUnZPS21ERXdURFpRQ3g1NFRFTFlNMHI2aUVmbnEzV1BZdFN2Sjl1dmtQUG1mRWVwTnVqYmoyZjJsOHBSN2xCLXRZUkpVNXk5Sm9iWUpaSkNiNEN5S2lwV2dBa2gzVjI3YmMxVHB2X096dC1ORGlzMG9KaTktUjNiUUhnRmc0UkJ0eVBuaTJUbkE?oc=5</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>auto-5b661b6a3289</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>British Airways flight BA16 to Singapore just returned to Sydney for emergency landing - airlive</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixgFBVV95cUxNQmlzTHJ2VTQwRW9OTlFtMTdIVUxnTW1WODNuU3IzbEpiZDR3NlJtclJTQVh0dFdKOUhmS1ZZUkNUZ09paXl3RmcySmdfZFdCSTM3T2gwUUJPeHo5ZndxVm9vUFhTMWZKX1FfOWdmOHEtZFFta0FpNUdWczVvWFI5ZkpMRHNaRFNsUC1udzBIUjVtU05VREFTdlhsMUpIb3UxQk9Jbk9fNGIwVEJRNG4zcWVwMzRzSjRQQXVsSkRMcTJDeWZweWc?oc=5" target="_blank"&gt;British Airways flight BA16 to Singapore just returned to Sydney for emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNQmlzTHJ2VTQwRW9OTlFtMTdIVUxnTW1WODNuU3IzbEpiZDR3NlJtclJTQVh0dFdKOUhmS1ZZUkNUZ09paXl3RmcySmdfZFdCSTM3T2gwUUJPeHo5ZndxVm9vUFhTMWZKX1FfOWdmOHEtZFFta0FpNUdWczVvWFI5ZkpMRHNaRFNsUC1udzBIUjVtU05VREFTdlhsMUpIb3UxQk9Jbk9fNGIwVEJRNG4zcWVwMzRzSjRQQXVsSkRMcTJDeWZweWc?oc=5</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>auto-f93f4b299089</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EasyJet flight from Liverpool diverted after emergency - Liverpool Echo</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxQTUhBaTYxWFZqeFI4Z0hCQkZqZkFlU1BZQTlpUjdGMXVkQUZoZ0tLeHBWSjFUblBkMFhEVW53TFR0bVRBSndiQnp6N3ZWMDQwZjhibnJZcVNlamFJMzR0ODBjVlZwQjRYbkxCZUJTM0xveW1FVGpNSFdKV3g3UktHODlrNG5kN3NZd0RVbXZNTUtzeDdXc3k2V0lESmtXWmktdmfSAacBQVVfeXFMTl8zWnNlQU9oMEdpUDA1b1c3QXFoY2xxdFRjODdmWHZIQUQxdWVtUHg4VGNzdmVBVXFJdVVSTUt5MHV0TjVXQ2k2eWhxekp1SnNHRTVjRGVaQkVfUVBObEtOcFY1WTltWjBhYWM1cmRrSTExc2xlYWdXV0FJTTZCZ3FuYzNWcl9DQ2RLUTJDcmd0OEx6dlhFSHFLdVF5cjQtZms3OGJCdHc?oc=5" target="_blank"&gt;EasyJet flight from Liverpool diverted after emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Liverpool Echo&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTUhBaTYxWFZqeFI4Z0hCQkZqZkFlU1BZQTlpUjdGMXVkQUZoZ0tLeHBWSjFUblBkMFhEVW53TFR0bVRBSndiQnp6N3ZWMDQwZjhibnJZcVNlamFJMzR0ODBjVlZwQjRYbkxCZUJTM0xveW1FVGpNSFdKV3g3UktHODlrNG5kN3NZd0RVbXZNTUtzeDdXc3k2V0lESmtXWmktdmfSAacBQVVfeXFMTl8zWnNlQU9oMEdpUDA1b1c3QXFoY2xxdFRjODdmWHZIQUQxdWVtUHg4VGNzdmVBVXFJdVVSTUt5MHV0TjVXQ2k2eWhxekp1SnNHRTVjRGVaQkVfUVBObEtOcFY1WTltWjBhYWM1cmRrSTExc2xlYWdXV0FJTTZCZ3FuYzNWcl9DQ2RLUTJDcmd0OEx6dlhFSHFLdVF5cjQtZms3OGJCdHc?oc=5</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>auto-e7d6b3c55574</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Germany investigates Vietnam Airlines 787 incident in Munich - thetraveler.org</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikwFBVV95cUxQTllBUmZYUHotVkllUXB3SGpyU3VtSnZzQWxXMDlYS1ZHZ2h1YmVVNGxpY28yMGxvM1NxWTJKVjg0cm53U1MtTlNXZ3RDZUpSMjhmNlU4N2xyNGZVRXJ0dC1pUWNqVk1UdU1uaXVncDF4UTNxNnB2bkRxRkp6dG1XeXQtdWNSZkdzZTdVRDFOekVmX1k?oc=5" target="_blank"&gt;Germany investigates Vietnam Airlines 787 incident in Munich&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;thetraveler.org&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQTllBUmZYUHotVkllUXB3SGpyU3VtSnZzQWxXMDlYS1ZHZ2h1YmVVNGxpY28yMGxvM1NxWTJKVjg0cm53U1MtTlNXZ3RDZUpSMjhmNlU4N2xyNGZVRXJ0dC1pUWNqVk1UdU1uaXVncDF4UTNxNnB2bkRxRkp6dG1XeXQtdWNSZkdzZTdVRDFOekVmX1k?oc=5</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>auto-01c94c884b02</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Air France Paris to Copenhagen Flight Makes Emergency Landing at Amsterdam - Aviation A2Z</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikwFBVV95cUxOcGMtWEstdlllUDJ6QlA3UTNRWnhQQWQ2dk14dmJ0OXB4c1Zfd1ZfdG4xS1ZvcHRuV1lxTDlXUy1DM0dzWmFJZUZvbHlUOFdJR2tyR2xiNklrUUZIUmJUVEpqcVZWRU9pckJxcmN4YTc4NHlOU0NnMEhvelR3STMyMnMzVGlKT3NpUTJhdXM1S0R4Sm8?oc=5" target="_blank"&gt;Air France Paris to Copenhagen Flight Makes Emergency Landing at Amsterdam&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation A2Z&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOcGMtWEstdlllUDJ6QlA3UTNRWnhQQWQ2dk14dmJ0OXB4c1Zfd1ZfdG4xS1ZvcHRuV1lxTDlXUy1DM0dzWmFJZUZvbHlUOFdJR2tyR2xiNklrUUZIUmJUVEpqcVZWRU9pckJxcmN4YTc4NHlOU0NnMEhvelR3STMyMnMzVGlKT3NpUTJhdXM1S0R4Sm8?oc=5</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>auto-58d84184d243</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Flight makes emergency landing after engine shuts down mid-air and passengers report hearing popping sounds - Daily Mail</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi4AFBVV95cUxNTGRjd0RLdTNuUnlIUFBvTFVMb0dmd2JCbDAzSjhWZVZEYXFnd1Zmb0V2VXlVWmRXWV8teGExaXZwT3F1cnp4S1E4NDlMNkVENWpRX2pGSmdzZks5SnE3eWFZQnpyclhMdjVmS0xCSGNCWllQYTQ1MTQwUFIyenhlV2RScXdQUlhnZ3M3ejVqWmRYQWIzZXNRNkFTMGQtNHl0WnlENEN6VEFDYlEzYXFhUko4NlY0UXVtVlJwSEp4Z1NLWk9RT01RMHp5bVByLXFZRW84Q3RLT0xKRVVhRzcyQg?oc=5" target="_blank"&gt;Flight makes emergency landing after engine shuts down mid-air and passengers report hearing popping sounds&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Daily Mail&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNTGRjd0RLdTNuUnlIUFBvTFVMb0dmd2JCbDAzSjhWZVZEYXFnd1Zmb0V2VXlVWmRXWV8teGExaXZwT3F1cnp4S1E4NDlMNkVENWpRX2pGSmdzZks5SnE3eWFZQnpyclhMdjVmS0xCSGNCWllQYTQ1MTQwUFIyenhlV2RScXdQUlhnZ3M3ejVqWmRYQWIzZXNRNkFTMGQtNHl0WnlENEN6VEFDYlEzYXFhUko4NlY0UXVtVlJwSEp4Z1NLWk9RT01RMHp5bVByLXFZRW84Q3RLT0xKRVVhRzcyQg?oc=5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7029,7 +7029,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7060,8 +7059,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>review</t>
@@ -7094,7 +7091,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7125,8 +7121,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>review</t>
@@ -7159,7 +7153,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7190,8 +7183,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>review</t>
@@ -7224,7 +7215,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7255,8 +7245,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>review</t>
@@ -7289,7 +7277,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7320,8 +7307,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>review</t>
@@ -7354,7 +7339,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7385,8 +7369,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>review</t>
@@ -7419,7 +7401,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7450,8 +7431,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>review</t>
@@ -7484,7 +7463,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -7515,8 +7493,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>review</t>
@@ -7549,7 +7525,6 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -7580,8 +7555,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>review</t>
@@ -7593,6 +7566,1241 @@
         </is>
       </c>
       <c r="O115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>auto-0354b98e8036</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>In Toronto festgehaltene Antonov An-124: Gericht bestätigt kanadische Sanktionen gegen Volga-Dnepr</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Die russische Frachtfluggesellschaft Volga-Dnepr ist mit einer Klage gegen die kanadischen Sanktionen gescheitert. Das Bundesgericht Kanadas entschied, dass die Airline nicht nachweisen konnte, dass die Sanktionierung des Unternehmens und seines früheren Vorsitzenden unangemessen oder verfahrensrechtlich unfair war.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/in-toronto-festgehaltene-antonov-an-124-gericht-bestaetigt-kanadische-sanktionen/89bhh43</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>auto-d98a7026774c</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Zambia Airways holt neuen Chef bei Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Zambia Airways hat Aman Wole Gurmu zum neuen Geschäftsführer ernannt. Der Manager hat den Posten zum 1. August übernommen und kommt von Ethiopian Airlines, wo er mehr als 19 Jahre tätig war. Unter anderem leitete er die Geschäfte in China und der Mongolei sowie in Frankreich und dem Maghreb und war als Regionalmanager für Sambia tätig. Gurmu ist seit der Wiederaufnahme des Flugbetriebs von Zambia Airways im Dezember 2021 bereits der dritte Manager von Ethiopian Airlines an der Spitze der Fluggesellschaft. Ethiopian hält 45 Prozent an Zambia Airways und darf gemäß der Vereinbarung mit der sambischen Regierung den Geschäftsführer nominieren. Gurmu folgt auf Thomas Gabreyohannes Woldesenbet.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/zambia-airways-holt-neuen-chef-bei-ethiopian-airlines/17djlwy</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>auto-d48b72a5cedb</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Teleport baut neues Fracht-Drehkreuz am Flughafen Avalon auf</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Teleport, die Frachttochter von Air-Asia-Mutter von Capital A, richtet am Flughafen Melbourne-Avalon ein neues Drehkreuz für Fracht und E-Commerce ein. Eine entsprechende Partnerschaft haben das Unternehmen und der australische Flughafen vereinbart. Über Avalon soll insbesondere der Warenverkehr zwischen wichtigen asiatischen Märkten und Australien abgewickelt werden. Teleport transportiert bereits Fracht aus China, Hongkong, Indien, Malaysia und Vietnam zu den australischen Flughäfen Melbourne, Sydney, Brisbane und Perth. Mit dem neuen Standort in Avalon setzt das Unternehmen den Ausbau seines Netzwerks in Ozeanien fort. Der Flughafen soll dabei als alternatives internationales Frachtdrehkreuz für den Bundesstaat Victoria dienen.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/teleport-baut-neues-fracht-drehkreuz-am-flughafen-avalon-auf/ynt6b19</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>auto-cc9c8c112485</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Indiens Milliarden-Poker um eine schlagkräftigere Luftwaffe</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>60 neue Transportflugzeuge, weitere Rafale und ein eigener Tarnkappenjet: Indien steckt Milliarden in die Modernisierung seiner Luftstreitkräfte. Dabei setzt Neu-Delhi auf Partner aus Frankreich, Großbritannien, Russland und womöglich Brasilien oder Europa.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/verteidigung/indien-modernisiert-luftwaffe-milliarden-fuer-neue-transport-und-kampfjets/nz5yp7y</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>auto-9f75019270fd</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>200 Tonnen Lachs pro Woche: China Southern startet neue Frachtroute von Oslo nach Shanghai</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>China Southern hat eine neue Frachtverbindung zwischen Oslo und Shanghai aufgenommen. Seit dem 19. August fliegt die Airline zweimal wöchentlich mit einer Boeing 777 F zwischen beiden Städten. Pro Flug stehen rund 100 Tonnen Frachtkapazität zur Verfügung.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/200-tonnen-lachs-pro-woche-china-southern-startet-neue-frachtroute-von-oslo-nach/y6m5cws</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>auto-7d252063e418</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Qatar Airways Cargo will in Hongkong ausbauen</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Der Flughafen Hongkong und Qatar Airways Cargo wollen ihre Zusammenarbeit vertiefen. Airport Authority Hong Kong und die Frachtfluggesellschaft haben dazu eine Absichtserklärung unterzeichnet. Ziel ist es, Hongkong stärker mit dem weltweiten Streckennetz von Qatar Airways Cargo zu verbinden.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/qatar-airways-cargo-will-in-hongkong-ausbauen/zjmd5x7</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>auto-e30a3fc1434b</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lufthansa steigt aus Dienstreiseregelung mit Condor aus</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa kappt eine weitere Kooperation mit Condor. Condor- und Lufthansa-Personal verliert Sonderkonditionen für dienstlich veranlasste Flüge im Netz der jeweils anderen Airline über das Buchungssystem "myIDTravel". Laut Lufthansa wurde die gegenseitige Vereinbarung zunehmend einseitig genutzt.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53424/Lufthansa-steigt-aus-Dienstreiseregelung-mit-Condor-aus.html</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>auto-e1bb967ce988</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TAP-Teilverkauf soll Portugal Milliardenerlös bringen</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>LISSABON - TAP Air Portugal geht entweder an Lufthansa oder an Air France-KLM. Die portugiesische Regierung wird in den nächsten Wochen entscheiden, bei welchem der Airlinekonzerne TAP über eine Teilprivatisierung andockt. Der Staat rechnet nach Medieninformationen mit einem Milliardenerlös.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53422/TAP-Teilverkauf-soll-Portugal-Milliardenerloes-bringen.html</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>auto-a974a0d2c8ca</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Neue Aufklärungsdrohne soll Schutz vor Bedrohung verbessern</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>STRAUSBERG - Zum Schutz kritischer Infrastruktur vor wachsender Bedrohung und zur Überwachung von Ost- und Nordsee will das Luftfahrtunternehmen Aerodata aus Braunschweig eine neue Aufklärungsdrohne liefern. Laut Unternehmen gibt es dazu auch Gespräche mit der Bundeswehr.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53420/Aerodata-stellt-neue-Aufklaerungsdrohne-vor.html</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>auto-aa8f1ebab9d3</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Erster Lufthansa-Airbus mit Starlink unterwegs</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Schneller surfen auf allen Sitzen: Lufthansa schaltet Starlink in einem ersten Flugzeug frei. Das Satelliten-Internet von SpaceX ist seit Mittwoch in einem Airbus A320neo der Kernmarke Lufthansa für Fluggäste verfügbar. Lufthansa will bis 2029 alle Passagierflugzeuge des Konzerns mit der Technik ausstatten.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53421/Erster-Lufthansa-Airbus-mit-Starlink-unterwegs.html</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>auto-6c6d2e4896fb</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>System-Teilausfall reduziert Kapazität am Flughafen Zürich</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ZÜRICH - Am Flughafen Zürich ist die Kapazität seit Dienstag eingeschränkt. Grund dafür ist der Teilausfall eines Systems. Die Ursache für den Ausfall sei derzeit Gegenstand von Abklärungen, teilte ein Flughafensprecher am Mittwoch auf Anfrage der Nachrichtenagentur Keystone-SDA mit. Der "Blick" berichtete online zuerst.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53418/System-Teilausfall-reduziert-Kapazitaet-am-Flughafen-Zuerich.html</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>auto-e8c57a6f818c</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Airbus trennen nur noch Wochen von A350F-Erstflug</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus bereitet die A350F auf den Erstflug vor. Der neue Frachter könnte schon nächsten Monat flügge werden.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53412/Airbus-trennen-nur-noch-Wochen-von-A350F-Erstflug.html</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>auto-b8a411c9c798</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Discover Airlines startet Langstreckenflüge ab München – erste Verbindung in die USA - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisAFBVV95cUxOV0t3cXRGT0lXeFM0dHRxZWZsY0NsdXg2Mm1RcmhDSGxqMVB1dE8tUDhpaTBIRVNjQ1k2dzF6ZG5jQ3plV21mbmNaNGVwOUgySml0UWI2TXVFSDJOa2JlMnY5UnZVZEc1WE16THo2eDROcnNOSWJiTGFLcTJZaUFMU2J5ZkI5dm8yeDdsSTUzby1hZDNVai1EWFFYdjRmVFBHckEyZ3ItTnF1ZHhwMjM1SQ?oc=5" target="_blank"&gt;Discover Airlines startet Langstreckenflüge ab München – erste Verbindung in die USA&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOV0t3cXRGT0lXeFM0dHRxZWZsY0NsdXg2Mm1RcmhDSGxqMVB1dE8tUDhpaTBIRVNjQ1k2dzF6ZG5jQ3plV21mbmNaNGVwOUgySml0UWI2TXVFSDJOa2JlMnY5UnZVZEc1WE16THo2eDROcnNOSWJiTGFLcTJZaUFMU2J5ZkI5dm8yeDdsSTUzby1hZDNVai1EWFFYdjRmVFBHckEyZ3ItTnF1ZHhwMjM1SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>auto-e4b6515bc6ef</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Vietnam Airlines flight makes emergency landing in Munich after technical issue - VnExpress International</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMizwFBVV95cUxPYlA5NjNQTWp6ZGh5VkFwZVZMSzNnTTRJTmN5eUZpcnhRYV9ZS1g1WTdhMTh6bzV2X2V5aFRoMjAtd095VFZ2cHJLTXNRamxaV1MyMXR0ZUlLUkNROFEzQVVaM0tpNmVGQkpNZk9HRDVLaDNUdlowVDJyY2V1YWdGRkxSMnI1VkJuNTlVMzdyTUs3eS1NT3JJeGE4ZzN1OGQ4Y2tzaXROWTM4T3hpMGh2R1lrVlBhb3N6UnNkeTN2OXA5aVBGS3BlMWVaOUVBYW8?oc=5" target="_blank"&gt;Vietnam Airlines flight makes emergency landing in Munich after technical issue&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;VnExpress International&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPYlA5NjNQTWp6ZGh5VkFwZVZMSzNnTTRJTmN5eUZpcnhRYV9ZS1g1WTdhMTh6bzV2X2V5aFRoMjAtd095VFZ2cHJLTXNRamxaV1MyMXR0ZUlLUkNROFEzQVVaM0tpNmVGQkpNZk9HRDVLaDNUdlowVDJyY2V1YWdGRkxSMnI1VkJuNTlVMzdyTUs3eS1NT3JJeGE4ZzN1OGQ4Y2tzaXROWTM4T3hpMGh2R1lrVlBhb3N6UnNkeTN2OXA5aVBGS3BlMWVaOUVBYW8?oc=5</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>auto-c6277a623d0e</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ryanair flight FR4017 to Milan declared an emergency over South of France - airlive.net</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxNWkdYelFrSFg1VE9BTGRQb1RaakVtbktRWTlIMllBbHl3TTNuWVcyZzU2OWpSekxGYzRZclpqLVFOb1RqYXZxUVI4dTc1ek1hXzZRTnl4dzJvd01qTk1vTXBxUmtsUVpHOHRyV1NGcmM3aFNlU1BBcEtHRHA1RVVEZHYzNml1Smt6bUVyREJXeUZNMnZLUTNldXdhb3VWcm1OYlQycmhLdF9PSnM3UTh5RFlHUzlBQQ?oc=5" target="_blank"&gt;Ryanair flight FR4017 to Milan declared an emergency over South of France&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive.net&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNWkdYelFrSFg1VE9BTGRQb1RaakVtbktRWTlIMllBbHl3TTNuWVcyZzU2OWpSekxGYzRZclpqLVFOb1RqYXZxUVI4dTc1ek1hXzZRTnl4dzJvd01qTk1vTXBxUmtsUVpHOHRyV1NGcmM3aFNlU1BBcEtHRHA1RVVEZHYzNml1Smt6bUVyREJXeUZNMnZLUTNldXdhb3VWcm1OYlQycmhLdF9PSnM3UTh5RFlHUzlBQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>auto-d1015c42120d</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>25 injured as turbulence rocks Delta flight to Europe, forces emergency landing in Minn. - EMS1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi0AFBVV95cUxOb0hrc1ZaX2FZdjYwc1BROUhtcE9fN184bTBNc0xiRThRMzZaVGV1dVZhYS00Qm9HaW0yNWJwUEZFdHdVVENoZ2JsWVhaUVhyVXNnRTUzRGxQT1doS0QxNXIyRWxFeTl0UGRjbjhlWnh5NFVkOWJIcnV4QjYzVnJDOGhpREJ5ZWRHVkhNRE51LWUzUVdLZmRqVDVldzVRbU1TdTVzZGdRbnRYNnd6YzRtSnNfTm44c3FBcVByRklDZ05sai14c1lIdndjVzdscVVF?oc=5" target="_blank"&gt;25 injured as turbulence rocks Delta flight to Europe, forces emergency landing in Minn.&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;EMS1&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOb0hrc1ZaX2FZdjYwc1BROUhtcE9fN184bTBNc0xiRThRMzZaVGV1dVZhYS00Qm9HaW0yNWJwUEZFdHdVVENoZ2JsWVhaUVhyVXNnRTUzRGxQT1doS0QxNXIyRWxFeTl0UGRjbjhlWnh5NFVkOWJIcnV4QjYzVnJDOGhpREJ5ZWRHVkhNRE51LWUzUVdLZmRqVDVldzVRbU1TdTVzZGdRbnRYNnd6YzRtSnNfTm44c3FBcVByRklDZ05sai14c1lIdndjVzdscVVF?oc=5</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>auto-527141160d88</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Airbus A320 makes emergency landing in Saint Petersburg, Russia - Gulf News</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxNRzBvcGRTMTA1M1ZEaVBhOWswNmd0UC1fTFg5R3kxOE1ybHNmaHVDLXEySFlyMVUzcDVkQ1BhZHVyM0VLdEZPU0VDV0pBeHExUUtmcU9pVFRlUHQzMWtzZElfZTBNQk1GWGYxX2ZhSmVFalRNc0g1S19Wb1R0OEJUWmpvMjdZMnlaX3ZFS3BGbDNtcWFHaElnZHk5dTZ5eFotNHJwb0NmMktIazNB0gG_AUFVX3lxTE9iV3BfanZDQXZVV3FHdnYzUlFUaXdnRzJPQ20zR0NhUGM5RTlzcW1RX1ctTTFuY19SLXA0Qm9oel9ROFRaRzM3blRKcFN3VnpsaVd1RHFEaExSLVhoNk55cHctcEp4ZU0ya041azVnbnJ3NkpSWjRkQ2o1b0pTTnlkQUFNcmxxQ2NQci1iUUFLdVpCYURpbG1yV3NLSTRkRzBOY0FEV21zeXo4UkUyOTM2WWlYY2p5eTg3Q2FUX2c4?oc=5" target="_blank"&gt;Airbus A320 makes emergency landing in Saint Petersburg, Russia&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Gulf News&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNRzBvcGRTMTA1M1ZEaVBhOWswNmd0UC1fTFg5R3kxOE1ybHNmaHVDLXEySFlyMVUzcDVkQ1BhZHVyM0VLdEZPU0VDV0pBeHExUUtmcU9pVFRlUHQzMWtzZElfZTBNQk1GWGYxX2ZhSmVFalRNc0g1S19Wb1R0OEJUWmpvMjdZMnlaX3ZFS3BGbDNtcWFHaElnZHk5dTZ5eFotNHJwb0NmMktIazNB0gG_AUFVX3lxTE9iV3BfanZDQXZVV3FHdnYzUlFUaXdnRzJPQ20zR0NhUGM5RTlzcW1RX1ctTTFuY19SLXA0Qm9oel9ROFRaRzM3blRKcFN3VnpsaVd1RHFEaExSLVhoNk55cHctcEp4ZU0ya041azVnbnJ3NkpSWjRkQ2o1b0pTTnlkQUFNcmxxQ2NQci1iUUFLdVpCYURpbG1yV3NLSTRkRzBOY0FEV21zeXo4UkUyOTM2WWlYY2p5eTg3Q2FUX2c4?oc=5</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>auto-42aaf6c50eee</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Delta: 25 injured by turbulence forces emergency landing - BBC</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiWkFVX3lxTE1oaXEyTUlFSVlzX05fZkJFUk1nVmo3NnVYV05YYjUxdEp1ZmNPMzVDZnNFekZpaFhUdkFrR3c0Q3ZJZUpEMGlVSEViOThRSmJrdkhFZGd3a1FsUQ?oc=5" target="_blank"&gt;Delta: 25 injured by turbulence forces emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;BBC&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1oaXEyTUlFSVlzX05fZkJFUk1nVmo3NnVYV05YYjUxdEp1ZmNPMzVDZnNFekZpaFhUdkFrR3c0Q3ZJZUpEMGlVSEViOThRSmJrdkhFZGd3a1FsUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>auto-8f8f38d7ea04</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Severe turbulence forces Delta plane to make emergency landing after 25 passengers injured - The Guardian</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilgFBVV95cUxNUmRYRHVjMkVTeG9LUk9CWjk1UmQyZl9ROERpaWJObjBHUGI4XzZfMWpVQlgxckJDSDdJdmN6VnVmQzF1ay1QV3JwT2pEbjg0ejF1YVYzMDZIRjluQ0dpZkNmQjBqTUJGaVdSQ0tDZDNReWtnSWpxa0F4STNoZHhwNzBXQ0E1T0JYNzhTck9XakVfdEh3elE?oc=5" target="_blank"&gt;Severe turbulence forces Delta plane to make emergency landing after 25 passengers injured&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Guardian&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNUmRYRHVjMkVTeG9LUk9CWjk1UmQyZl9ROERpaWJObjBHUGI4XzZfMWpVQlgxckJDSDdJdmN6VnVmQzF1ay1QV3JwT2pEbjg0ejF1YVYzMDZIRjluQ0dpZkNmQjBqTUJGaVdSQ0tDZDNReWtnSWpxa0F4STNoZHhwNzBXQ0E1T0JYNzhTck9XakVfdEh3elE?oc=5</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7587,7 +7587,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7618,8 +7617,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>review</t>
@@ -7652,7 +7649,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7683,8 +7679,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>review</t>
@@ -7717,7 +7711,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7748,8 +7741,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>review</t>
@@ -7782,7 +7773,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7813,8 +7803,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>review</t>
@@ -7847,7 +7835,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7878,8 +7865,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>review</t>
@@ -7912,7 +7897,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -7943,8 +7927,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>review</t>
@@ -7977,7 +7959,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8008,8 +7989,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>review</t>
@@ -8042,7 +8021,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8073,8 +8051,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>review</t>
@@ -8107,7 +8083,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8138,8 +8113,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>review</t>
@@ -8172,7 +8145,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8203,8 +8175,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>review</t>
@@ -8237,7 +8207,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8268,8 +8237,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>review</t>
@@ -8302,7 +8269,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8333,8 +8299,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>review</t>
@@ -8367,7 +8331,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8398,8 +8361,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
           <t>review</t>
@@ -8432,7 +8393,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -8463,8 +8423,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>review</t>
@@ -8497,7 +8455,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8528,8 +8485,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>review</t>
@@ -8562,7 +8517,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -8593,8 +8547,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
           <t>review</t>
@@ -8627,7 +8579,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -8658,8 +8609,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>review</t>
@@ -8692,7 +8641,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -8723,8 +8671,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
           <t>review</t>
@@ -8757,7 +8703,6 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -8788,8 +8733,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
           <t>review</t>
@@ -8801,6 +8744,656 @@
         </is>
       </c>
       <c r="O134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>auto-7b34f106eb3f</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>45 Jahre alte Lockheed L-1011 Tristar soll noch in diesem Jahr wieder fliegen</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>In Kenias Hauptstadt Nairobi steht eine 45-jährige Lockheed L-1011 Tristar, die wieder abheben und Fracht transportieren soll. aeroTELEGRAPH sprach mit einem, der an dem Projekt beteiligt ist - und auch eine 57-jährige Douglas DC-8 wieder in die Luft bringen will.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/45-jahre-alte-lockheed-l-1011-tristar-soll-noch-in-diesem-jahr-wieder-fliegen/nh41q2n</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>auto-3251f24aab05</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Condor kehrt erst im Mai 2027 nach Tiflis zurück</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Condor hat die geplante Wiederaufnahme der Verbindung von Frankfurt nach Tiflis deutlich nach hinten verschoben. Statt wie ursprünglich vorgesehen ab 15. Juni 2026 soll die Strecke nun ab dem 2. Mai 2027 wieder bedient werden. Die Verbindung war zuletzt im Oktober 2023 angeboten worden, so das Portal Aero Routes.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/condor-kehrt-erst-im-mai-2027-nach-tiflis-zurueck/86dfmws</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>auto-ff1e79119c06</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Boeing 747-8 von Lufthansa muss in Schottland runter</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Eine Lufthansa-Maschine ist am Donnerstag auf dem Weg von Frankfurt am Main nach Chicago außerplanmäßig in Schottland gelandet.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53435/Boeing-747-8-von-Lufthansa-muss-in-Schottland-runter.html</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>auto-d28b2818813a</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Jüngere Lufthansa-Piloten sind im Job zufriedener als ältere</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Wie ist die Stimmung unter Lufthansa-Piloten? Die Vereinigung Cockpit (VC) hat eine Forsa-Umfrage beauftragt - eine "repräsentative Mitgliederbefragung" deckt deutliche Unterschiede im Meinungsbild nach Altergruppen auf. Die Umfrage selbst war nach Informationen von aero.de unter Lufthansa-Piloten nicht unumstritten.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53431/Juengere-Lufthansa-Piloten-sind-im-Job-zufriedener-als-aeltere.html</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>auto-1372638ffa33</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Das ist der Sommerflugplan 2026 am Flughafen Frankfurt - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lvMVdIdnRGUWVNYzR4c2ZwYTBFamo0TWp4TVo1WWhQRWt2bm1qVXpudFdlM0g1eHpZaXZXYnZWOFh3OXJ3cm9pbDdnOTZjOW9KTV9vamRiTmIwSndpSDRFSHNBZVNEbnpaek5xdkxsb1JNRjR3UWtmTDQ1eHFnamJuTWxxMTNmZEVHcW9KZHd5NVppc1JFZ1NVTkNTeG5F?oc=5" target="_blank"&gt;Das ist der Sommerflugplan 2026 am Flughafen Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lvMVdIdnRGUWVNYzR4c2ZwYTBFamo0TWp4TVo1WWhQRWt2bm1qVXpudFdlM0g1eHpZaXZXYnZWOFh3OXJ3cm9pbDdnOTZjOW9KTV9vamRiTmIwSndpSDRFSHNBZVNEbnpaek5xdkxsb1JNRjR3UWtmTDQ1eHFnamJuTWxxMTNmZEVHcW9KZHd5NVppc1JFZ1NVTkNTeG5F?oc=5</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>auto-f152116f6ce5</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Neues Direktziel ab Frankfurt: Diese Weltmetropole fliegt Condor ab sofort täglich an - fnp.de</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqAFBVV95cUxQWWJCRzFiWEswRWd4aDl0SVVkYkZUSDdsdzNQaVJweEJLT292aEVETkpRNUZvbVoxM1RobXZrZGxEUk1PMFZxSE9rcG5uVDRQdUNuSjd6WEVnMC11UXF6NV9tODBFVldzNTY1TVlkdGlKajBocVZESlNTamtTd2p1NnhLZ21lVzF1S1lkcGtSek5MY2ZMTzA3QXZrYTkyNEs4LWxDNmhpckk?oc=5" target="_blank"&gt;Neues Direktziel ab Frankfurt: Diese Weltmetropole fliegt Condor ab sofort täglich an&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQWWJCRzFiWEswRWd4aDl0SVVkYkZUSDdsdzNQaVJweEJLT292aEVETkpRNUZvbVoxM1RobXZrZGxEUk1PMFZxSE9rcG5uVDRQdUNuSjd6WEVnMC11UXF6NV9tODBFVldzNTY1TVlkdGlKajBocVZESlNTamtTd2p1NnhLZ21lVzF1S1lkcGtSek5MY2ZMTzA3QXZrYTkyNEs4LWxDNmhpckk?oc=5</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>auto-c9ae4cd4ce00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Asiana Airlines kommt seltener nach Frankfurt - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilAFBVV95cUxQUHZ3Y1ZWcXVUbFp6OWF3UlNnU1NVeF9JUHo0MnZ0akdla2FLbEhkX3M0Z2tsQ1ZtWkI4NVlpaVlOMUYzQmJYdWpSWVpiODFKVTBFb0p4Z3RHYjlOZ0g0ZUJvcXc1bExTdVU0MGRnZ0dvYXBXVWgwSHJMXzNSSlMwZUVISFpRZFNPVnA0TGFvTlRVNGll?oc=5" target="_blank"&gt;Asiana Airlines kommt seltener nach Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQUHZ3Y1ZWcXVUbFp6OWF3UlNnU1NVeF9JUHo0MnZ0akdla2FLbEhkX3M0Z2tsQ1ZtWkI4NVlpaVlOMUYzQmJYdWpSWVpiODFKVTBFb0p4Z3RHYjlOZ0g0ZUJvcXc1bExTdVU0MGRnZ0dvYXBXVWgwSHJMXzNSSlMwZUVISFpRZFNPVnA0TGFvTlRVNGll?oc=5</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>auto-c3a7492ced7c</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: AHS fertigt Maschinen für T’Way Air ab - Airportzentrale</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMinAFBVV95cUxPQnRxRTdyNFJRdnljMDQwS2VuU0F3VzNZVEFZWjFqYkNmaDBTNFpBeXhjLS1EdGRzSjhkdWptcldKcGZJRk1Ub0ZTTlN0Vk5kNGlyRXBTSVZrM0xVcDlxN1ViMWNqbUdvYU9OdHdpTGx0MEhQenJlMHZLM1ZQcGY1cHJveU85X2pVUVJ1U0FlNy03ckpJdm1xT1NVRHA?oc=5" target="_blank"&gt;Flughafen Frankfurt: AHS fertigt Maschinen für T’Way Air ab&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airportzentrale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPQnRxRTdyNFJRdnljMDQwS2VuU0F3VzNZVEFZWjFqYkNmaDBTNFpBeXhjLS1EdGRzSjhkdWptcldKcGZJRk1Ub0ZTTlN0Vk5kNGlyRXBTSVZrM0xVcDlxN1ViMWNqbUdvYU9OdHdpTGx0MEhQenJlMHZLM1ZQcGY1cHJveU85X2pVUVJ1U0FlNy03ckpJdm1xT1NVRHA?oc=5</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>auto-a185841b7f10</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Lufthansa: Der ewige Konkurrenzkampf zwischen Frankfurt und München - Aviation.Direct</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilgFBVV95cUxNZ0g2dHAzczFabW12NE9UeV9vbFp2RWtOMXVZbnF3YkY4anlCYUxqNW5WUTczTl9WUHdGVzY2cG5ZR2RvcWN5MmhGUXR0OG1ISVlsSTktX2dyc2RMaDlYVTUxZl8wc2VZeXN2eElPbThTZjBCak5tSTVYVlNaYXZSSmtHZVc0Z09ONGQ5SkRKNXY5aHZGX2c?oc=5" target="_blank"&gt;Lufthansa: Der ewige Konkurrenzkampf zwischen Frankfurt und München&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation.Direct&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNZ0g2dHAzczFabW12NE9UeV9vbFp2RWtOMXVZbnF3YkY4anlCYUxqNW5WUTczTl9WUHdGVzY2cG5ZR2RvcWN5MmhGUXR0OG1ISVlsSTktX2dyc2RMaDlYVTUxZl8wc2VZeXN2eElPbThTZjBCak5tSTVYVlNaYXZSSmtHZVc0Z09ONGQ5SkRKNXY5aHZGX2c?oc=5</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>auto-a3ee06a86d49</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Toilette übergelaufen: United Airlines-Flug muss nach Frankfurt zurückkehren - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipwFBVV95cUxOWFpLdXZQeEhCUUcwRFdIVU5GcWJaU2YtVF8xOFR3c3ZJcm04RklkXzFZeDNIc1U4SFB3aTc3bzBPTUl4LU03bnRNbkZ1b250TFJxTlBXTmRkUk1BUWNORVFfVmxEOHNZLWJCcGZxOUl2TzBORWlnR19Dd3A2ZmUtNmJ5cTBLanhOMmk3bFZHT0wwcDJjUnhoaUNUWDVZTzFEX0ZRSUd5WQ?oc=5" target="_blank"&gt;Toilette übergelaufen: United Airlines-Flug muss nach Frankfurt zurückkehren&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOWFpLdXZQeEhCUUcwRFdIVU5GcWJaU2YtVF8xOFR3c3ZJcm04RklkXzFZeDNIc1U4SFB3aTc3bzBPTUl4LU03bnRNbkZ1b250TFJxTlBXTmRkUk1BUWNORVFfVmxEOHNZLWJCcGZxOUl2TzBORWlnR19Dd3A2ZmUtNmJ5cTBLanhOMmk3bFZHT0wwcDJjUnhoaUNUWDVZTzFEX0ZRSUd5WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8765,7 +8765,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8796,8 +8795,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
           <t>review</t>
@@ -8830,7 +8827,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8861,8 +8857,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>review</t>
@@ -8895,7 +8889,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8926,8 +8919,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
           <t>review</t>
@@ -8960,7 +8951,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -8991,8 +8981,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
           <t>review</t>
@@ -9025,7 +9013,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9056,8 +9043,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
           <t>review</t>
@@ -9090,7 +9075,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9121,8 +9105,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
           <t>review</t>
@@ -9155,7 +9137,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9186,8 +9167,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
           <t>review</t>
@@ -9220,7 +9199,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9251,8 +9229,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
           <t>review</t>
@@ -9285,7 +9261,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9316,8 +9291,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>review</t>
@@ -9350,7 +9323,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9381,8 +9353,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>review</t>
@@ -9394,6 +9364,1046 @@
         </is>
       </c>
       <c r="O144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>auto-36c99b8a074b</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ITA Airways reduziert Deutschland-Flüge im Winter</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>ITA Airways kürzt zum Winterflugplan 2026/27 ihr Angebot zwischen Rom und Deutschland. Ab dem 25. Oktober reduziert die italienische Fluggesellschaft sowohl Frankfurt als auch München von zwei auf einen täglichen Flug.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ita-airways-reduziert-deutschland-fluege-im-winter/eyx9smp</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>auto-970494ababd4</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt setzt elektrische Schlepper für Großflugzeuge ein</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Betreiberin Fraport hat am Flughafen Frankfurt zwei vollelektrische Flugzeugschlepper des Typs E-Phoenix von Goldhofer in Betrieb genommen. Ein drittes Fahrzeug ist bereits bestellt. Die Schlepper können auch große Passagierflugzeuge bewegen, etwa beim Pushback oder bei Positionswechseln auf dem Vorfeld.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-frankfurt-setzt-elektrische-schlepper-fuer-grossflugzeuge-ein/678whj5</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>auto-bc5419b57f90</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Flughafen Zürich steigt beim Flughafen Belo Horizonte aus</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Die Flughafen Zürich AG verkauft ihre Minderheitsbeteiligung von 12,75 Prozent am internationalen Flughafen Belo Horizonte in Brasilien. Käuferin ist Aeropuerto de Cancún, eine Tochter der mexikanischen Flughafenbetreiberin Asur. Bei Abschluss der Transaktion erwartet der Flughafen Zürich einen einmaligen Reingewinn von rund 17 Millionen Franken.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-zuerich-steigt-beim-flughafen-belo-horizonte-aus/kwv87bg</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>auto-286553cce496</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>German Airways fliegt im Winter für Condor auch nach Zürich</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>German Airways wird im Winterflugplan 2026/27 mit Embraer E190 hauptsächlich auf vier Strecken für Condor fliegen. Saisonal verändert sich das Streckennetz: Venedig entfällt im Winter, dafür kommt für die deutsche Wet-Lease-Fluglinie Zürich neu hinzu. Condor fliegt drei Mal täglich zwischen Frankfurt und Zürich. Auf der Strecke ist auch Helvetic Airways für den deutschen Städte- und Ferienflieger unterwegs.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/german-airways-fliegt-im-winter-fuer-condor-auch-nach-zuerich/2sv274r</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>auto-56b19fcb9ae9</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Warum bei City Airlines Gehaltsforderungen aufliefen</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa hat City Airlines im April 2026 aus einem Guss tarifiert. Piloten und Flugbegleiter arbeiten unter aufeinander abgestimmten Verdi-Konditionen. Nur an der Umsetzung der Verträge hapert es - Verdi wirft City Airlines "Zahlungsverzug" vor. Die Lufthansa-Tochter erklärt sich, Ufo grätscht in den Streit.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53442/Ufo-City-Airlines-und-Verdi-bummeln-bei-Tarifabsprachen.html</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>auto-dcc856fce12f</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Flug von Thai Airways kehrt nach Frankfurt um</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Ein Flugzeug von Frankfurt nach Bangkok kehrt außerplanmäßig nach Frankfurt zurück.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53448/Flug-von-Thai-Airways-kehrt-nach-Frankfurt-um.html</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>auto-9f8adb6a85e1</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Bilger: Interimstechnik für Drohnenabwehr an Flughäfen</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>FRANKFURT - An Deutschlands Flughäfen sollen Drohnen künftig schneller und früher entdeckt werden. In den An- und Abflugbereichen der Flughäfen soll kurzfristig eine Interimstechnik der Deutschen Flugsicherung (DFS) zum Einsatz kommen, wie Bundesverkehrsminister Steffen Bilger (CDU) angekündigt hat.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53447/Bilger-Interimstechnik-fuer-Drohnenabwehr-an-Flughaefen.html</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>auto-cc7b88f5449a</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Roland Koch und Bodo Ramelow vermitteln bei Lufthansa</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Im Tarifstreit zwischen der Lufthansa und ihren Piloten haben die beiden Seiten zwei frühere Ministerpräsidenten als Schlichter gewonnen.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53444/Vereinigung-Cockpit-schickt-Bodo-Ramelow-ins-Rennen.html</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>auto-8b6d0d35080d</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Airbus verpackt erste A350F in einer Paketlackierung</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus will mit der A350F auch im Frachtermarkt an die Spitze. Der erste Prototyp steht vor dem Eintritt in die Flugerprobung. Jetzt ist das Flugzeug lackiert - Airbus hat der ersten A350F ein Sonderdesign verpasst. Auch das zweite Flugzeug für die Flugtestphase macht Fortschritte.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53441/Airbus-verpackt-erste-A350F-in-einer-Paketlackierung.html</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>auto-c7a4db021252</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Discover Airlines muss auf Namibia-Linie Tankstopp einlegen</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Befürchtete Mangellagen bei Flugtreibstoff durch den Iran-Krieg blieben aus - Europas Airlines operieren im Flugsommer 2026 stabil. Vereinzelt hapert es mit der Kerosinversorgung vor Ort aber doch - Discover Airlines ist in Namibia aktuell mit Treibstoffrationierungen konfrontiert.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53440/Discover-Airlines-muss-auf-Namibia-Linie-Tankstopp-einlegen.html</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>auto-58aa34945a23</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Airline vollzieht Umzug an den Flughafen Frankfurt – Abflüge künftig am neuen Terminal - Frankfurter Rundschau</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiywFBVV95cUxPcWREY3RzeWVjN2RGc1RGc05LQUFFal9CQ3VNN3pfM1FEY0V3LVZmTXFFNnFCR0paWVR0aG1UdFZ1UDVfQTZ0SDU0VEhZYURBVE1zYVJ3anZweUlhdDVUcGZiQURCU1kyVnVaNFJBMFlXcU5qRkw5LVdfdkxaeTNlYXJEV00tX0hTYml0WXZYQzY1aDAyUjI5YzdYWmZmM1JscFdROTVBR0VhNW10ZnlFN1RFdmpXelp1U21aNGNnMWgxaExCQzNHTGwxVQ?oc=5" target="_blank"&gt;Airline vollzieht Umzug an den Flughafen Frankfurt – Abflüge künftig am neuen Terminal&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurter Rundschau&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPcWREY3RzeWVjN2RGc1RGc05LQUFFal9CQ3VNN3pfM1FEY0V3LVZmTXFFNnFCR0paWVR0aG1UdFZ1UDVfQTZ0SDU0VEhZYURBVE1zYVJ3anZweUlhdDVUcGZiQURCU1kyVnVaNFJBMFlXcU5qRkw5LVdfdkxaeTNlYXJEV00tX0hTYml0WXZYQzY1aDAyUjI5YzdYWmZmM1JscFdROTVBR0VhNW10ZnlFN1RFdmpXelp1U21aNGNnMWgxaExCQzNHTGwxVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>auto-3b56ca54e8c1</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Indien ab 1.373€ in der Air India Business Class von Frankfurt - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMicEFVX3lxTE1MOG85THhUWHdjZG5yeHhMSThLQVVXR3ozNjdDeWQ2Z0hHVnRtSUlZN3hWTXZkeW5vYjJOcWxSeGw2Ry1CU3NmSEpHOEtFa0NsQV9jLUFzUnkzUG5jUUFJUEJhcnpuaU4yczJ6Y2ExWmI?oc=5" target="_blank"&gt;Indien ab 1.373€ in der Air India Business Class von Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1MOG85THhUWHdjZG5yeHhMSThLQVVXR3ozNjdDeWQ2Z0hHVnRtSUlZN3hWTXZkeW5vYjJOcWxSeGw2Ry1CU3NmSEpHOEtFa0NsQV9jLUFzUnkzUG5jUUFJUEJhcnpuaU4yczJ6Y2ExWmI?oc=5</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>auto-194f09a05940</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pharma-Hub FRA – Gemeinsam für eine starke Luftfracht in der Pandemie - Mynewsdesk</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiyAFBVV95cUxOc0Fldkl6TzEtc00zei0zV293blZra3Vrc2NhU0NNWm9xaVNlaG1kMHpHRjFWSTloeUdMeE14RVdWRzdGUG0wZmp4V00xSHgwQ05WNllEd3pjM3VwZ3Q3ZFd1aS1hdm9DVVE1czlrLWxBaDZ4UXBXeWI1T1NkQUFBbEpXOGFEZHVkMmVoMDBKbG11SzRLdWRmeTIxQ2VrQUdGQlVtNmN0blBfNm1tRWhDMExBU09qUVBSUl8zaW9oanB6Z0xxR0ZPZw?oc=5" target="_blank"&gt;Pharma-Hub FRA – Gemeinsam für eine starke Luftfracht in der Pandemie&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Mynewsdesk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOc0Fldkl6TzEtc00zei0zV293blZra3Vrc2NhU0NNWm9xaVNlaG1kMHpHRjFWSTloeUdMeE14RVdWRzdGUG0wZmp4V00xSHgwQ05WNllEd3pjM3VwZ3Q3ZFd1aS1hdm9DVVE1czlrLWxBaDZ4UXBXeWI1T1NkQUFBbEpXOGFEZHVkMmVoMDBKbG11SzRLdWRmeTIxQ2VrQUdGQlVtNmN0blBfNm1tRWhDMExBU09qUVBSUl8zaW9oanB6Z0xxR0ZPZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>auto-aa743dc3046f</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Wizz Air nimmt FRA ins Visier - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMieEFVX3lxTFAwLXFTd3QwZVk5WUZYUnhkUldLaXpPeWxaWU16TU11SXBGLWxDb012UEhIMjVodVFQR29TenFrZTQ2SDJ4Rk45QzU1RTV1dkRyd0FsbE41N284TnhjY25XdnVCX2R4eHpxcGNNMkhNYUtlMGx5TWp0aA?oc=5" target="_blank"&gt;Wizz Air nimmt FRA ins Visier&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFAwLXFTd3QwZVk5WUZYUnhkUldLaXpPeWxaWU16TU11SXBGLWxDb012UEhIMjVodVFQR29TenFrZTQ2SDJ4Rk45QzU1RTV1dkRyd0FsbE41N284TnhjY25XdnVCX2R4eHpxcGNNMkhNYUtlMGx5TWp0aA?oc=5</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>auto-6470f3a37867</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>FRA-Sommerflugplan 2013: 295 Ziele in 107 Ländern - Austrian Wings</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikwFBVV95cUxPbGNWM09pNVdla185YWZxeUk4RHMwTkR0TDlYMWJVTVp6S2dhNWVGUGxQQ1Q5cFN5NWhYV0lZVGNhVTRhWHQ0cGRXNE5NamUzTGMxRTdJZ0Q0U3pRUXlOaGIzTEZsUk95OV9RcDVDOHFyZGFhOE81VC1aRXBjT1RBS3hnLWFHUUp0ZENfaUV1ZklCM0k?oc=5" target="_blank"&gt;FRA-Sommerflugplan 2013: 295 Ziele in 107 Ländern&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Austrian Wings&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbGNWM09pNVdla185YWZxeUk4RHMwTkR0TDlYMWJVTVp6S2dhNWVGUGxQQ1Q5cFN5NWhYV0lZVGNhVTRhWHQ0cGRXNE5NamUzTGMxRTdJZ0Q0U3pRUXlOaGIzTEZsUk95OV9RcDVDOHFyZGFhOE81VC1aRXBjT1RBS3hnLWFHUUp0ZENfaUV1ZklCM0k?oc=5</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>auto-fc077750aab2</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Thai Airways Boeing 777 flight TG921 to Bangkok declared an emergency and just returned to Frankfurt - airlive</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2gFBVV95cUxQdWtvbUg3MVo1MWJqX2VBbW0xTmxrVXU3VzVRaXBzWDJ3Qllza2hkZVdGOFl5ZGVGSk4wbktmdlF1U3lmZTBKZUNaS3BDTGtRR1QyZXk0aC1feEZnZkE1Vk9sdnJvNjVlb1BzdGpGeXU4RXhUeWIzakJYeHg5Z3dkSGV2WDVQYkRZVUx6Z3BOcGh4ampuTDhTNUhNUFpJUzVjSS16N1A0dER6WFlOaWtPQ0FQbEdxSDVXOGcwZ3ExMmcxaF9ubk52ZTFyc0NTa25PQ1VQRVNwT183Zw?oc=5" target="_blank"&gt;Thai Airways Boeing 777 flight TG921 to Bangkok declared an emergency and just returned to Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQdWtvbUg3MVo1MWJqX2VBbW0xTmxrVXU3VzVRaXBzWDJ3Qllza2hkZVdGOFl5ZGVGSk4wbktmdlF1U3lmZTBKZUNaS3BDTGtRR1QyZXk0aC1feEZnZkE1Vk9sdnJvNjVlb1BzdGpGeXU4RXhUeWIzakJYeHg5Z3dkSGV2WDVQYkRZVUx6Z3BOcGh4ampuTDhTNUhNUFpJUzVjSS16N1A0dER6WFlOaWtPQ0FQbEdxSDVXOGcwZ3ExMmcxaF9ubk52ZTFyc0NTa25PQ1VQRVNwT183Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O160"/>
+  <dimension ref="A1:O166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9385,7 +9385,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9416,8 +9415,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>review</t>
@@ -9450,7 +9447,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9481,8 +9477,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>review</t>
@@ -9515,7 +9509,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9546,8 +9539,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>review</t>
@@ -9580,7 +9571,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9611,8 +9601,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>review</t>
@@ -9645,7 +9633,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9676,8 +9663,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>review</t>
@@ -9710,7 +9695,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9741,8 +9725,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>review</t>
@@ -9775,7 +9757,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9806,8 +9787,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>review</t>
@@ -9840,7 +9819,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9871,8 +9849,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>review</t>
@@ -9905,7 +9881,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -9936,8 +9911,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>review</t>
@@ -9970,7 +9943,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10001,8 +9973,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
           <t>review</t>
@@ -10035,7 +10005,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10066,8 +10035,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
           <t>review</t>
@@ -10100,7 +10067,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10131,8 +10097,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
           <t>review</t>
@@ -10165,7 +10129,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10196,8 +10159,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
           <t>review</t>
@@ -10230,7 +10191,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10261,8 +10221,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
           <t>review</t>
@@ -10295,7 +10253,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10326,8 +10283,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>review</t>
@@ -10360,7 +10315,6 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10391,8 +10345,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
           <t>review</t>
@@ -10404,6 +10356,396 @@
         </is>
       </c>
       <c r="O160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>auto-6ecb0ef2d1cb</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Urlaubs-Umzug in Frankfurt: Erster Ferienflieger startet in Terminal 3 - TUI Group</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisAFBVV95cUxOdGpOMnB6YmM3UzJPQnNxNGhZRVkydk9fVEJKVHRacXdodTRGZ1FWYWtYOUEzVHhtWUYyZUE1WWdBS25TZFZEN18wd1lkZFNxdEktdlUzYUFBUnZWaXJMOEo1aHBES1IxdmNRTVV0WmhlemJ0M0thQ2Y1bHkyYnlOSlRzSXZ0dENYb3ZXLUhkYm1aNGVnUzZySzR4dzRmUlBpdXdJeTdQUjlOdE8zallNLQ?oc=5" target="_blank"&gt;Urlaubs-Umzug in Frankfurt: Erster Ferienflieger startet in Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TUI Group&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOdGpOMnB6YmM3UzJPQnNxNGhZRVkydk9fVEJKVHRacXdodTRGZ1FWYWtYOUEzVHhtWUYyZUE1WWdBS25TZFZEN18wd1lkZFNxdEktdlUzYUFBUnZWaXJMOEo1aHBES1IxdmNRTVV0WmhlemJ0M0thQ2Y1bHkyYnlOSlRzSXZ0dENYb3ZXLUhkYm1aNGVnUzZySzR4dzRmUlBpdXdJeTdQUjlOdE8zallNLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>auto-c7d8a8e49e59</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Terminal 3 eröffnet – das sind die Auswirkungen für Reisende - Main-Post</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2AFBVV95cUxNZGd3TmtqZ2c1SThzM0lFYVVtei03SWhFdzY2OG44Y2JlQl9jWC1rOTdXX3B6MVVVQjBzSkw4RjcwdTh0TUpYb2ZEMXNyNTUwOWZrNWM1ZXd3THI1ZHc3OUQyZWNpRW9yNnBsOGFHWXdWX1kxZV9adW9RTHlYZnp3R0ZoY01DZG5wUUNqdlAwR015SDltQzBKQjBHenpPQXAyel9uTjhqSkV5Mml4U3ZqUUdxZzdBYVM5TlkxZmJCN25QUlJNeF94ZS1KX2kxNlpaU01lZnhHTmg?oc=5" target="_blank"&gt;Flughafen Frankfurt: Terminal 3 eröffnet – das sind die Auswirkungen für Reisende&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Main-Post&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNZGd3TmtqZ2c1SThzM0lFYVVtei03SWhFdzY2OG44Y2JlQl9jWC1rOTdXX3B6MVVVQjBzSkw4RjcwdTh0TUpYb2ZEMXNyNTUwOWZrNWM1ZXd3THI1ZHc3OUQyZWNpRW9yNnBsOGFHWXdWX1kxZV9adW9RTHlYZnp3R0ZoY01DZG5wUUNqdlAwR015SDltQzBKQjBHenpPQXAyel9uTjhqSkV5Mml4U3ZqUUdxZzdBYVM5TlkxZmJCN25QUlJNeF94ZS1KX2kxNlpaU01lZnhHTmg?oc=5</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>auto-709f671a5cb8</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: Pilot Operation for Digital Pickup Process - Logistik Heute</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxOaUg4M2xiVzZRMkhrNzI2cEhINTVIc2hrZXdROW9UNGpmT0dTck5pR2xmRWNvT1FuLXhkOGxyZG1FT2hLWlRNS3p2TWl0QlQtb3dtV3pOSGJKTU9mWmc2QW9fMHBTcWN2RWRDUWRRbGlnT2gweGpZQzRZSEpDYk56QzJPS1JVaVRaV3FnZm9pZnQ4TXVxX1dXb0JvYzR0aExjdEJHNw?oc=5" target="_blank"&gt;Frankfurt Airport: Pilot Operation for Digital Pickup Process&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Logistik Heute&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOaUg4M2xiVzZRMkhrNzI2cEhINTVIc2hrZXdROW9UNGpmT0dTck5pR2xmRWNvT1FuLXhkOGxyZG1FT2hLWlRNS3p2TWl0QlQtb3dtV3pOSGJKTU9mWmc2QW9fMHBTcWN2RWRDUWRRbGlnT2gweGpZQzRZSEpDYk56QzJPS1JVaVRaV3FnZm9pZnQ4TXVxX1dXb0JvYzR0aExjdEJHNw?oc=5</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>auto-9956729a35b3</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Infektionen am Frankfurter Flughafen: Vier Fälle von sogenannter Airport-Malaria bestätigt - Aviation.Direct</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxOTzJObEl0ZEotR21fOUVGREU5REFNZWxMRXdDX3BRaHhWd0xpY2YtSk9OZ09Hb2l4Ql93NDRwOUdTenZ2VGlZQVpaeDkxWGZOU2h0NnI4SGNLNFZEbzhveUpFRVZ5VjBDQmZJcUE0NmxPaHFpV1BBTUJMVkZtV1VCdU5ocmd5clZES29ENjRISm9UV3ZIb05wMGZKVzNHaHptaEpRcFZheGVDMUVCTldwRkRPc2Rqdw?oc=5" target="_blank"&gt;Infektionen am Frankfurter Flughafen: Vier Fälle von sogenannter Airport-Malaria bestätigt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Aviation.Direct&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTzJObEl0ZEotR21fOUVGREU5REFNZWxMRXdDX3BRaHhWd0xpY2YtSk9OZ09Hb2l4Ql93NDRwOUdTenZ2VGlZQVpaeDkxWGZOU2h0NnI4SGNLNFZEbzhveUpFRVZ5VjBDQmZJcUE0NmxPaHFpV1BBTUJMVkZtV1VCdU5ocmd5clZES29ENjRISm9UV3ZIb05wMGZKVzNHaHptaEpRcFZheGVDMUVCTldwRkRPc2Rqdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>auto-3936a0d71356</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>DLR - Frankfurt Airport - Deutsches Zentrum für Luft- und Raumfahrt</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiY0FVX3lxTE5sa19mblNuOTAxc2VITjNBX3o5dkh6VlF2RXRvc3VRSko0VmVUclZhY0UtNmVCNTFoV2p0eWZDVTdsOTZTV1J5NGlEUEFKRFpvbThhX25Hd0tkVWtndHRmRVFqSQ?oc=5" target="_blank"&gt;DLR - Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Deutsches Zentrum für Luft- und Raumfahrt&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5sa19mblNuOTAxc2VITjNBX3o5dkh6VlF2RXRvc3VRSko0VmVUclZhY0UtNmVCNTFoV2p0eWZDVTdsOTZTV1J5NGlEUEFKRFpvbThhX25Hd0tkVWtndHRmRVFqSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>auto-c8d23f36f690</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Ist das der witzigste Airport Deutschlands? - fnp.de</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxQTTlGZkpPU2NHVF9iM25KZ0xzRm1ZRzBJNTAySHhrcTlNWHllVVNzOWlKYWE1ZlBiOWxITUJ0azJlMDdhVmxsTG1nU3FDOXpuWEhoOUVod2kxNTNBZlpNbTRiUmh5dHVvNEFpTk0yS19tem1meXRibzVRMEstLTlRa1hselU4cU5OTng4c3VrQmpMUlBIOHlfQ25rOVFZZURCYUJaaA?oc=5" target="_blank"&gt;Flughafen Frankfurt: Ist das der witzigste Airport Deutschlands?&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQTTlGZkpPU2NHVF9iM25KZ0xzRm1ZRzBJNTAySHhrcTlNWHllVVNzOWlKYWE1ZlBiOWxITUJ0azJlMDdhVmxsTG1nU3FDOXpuWEhoOUVod2kxNTNBZlpNbTRiUmh5dHVvNEFpTk0yS19tem1meXRibzVRMEstLTlRa1hselU4cU5OTng4c3VrQmpMUlBIOHlfQ25rOVFZZURCYUJaaA?oc=5</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O166"/>
+  <dimension ref="A1:O176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10377,7 +10377,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10408,8 +10407,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>review</t>
@@ -10442,7 +10439,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10473,8 +10469,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>review</t>
@@ -10507,7 +10501,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10538,8 +10531,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>review</t>
@@ -10572,7 +10563,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10603,8 +10593,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>review</t>
@@ -10637,7 +10625,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10668,8 +10655,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>review</t>
@@ -10702,7 +10687,6 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10733,8 +10717,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
           <t>review</t>
@@ -10746,6 +10728,656 @@
         </is>
       </c>
       <c r="O166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>auto-b11a45b50e88</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Singapore Airlines erweitert Codeshare mit Lufthansa nach Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Singapore Airlines erweitert zum Winterflugplan 2026/27 die Codeshare-Partnerschaft mit Lufthansa. Ab 25. Oktober trägt die Verbindung Frankfurt–Kuala Lumpur zusätzlich SIA-Flugnummern. Lufthansa bedient die Strecke fünf Mal pro Woche mit Boeing 787-9, meldet das Portal Aero Routes.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/singapore-airlines-erweitert-codeshare-mit-lufthansa-nach-kuala-lumpur/jenjhg5</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>auto-1113dd0eeabb</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Air Asia X gibt Sydney auf und baut Melbourne und Perth aus</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Air Asia X stellt ihre Verbindung zwischen Sydney und Kuala Lumpur ein. Als Gründe nennt die Fluggesellschaft gestiegene Kosten, eine schwächere Nachfrage und eine Neuausrichtung von Flotte und Streckennetz. Die bislang auf der Route eingesetzten Airbus A330 sollen künftig auf anderen Verbindungen eingesetzt werden.</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-asia-x-gibt-sydney-auf-und-baut-melbourne-und-perth-aus/3m90cj4</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>auto-1551f059a3fe</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ein Drittel der weltweiten Urlaubsausgaben entfällt auf Europa</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Europa hat 2025 rund ein Drittel der weltweiten Ausgaben für Urlaubsreisen auf sich vereint. Nach Daten des World Travel &amp;amp; Tourism Council wurden in der Region zwei Billionen US-Dollar (rund 1,7 Billionen Euro) ausgegeben. Weltweit waren es 6,15 Billionen US-Dollar (rund 5,2 Billionen Euro), 3,5 Prozent mehr als im Vorjahr. Besonders Südeuropa profitiert von der Nachfrage. Für 2026 erwartet der WTTC in Europa ein Wachstum der Urlaubsausgaben um 3,7 Prozent, gegenüber 3,1 Prozent weltweit. Italien soll mit 4,7 Prozent am stärksten wachsen, gefolgt von Spanien mit 4,3 Prozent, der Türkei mit 4,1 Prozent und Frankreich mit 2,6 Prozent.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ein-drittel-der-weltweiten-urlaubsausgaben-entfaellt-auf-europa/xhed8d2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>auto-7aaf42f3d8cb</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Royal Jordanian und Air China planen engere Zusammenarbeit</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Royal Jordanian und Air China wollen ihre Zusammenarbeit ausbauen. Beide Fluggesellschaften unterzeichneten in Peking eine Absichtserklärung. Geprüft werden unter anderem Codeshare-Verbindungen sowie eine Zusammenarbeit bei Interline-Abkommen, Bodenabfertigung, Fracht und Catering. Dabei sollen die Drehkreuze Amman und Peking für zusätzliche Umsteigeverbindungen genutzt werden. Die Kooperation soll auch die geplante Aufnahme einer Direktverbindung zwischen den beiden Hauptstädten unterstützen.</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/royal-jordanian-und-air-china-planen-engere-zusammenarbeit/hy7p3y9</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>auto-ebb00b67d212</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: Partnership with Bangalore International Airport - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirgFBVV95cUxPUWp3aS1PMTJncXhTRmJ3eTRYQngxeGc4TVgxQkk2ZEE3OXp1SmI0RHdvbm1EbFdlamZ4YldaTl9NS3NmLXZ4YXMtWDl6dVNNblZwNGc2NjBoeEwyTE9WNUxvdElKdjlCS1RIdzRUS1Z1OGhpYWtCRW12c0VJVjV0Q2l3eUc5Nml4ZjdfOF9Ybm5VWXBQbzRoZWNpT01Pcm0zVXEwM0k4a2hYVkNNUXc?oc=5" target="_blank"&gt;Frankfurt Airport: Partnership with Bangalore International Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUWp3aS1PMTJncXhTRmJ3eTRYQngxeGc4TVgxQkk2ZEE3OXp1SmI0RHdvbm1EbFdlamZ4YldaTl9NS3NmLXZ4YXMtWDl6dVNNblZwNGc2NjBoeEwyTE9WNUxvdElKdjlCS1RIdzRUS1Z1OGhpYWtCRW12c0VJVjV0Q2l3eUc5Nml4ZjdfOF9Ybm5VWXBQbzRoZWNpT01Pcm0zVXEwM0k4a2hYVkNNUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>auto-5139a59a39b1</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Drei asiatische Airlines schicken Boeing 777 mit Sonderlackierung zum Start von Terminal 3 in Frankfurt - aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwgFBVV95cUxNNEl1QVoxcFpIalNzMk93M0JqNzNIWkZhNWZlMDJVY0U4YjRieG9hTFBJYXdTUXFTUDZJZVhxdGlhSXExUmlVc1NNOFdGaFpkTTJ6MEU2OGhic3c1d0Y1cnYwR3hvdXhVMHd6M25GY0pzazFmNFpXazBESGlLeDBFajVycE51VnNDY2hsVDhVSXlqdWpnWkVTX1luWGNYZUgzSnFOYkJsejZjakdJdDFqMml5QUpudzM3aE1YT2EyVWtUZw?oc=5" target="_blank"&gt;Drei asiatische Airlines schicken Boeing 777 mit Sonderlackierung zum Start von Terminal 3 in Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aeroTELEGRAPH&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNNEl1QVoxcFpIalNzMk93M0JqNzNIWkZhNWZlMDJVY0U4YjRieG9hTFBJYXdTUXFTUDZJZVhxdGlhSXExUmlVc1NNOFdGaFpkTTJ6MEU2OGhic3c1d0Y1cnYwR3hvdXhVMHd6M25GY0pzazFmNFpXazBESGlLeDBFajVycE51VnNDY2hsVDhVSXlqdWpnWkVTX1luWGNYZUgzSnFOYkJsejZjakdJdDFqMml5QUpudzM3aE1YT2EyVWtUZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>auto-742b1450cf00</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: DHL starts a new airfreight hall in Cargocity - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaWNTbHpGVU95LW02WmhrYXBEd1NHajhxZGtSSjdOQUpYNlNkU1NpTUYzRU1wR0d2OWtZSDhPVG9nUkJsWXc1UmZ2QlpnZjlISkxCLU4wem5EelQwX1ZPb1hzNmFCY2xITG1sR0JDZW5kaEFfOFROSGVkcjREdFlKeG5mNnRTVjQ1Ml9XT2xHWWc0ZU5tcUNIbERXSElKdmNtY3g2TXJqR1Vwdw?oc=5" target="_blank"&gt;Frankfurt Airport: DHL starts a new airfreight hall in Cargocity&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaWNTbHpGVU95LW02WmhrYXBEd1NHajhxZGtSSjdOQUpYNlNkU1NpTUYzRU1wR0d2OWtZSDhPVG9nUkJsWXc1UmZ2QlpnZjlISkxCLU4wem5EelQwX1ZPb1hzNmFCY2xITG1sR0JDZW5kaEFfOFROSGVkcjREdFlKeG5mNnRTVjQ1Ml9XT2xHWWc0ZU5tcUNIbERXSElKdmNtY3g2TXJqR1Vwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>auto-5bf79523383c</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Nah am Airport: Air France-KLM bezieht neue Büros in Frankfurt - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxQY0Vkb1h5azhXMFR3V1Jqc05VR0JxWmFOMHdsZzlxa1V2Y1lPbjZBcGdJamZrdFZicVNQcFVlZmlEVnRjZ1FZN29zeEVKcXRTOUc5OGwwOE42eXNUYnhGX005OFpuWWRXeTFKcWZZSTBaZm9uOEZxRE4xeF92akZLNXhHZ0p5WU0zejBMYnBFM3pibk5OMTExLVNRSV83ZmtNbDhpTDlNTTljZw?oc=5" target="_blank"&gt;Nah am Airport: Air France-KLM bezieht neue Büros in Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQY0Vkb1h5azhXMFR3V1Jqc05VR0JxWmFOMHdsZzlxa1V2Y1lPbjZBcGdJamZrdFZicVNQcFVlZmlEVnRjZ1FZN29zeEVKcXRTOUc5OGwwOE42eXNUYnhGX005OFpuWWRXeTFKcWZZSTBaZm9uOEZxRE4xeF92akZLNXhHZ0p5WU0zejBMYnBFM3pibk5OMTExLVNRSV83ZmtNbDhpTDlNTTljZw?oc=5</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>auto-1e7ee91709ab</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>United UA817 from San Francisco declared an emergency and diverted to Los Angeles - airlive</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwAFBVV95cUxPeGg2ZFNOb2NKM0lqY1JlNVgwZkZXSGxnc0ZZc093R3UyS2Vtay1OSXA4c3FoRWlqRE11M011VjljQzNjWFpEb1F4N1d5b0FhalQ2ckFyVEUzVXIxU0Y0a211MkVYUGdaVG51R1gwaVVjNE93UVNMMmU5OWZUSFFlR0htNmY4V0FEZjMxVE1TcUItZVg0LXJ5MDBXNXBJQUhVd1gzbkg0WVZwQzNqZzdjX3F4ZjBQbGJiSXo1dGVLNGs?oc=5" target="_blank"&gt;United UA817 from San Francisco declared an emergency and diverted to Los Angeles&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPeGg2ZFNOb2NKM0lqY1JlNVgwZkZXSGxnc0ZZc093R3UyS2Vtay1OSXA4c3FoRWlqRE11M011VjljQzNjWFpEb1F4N1d5b0FhalQ2ckFyVEUzVXIxU0Y0a211MkVYUGdaVG51R1gwaVVjNE93UVNMMmU5OWZUSFFlR0htNmY4V0FEZjMxVE1TcUItZVg0LXJ5MDBXNXBJQUhVd1gzbkg0WVZwQzNqZzdjX3F4ZjBQbGJiSXo1dGVLNGs?oc=5</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>auto-6ded02eb500d</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Air France Flight AF442 Paris to Rio Declares Emergency and Returns to CDG - Nomad Lawyer</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMilwFBVV95cUxOelRfSkFOQzVFa1RQb0Vwc1ZjN0FNRWJqcXVhU2puS2VqWU9oRmpORFNGX1ZhMDFqS2VLY1VXaTFxSVJ2cmVNWkJtb000cWwyRF9TRkl2clRMdXBvWW1xSllmai1OdmFHWmVBU0k4Ti0tczNXakxRNjVEUjBaYm9DcGo2b29ta1ZQOE1RaXhPeFl5aVhIMFQ0?oc=5" target="_blank"&gt;Air France Flight AF442 Paris to Rio Declares Emergency and Returns to CDG&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Nomad Lawyer&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOelRfSkFOQzVFa1RQb0Vwc1ZjN0FNRWJqcXVhU2puS2VqWU9oRmpORFNGX1ZhMDFqS2VLY1VXaTFxSVJ2cmVNWkJtb000cWwyRF9TRkl2clRMdXBvWW1xSllmai1OdmFHWmVBU0k4Ti0tczNXakxRNjVEUjBaYm9DcGo2b29ta1ZQOE1RaXhPeFl5aVhIMFQ0?oc=5</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:O184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10749,7 +10749,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10780,8 +10779,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
           <t>review</t>
@@ -10814,7 +10811,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10845,8 +10841,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>review</t>
@@ -10879,7 +10873,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10910,8 +10903,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
           <t>review</t>
@@ -10944,7 +10935,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -10975,8 +10965,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
           <t>review</t>
@@ -11009,7 +10997,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11040,8 +11027,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
           <t>review</t>
@@ -11074,7 +11059,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11105,8 +11089,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
           <t>review</t>
@@ -11139,7 +11121,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11170,8 +11151,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
           <t>review</t>
@@ -11204,7 +11183,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11235,8 +11213,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
           <t>review</t>
@@ -11269,7 +11245,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -11300,8 +11275,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
           <t>review</t>
@@ -11334,7 +11307,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11365,8 +11337,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
           <t>review</t>
@@ -11378,6 +11348,526 @@
         </is>
       </c>
       <c r="O176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>auto-e2decace5caa</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>UPS baut neue Luftfrachtzentren auf den Philippinen und in Hongkong</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>UPS investiert von 2024 bis 2028 mehr als zwei Milliarden US-Dollar (1,7 Milliarden Euro) in den Ausbau seines internationalen Logistikgeschäfts, seiner Healthcare-Sparte und seiner Supply-Chain-Lösungen. Geplant sind neue und erweiterte Standorte in Europa, Asien und Nordamerika.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ups-baut-neue-luftfrachtzentren-auf-den-philippinen-und-in-hongkong/k06z72p</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>auto-273671f9d833</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>175 Kilometer: United verbindet Los Angeles wieder mit Bakersfield</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>United Airlines fliegt nach zwölf Jahren wieder zwischen Los Angeles und Bakersfield in Kalifornien. Die am 11. August gestartete Verbindung wird einmal täglich von SkyWest Airlines unter der Marke United Express mit Embraer E175 bedient. Die nur rund 175 Kilometer lange Strecke gehört zu den kürzesten im US-Inlandsnetz von United. Mit Los Angeles bedient die Fluggesellschaft ab Bakersfield nun drei Ziele: Los Angeles, San Francisco und Denver.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/175-kilometer-united-verbindet-los-angeles-wieder-mit-bakersfield/g1pmxz1</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>auto-d96fd1569e0d</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Frankreichs Rekordmeister trägt jetzt Luftfahrt</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Toulouse ist Europas Rugby-Hochburg – und Europas Luftfahrtmetropole. Der Stade Toulousain bringt diese beiden Identitäten nun zusammen: Sein neues Heimtrikot ist von Flugzeugen, Aerodynamik und dem Luftfahrterbe der Stadt inspiriert.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/frankreichs-rekordmeister-traegt-jetzt-luftfahrt/jfkbehl</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>auto-dcc5616ecf5a</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Abra Group: Noch nicht entscheiden, welche Airline Embraer E195-E2 betrieben wird</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Die Abra Group hat noch nicht entschieden, welche ihrer Fluggesellschaften die bestellten Embraer E195-E2 betreiben wird. Nach Angaben des Mutterkonzerns von Gol und Avianca laufen jedoch bereits Vorbereitungen für die Pilotenausbildung. Auch eine mögliche Übernahme von Sky Airline könnte die Einsatzmöglichkeiten erweitern. Abra hatte im Mai fünf E195-E2 fest bestellt und sich Kaufrechte für weitere 45 Exemplare gesichert. Ausschlaggebend für die frühe Bestellung war unter anderem die Möglichkeit, vergleichsweise zeitnahe Lieferpositionen bei Embraer zu erhalten. Die Verteilung der Flugzeuge soll abhängig von Marktlage und Nachfrage näher am Liefertermin festgelegt werden.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/abra-group-noch-nicht-entscheiden-welche-airline-embraer-e195-e2-betrieben-wird/dkdym5v</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>auto-701ec6ed2217</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Flughafen Brüssel testet autonomen Elektro-Schlepper</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Am Flughafen Brüssel hat ein Praxistest mit einem autonomen Elektro-Schlepper für den Frachttransport begonnen. Das Fahrzeug soll Anhänger zwischen Lagerhallen und dem Vorfeld befördern. Nach Angaben des Flughafens ist es der erste Test dieser Art unter realen Bedingungen an einem belgischen Flughafen. Der Schlepper fährt auf vier festgelegten Routen, kann bis zu vier Anhänger ziehen und erreicht autonom maximal zwölf Kilometer pro Stunde. Navigation und Hinderniserkennung erfolgen über Satellitennavigation und Lasersensoren. Während der Tests bleibt ein geschulter Mitarbeiter an Bord und kann bei Bedarf eingreifen. Untersucht werden unter anderem Effizienz und Sicherheit der Technik.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-bruessel-testet-autonomen-elektro-schlepper/0979dk0</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>auto-3784d2b8b8fd</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Frankfurt ist Start-Airport: Condor bietet neuen Gepäckservice - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMWNjbl8yZVRKTVpHZWt2ZVQ5cDRpVkNGXzNrc1hBRDFqaFh2Vk5jam9oWVhIcFlucU9MVTlXa2ttUWU3NFgzWWhWV2R4NlhFaWRmZGV1MEE4cHEwcHExTkltaFJhV2JfWmM0bHZDYVBORHJqbm5CWE5SSDByWHFsbTdJenlEMlpRWWhBSkowS0F0TVFPY1U3LXZmTUNwbHJ1bV9kanRnMlBjQQ?oc=5" target="_blank"&gt;Frankfurt ist Start-Airport: Condor bietet neuen Gepäckservice&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMWNjbl8yZVRKTVpHZWt2ZVQ5cDRpVkNGXzNrc1hBRDFqaFh2Vk5jam9oWVhIcFlucU9MVTlXa2ttUWU3NFgzWWhWV2R4NlhFaWRmZGV1MEE4cHEwcHExTkltaFJhV2JfWmM0bHZDYVBORHJqbm5CWE5SSDByWHFsbTdJenlEMlpRWWhBSkowS0F0TVFPY1U3LXZmTUNwbHJ1bV9kanRnMlBjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>auto-7d52133975cd</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Spanish PM Pedro Sanchez’s plane makes emergency landing in Turkey - France 24</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxNTUFzbllBQkVtcjdpQXlpSmY0eE5tQVlkZktwZEs4WjduRmlFOXpxclBTTHdiRHBuUW9JbDExOHpKQ0RaNVNUdmhrMF81SVl2cy0xNFlKZjJUbEEtdjdsV1M4a1dyU282T0FoWUR1RkpJQkU3aEllX0FBMnJWOWlGVU5xRzFrQ2k3aXVWbVVJcmlnY0thWmdOd1RYX3hITnlENHg0bzZBS2tIOW5aWmNkeDdyMmxyUQ?oc=5" target="_blank"&gt;Spanish PM Pedro Sanchez’s plane makes emergency landing in Turkey&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;France 24&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNTUFzbllBQkVtcjdpQXlpSmY0eE5tQVlkZktwZEs4WjduRmlFOXpxclBTTHdiRHBuUW9JbDExOHpKQ0RaNVNUdmhrMF81SVl2cy0xNFlKZjJUbEEtdjdsV1M4a1dyU282T0FoWUR1RkpJQkU3aEllX0FBMnJWOWlGVU5xRzFrQ2k3aXVWbVVJcmlnY0thWmdOd1RYX3hITnlENHg0bzZBS2tIOW5aWmNkeDdyMmxyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>auto-2f90670e21ee</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Another Boeing 787 makes emergency landing with RAT deployed at LAX Airport - airlive</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiowFBVV95cUxOTUFzR25HSlRyMnFoVzRIUUtmdTl1RWJyOFdGRGxueENkVDdXc3ZRajNvX2N1MXdDWHYxR1prdndLOUY5U3V6TGVZYnhiQzNKMUk4WU1pdHc4STItZ05CZWxyQ0R0dnowNEFBdGFmN3Y3WkpSUWVOSTFKcnRxUEowRk4wdmF3aEpGZHRsb2NwWG02OHR0eERxVnhQb1BPRGk1VUtn?oc=5" target="_blank"&gt;Another Boeing 787 makes emergency landing with RAT deployed at LAX Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOTUFzR25HSlRyMnFoVzRIUUtmdTl1RWJyOFdGRGxueENkVDdXc3ZRajNvX2N1MXdDWHYxR1prdndLOUY5U3V6TGVZYnhiQzNKMUk4WU1pdHc4STItZ05CZWxyQ0R0dnowNEFBdGFmN3Y3WkpSUWVOSTFKcnRxUEowRk4wdmF3aEpGZHRsb2NwWG02OHR0eERxVnhQb1BPRGk1VUtn?oc=5</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O184"/>
+  <dimension ref="A1:O187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11369,7 +11369,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11400,8 +11399,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
           <t>review</t>
@@ -11434,7 +11431,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11465,8 +11461,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
           <t>review</t>
@@ -11499,7 +11493,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11530,8 +11523,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
           <t>review</t>
@@ -11564,7 +11555,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11595,8 +11585,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>review</t>
@@ -11629,7 +11617,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11660,8 +11647,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
           <t>review</t>
@@ -11694,7 +11679,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11725,8 +11709,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
           <t>review</t>
@@ -11759,7 +11741,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -11790,8 +11771,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
           <t>review</t>
@@ -11824,7 +11803,6 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -11855,8 +11833,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
           <t>review</t>
@@ -11868,6 +11844,201 @@
         </is>
       </c>
       <c r="O184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>auto-42ecc24ca48e</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Air Tahiti Nui investiert Millionen in neue Kabinen ihrer Boeing 787 - und Highspeed-Internet</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Air Tahiti Nui will ab 2028 die Kabinen ihrer vier Boeing 787 modernisieren. Das Projekt kostet 8,5 Milliarden CFP-Franc (rund 71 Millionen Euro) und soll über ein Darlehen Französisch-Polynesiens finanziert werden. Voraussetzung ist noch die Zustimmung der Versammlung, berichtet der Tv-Sender TNTV News.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-tahiti-nui-investiert-millionen-in-neue-kabinen-ihrer-boeing-787-und-highspeed/ep3dnk5</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>auto-3ac39acbe336</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>„Etwas ganz Besonderes“: Deutsche Airline nimmt neues Reiseziel ab Flughafen Frankfurt ins Visier - fnp.de</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxQMGV5WExycEVEcXZnakt4NHJUenBrUXJvSXc3SnNnUk9wSVdGaDJOek9aUkF2bXZINjNBYUR6eHBFdS16RnZ4U01DOFdaaGhsZF80Wjhvb0VRY3NxeV94QlNLTXg0ejdtdzdOdXRfelBtdXB0U0pfMVQwMzltVkp4NjJ5TXZOSjVhaW5RVGJmUmstazdfcU9WSW9zSEJSRHNnTlB6MDNKSFdZVjFL?oc=5" target="_blank"&gt;„Etwas ganz Besonderes“: Deutsche Airline nimmt neues Reiseziel ab Flughafen Frankfurt ins Visier&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQMGV5WExycEVEcXZnakt4NHJUenBrUXJvSXc3SnNnUk9wSVdGaDJOek9aUkF2bXZINjNBYUR6eHBFdS16RnZ4U01DOFdaaGhsZF80Wjhvb0VRY3NxeV94QlNLTXg0ejdtdzdOdXRfelBtdXB0U0pfMVQwMzltVkp4NjJ5TXZOSjVhaW5RVGJmUmstazdfcU9WSW9zSEJSRHNnTlB6MDNKSFdZVjFL?oc=5</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>auto-fe6a96068603</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Air France Boeing 777 Makes Emergency Landing After The Plane Turned Into a Sauna - PYOK</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixwFBVV95cUxNeE4zMlJPZzhQS0duLU5pdUJhMmZ6QUluYXM1dV9SUzYtWHFQUVdWN1VrdVBZRjRBbnVBeTAtQlpXVXBQU1NyLXJlaFdxc2dnOXYyUXd6Q3JzaXpNdV83TGRDaVNmTzhZak9KSmNoZ0RfaEIwWFpSdDRIcFowT0d2aWwtRkNkeUhfWjU3REFUQ25DeDY1aGc1RGE3czc1aTh1b1U2WERyekZzVm1MM1FWZzZKZUpPZUpjSWVUdE5FS1RIWEZrQzhV?oc=5" target="_blank"&gt;Air France Boeing 777 Makes Emergency Landing After The Plane Turned Into a Sauna&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;PYOK&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNeE4zMlJPZzhQS0duLU5pdUJhMmZ6QUluYXM1dV9SUzYtWHFQUVdWN1VrdVBZRjRBbnVBeTAtQlpXVXBQU1NyLXJlaFdxc2dnOXYyUXd6Q3JzaXpNdV83TGRDaVNmTzhZak9KSmNoZ0RfaEIwWFpSdDRIcFowT0d2aWwtRkNkeUhfWjU3REFUQ25DeDY1aGc1RGE3czc1aTh1b1U2WERyekZzVm1MM1FWZzZKZUpPZUpjSWVUdE5FS1RIWEZrQzhV?oc=5</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O187"/>
+  <dimension ref="A1:O195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11865,7 +11865,6 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11896,8 +11895,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
           <t>review</t>
@@ -11930,7 +11927,6 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -11961,8 +11957,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
           <t>review</t>
@@ -11995,7 +11989,6 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -12026,8 +12019,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
           <t>review</t>
@@ -12039,6 +12030,526 @@
         </is>
       </c>
       <c r="O187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>auto-5cc51a540813</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Boeing 787 von Lufthansa muss Flug nach Delhi abbrechen und landet in Baku</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Eine Boeing 787-9 von Lufthansa musste am Dienstag (25. August) auf dem Weg von Frankfurt nach Delhi außerplanmäßig in Baku landen. Flug LH760 war in rund 11.900 Metern Höhe über Turkmenistan unterwegs, als die über ADS-B übertragenen Positionsdaten des Flugzeugs mit dem Kennzeichen D-ABPH massiv fehlerhaft wurden, wie das Portal Aviation Herald berichtet. Zeitweise zeigten die Daten das Flugzeug sogar im Kaspischen Meer.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/boeing-787-von-lufthansa-muss-flug-nach-delhi-abbrechen-und-landet-in-baku/42g94ff</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>auto-109f850a0f23</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Frankreich erkennt Brustkrebs bei Flugbegleiterin als Berufskrankheit an</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Erstmals in Frankreich ist die Brustkrebserkrankung einer ehemaligen Flugbegleiterin als Berufskrankheit anerkannt worden. Ein Gericht in Bayonne entschied kürzlich zugunsten von Sophie Lainault, die von 1989 bis 2019 für Air France auf Langstrecken arbeitete, etwa die Hälfte davon nachts. 2019 wurde bei ihr Brustkrebs diagnostiziert. Die sberichtete zuerst die Nachrichtenagentur AFP.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/frankreich-erkennt-brustkrebs-bei-flugbegleiterin-als-berufskrankheit-an/4yt15dw</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>auto-594c3857e014</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Vini baut Angebot ab Bern mit täglichen Flügen aus - falls Nachfrage da ist</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Vini - ehemals Flyv oder Flybird - erweitert nach einer Testphase sein Angebot ab Bern. Die bisher drei Mal wöchentlich fest angebotene Verbindung nach München kann künftig für jeden Wochentag angefragt werden. Kommt genügend Nachfrage zusammen, setzt Vini einen zusätzlichen Flug an. Mit dem neuen Konzept Make It Fly können Reisende zudem Verbindungen zu neuen Zielen wie St. Tropez anstoßen.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/vini-baut-angebot-ab-bern-mit-taeglichen-fluegen-aus-falls-nachfrage-da-ist/hqst1wj</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>auto-c14876c9b32e</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Dassault baut die Super-Rafale – startklar ab 2034</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Mehr Sensoren, neues Radar, künstliche Intelligenz und eine unbemannte Begleitdrohne: Dassault treibt die Rafale F5 voran. Der neue Standard soll Frankreichs Kampfjet fit für die nächste Dekade machen – und auch bei der nuklearen Abschreckung eine zentrale Rolle spielen.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/verteidigung/dassault-baut-die-super-rafale-startklar-ab-2034/gschly7</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>auto-8882ebb14723</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Discover Airlines nimmt drei Ziele in Großbritannien auf</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Discover Airlines baut im Sommer 2027 ihr Kurzstreckenangebot aus und fliegt erstmals nach England und Schottland. Ab Frankfurt nimmt die Lufthansa-Tochter Bristol, Glasgow und Inverness ins Programm auf. Glasgow wird zusätzlich ab München bedient. Zum Einsatz kommen Airbus A320.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/discover-airlines-nimmt-drei-ziele-in-grossbritannien-auf/r4gdj56</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>auto-b436215186cc</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nepal verbietet Airlines Preiserhöhungen nach verheerenden Überschwemmungen</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Die nepalesische Luftfahrtbehörde CAAN hat die Fluggesellschaften des Landes angewiesen, ihre Ticketpreise trotz der gestiegenen Nachfrage infolge schwerer Überschwemmungen nicht zu erhöhen. Tickets sollen weiterhin unterhalb der zulässigen Höchsttarife angeboten werden und ausreichend verfügbar sein.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/nepal-verbietet-airlines-preiserhoehungen-nach-verheerenden-ueberschwemmungen/2dyb66p</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>auto-59ac7cecf22c</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Zwei Tote durch Malaria am Frankfurter Flughafen</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Mehrere Beschäftigte am Frankfurter Flughafen infizieren sich mit Malaria. Zwei von ihnen sterben an den Folgen der Infektion. Experten untersuchen nun, wie genau die Krankheit übertragen wurde.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53464/Mitarbeiter-des-Frankfurter-Flughafens-an-Malaria-gestorben.html</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>auto-20aee11a9d32</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Gran Canaria flight makes horror emergency landing after passenger dies onboard - The Mirror</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiigFBVV95cUxNaFhEZmxjQVJqNG9oX3gzS0pqY1BHREVXYXgzbTViVk5FdTlLTHRIeHNyd1IxMGZrMVQwMXBLajBCRFBsVktvRHQyS200cVkxRTVvcVRZakotOWRuTlRqaTdKNWRrYlhYaThmblhwZGVkbkVDSnloRHRWWmNfMmFvLWlrdWFqRWZJQ1HSAY8BQVVfeXFMTzVzRXpkaXdSdjltQk84eWNZVEVCX01uaEx5TGF4Nml0VUZBb0VzWXZEQXR6eHZKN2lqVGplakpwMHpoLU9JV09ocnRDQ2IwRkNUMU44anFEd0tjYWhMemFYd3p0MGhYcHNOY1F6d0hPeFJTazBWNTdLN1F6Znp1TVR0Rm9KTkhON0FhVkZudUk?oc=5" target="_blank"&gt;Gran Canaria flight makes horror emergency landing after passenger dies onboard&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Mirror&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNaFhEZmxjQVJqNG9oX3gzS0pqY1BHREVXYXgzbTViVk5FdTlLTHRIeHNyd1IxMGZrMVQwMXBLajBCRFBsVktvRHQyS200cVkxRTVvcVRZakotOWRuTlRqaTdKNWRrYlhYaThmblhwZGVkbkVDSnloRHRWWmNfMmFvLWlrdWFqRWZJQ1HSAY8BQVVfeXFMTzVzRXpkaXdSdjltQk84eWNZVEVCX01uaEx5TGF4Nml0VUZBb0VzWXZEQXR6eHZKN2lqVGplakpwMHpoLU9JV09ocnRDQ2IwRkNUMU44anFEd0tjYWhMemFYd3p0MGhYcHNOY1F6d0hPeFJTazBWNTdLN1F6Znp1TVR0Rm9KTkhON0FhVkZudUk?oc=5</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O195"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12051,7 +12051,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12082,8 +12081,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
           <t>review</t>
@@ -12116,7 +12113,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12147,8 +12143,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
           <t>review</t>
@@ -12181,7 +12175,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12212,8 +12205,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
           <t>review</t>
@@ -12246,7 +12237,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12277,8 +12267,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
           <t>review</t>
@@ -12311,7 +12299,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12342,8 +12329,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
           <t>review</t>
@@ -12376,7 +12361,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12407,8 +12391,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
           <t>review</t>
@@ -12441,7 +12423,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12472,8 +12453,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
           <t>review</t>
@@ -12506,7 +12485,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -12537,8 +12515,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
           <t>review</t>
@@ -12550,6 +12526,396 @@
         </is>
       </c>
       <c r="O195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>auto-fbe4720a09bd</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Flughafen Memmingen baut für zehn Millionen Euro aus</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Der Flughafen Memmingen investiert in diesem Jahr mehr als zehn Millionen Euro in seine Infrastruktur, wie der Airport am Freitag (28. August) mitteilt. Im Terminal wird derzeit das Obergeschoss ausgebaut, um zusätzliche Gates zu schaffen. Diese sollen insbesondere Reisenden aus dem Non-Schengen-Raum zugutekommen und in Spitzenzeiten für kürzere Wartezeiten sorgen. Die Arbeiten auf der Westseite sind bereits abgeschlossen, während im östlichen Bereich weitergebaut wird. Zudem wird das Vorfeld erweitert: Zwei neue, zu Fuß erreichbare Flugzeugstellplätze sollen die Leistungsfähigkeit erhöhen und weiteres Wachstum ermöglichen. Im Herbst ist außerdem der Bau eines neuen Turnpads geplant, der das Wenden von Flugzeugen an der Ostseite der Start- und Landebahn erleichtern soll. Für 2026 erwartet der Flughafen rund 3,8 Millionen Fluggäste nach 3,7 Millionen im Vorjahr.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flughafen-memmingen-baut-fuer-zehn-millionen-euro-aus/0bey5ft</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>auto-74a835498239</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Luftfrachtumschlag in Deutschland legt leicht zu</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Die Mitgliedsunternehmen des Verbands der Air Cargo Abfertiger Deutschlands (VACAD) haben im zweiten Quartal 2026 insgesamt 454.191 Tonnen Luftfracht abgefertigt. Das entspricht einem Plus von 2,4 Prozent gegenüber dem ersten Quartal und 1,7 Prozent gegenüber dem Vorjahreszeitraum, wie der Verband am Freitag (28. August) mitteilt.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/luftfrachtumschlag-in-deutschland-legt-leicht-zu/0wls70j</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>auto-bd4bc1db4184</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Air Europa feiert in Frankfurt ihr 40-jähriges Bestehen - und bereitet Start in Düsseldorf vor</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Die spanische Fluggesellschaft hat ihr 40-jähriges Firmenjubiläum mit einer Veranstaltung in Frankfurt gefeiert. Dazu waren zahlreiche Kunden und Partner aus Deutschland eingeladen.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-europa-feiert-in-frankfurt-ihr-40-jaehriges-bestehen-und-bereitet-start-in/qdfzr4j</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>auto-9e7909192da1</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Northeast Airlines soll mit Boeing 737 wiederauferstehen</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Bis 1972 flog im Nordosten der USA Northeast Airlines. Nun soll der Name an den Himmel zurückkehren - als Frachtfluggesellschaft mit Boeing 737-800.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/northeast-airlines-soll-mit-boeing-737-wiederauferstehen/n1cjn4w</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>auto-1ee7d7c89683</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Drohnen über kritischen Anlagen: Wie Sachsen reagiert</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DRESDEN - Mehr als ein Dutzend Drohnenüberflüge über kritischen Infrastrukturen wurden in Sachsen gemeldet. Welche Konsequenzen drohen und wie wird auf die neuen Sicherheitsrisiken reagiert?</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53473/Drohnen-ueber-kritischen-Anlagen-Wie-Sachsen-reagiert.html</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>auto-12a279f98d2b</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Emirates Flights Diverted as Seven UAE-Europe Routes Make Emergency Landings - thetraveler.org</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqAFBVV95cUxOcnpXY0FuZEd0Q0JUbjZOVUp5c3BiVE5EYjl3QXU3Z29Hdkp2U20td2xsN3NkeUl5QUVmTHdLUUtBYWZHVnZJMUktN0hfVHJsam9PTkxZQ29IRi1RVG1jeWo4M01mYzVNWEJ0SnQxYm15NVp6TmZuOV9adV9menpnZlJXd0ZNSk1lOHlhZWgwYXFtajh3RW5KOUxqZEE4YmNXaE1Qb1JHRHY?oc=5" target="_blank"&gt;Emirates Flights Diverted as Seven UAE-Europe Routes Make Emergency Landings&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;thetraveler.org&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOcnpXY0FuZEd0Q0JUbjZOVUp5c3BiVE5EYjl3QXU3Z29Hdkp2U20td2xsN3NkeUl5QUVmTHdLUUtBYWZHVnZJMUktN0hfVHJsam9PTkxZQ29IRi1RVG1jeWo4M01mYzVNWEJ0SnQxYm15NVp6TmZuOV9adV9menpnZlJXd0ZNSk1lOHlhZWgwYXFtajh3RW5KOUxqZEE4YmNXaE1Qb1JHRHY?oc=5</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12547,7 +12547,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12578,8 +12577,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
           <t>review</t>
@@ -12612,7 +12609,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12643,8 +12639,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
           <t>review</t>
@@ -12677,7 +12671,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12708,8 +12701,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
           <t>review</t>
@@ -12742,7 +12733,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12773,8 +12763,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
           <t>review</t>
@@ -12807,7 +12795,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12838,8 +12825,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
           <t>review</t>
@@ -12872,7 +12857,6 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -12903,8 +12887,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
           <t>review</t>
@@ -12916,6 +12898,136 @@
         </is>
       </c>
       <c r="O201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>auto-2e41cb0c1e5b</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Frankfurt: Hunderte Komparsen testen neues Airport-Terminal - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxPb0pHLTd4VXA4MEZQZTVRaDVnakNiM1hHSnpPSXI0U0N3SmktMVRvMjlVWGJJWHlpbmpLVTlCSXBMTzhPaVo4SlRIME5mT3Zxa1FFY1dzdk5XWEZyVmhSdnVTSjN5bm9RVHdyRG93eUF1UnlTeDJvbEpJRURBWXdQelZUdVRyajlRZjAwYkMzS0lCYncyNjgzT2ZFR19iZm1id281bQ?oc=5" target="_blank"&gt;Frankfurt: Hunderte Komparsen testen neues Airport-Terminal&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPb0pHLTd4VXA4MEZQZTVRaDVnakNiM1hHSnpPSXI0U0N3SmktMVRvMjlVWGJJWHlpbmpLVTlCSXBMTzhPaVo4SlRIME5mT3Zxa1FFY1dzdk5XWEZyVmhSdnVTSjN5bm9RVHdyRG93eUF1UnlTeDJvbEpJRURBWXdQelZUdVRyajlRZjAwYkMzS0lCYncyNjgzT2ZFR19iZm1id281bQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>auto-bbaed6f067b3</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Emergency: United Boeing 767 to Newark dumped fuel before diversion to London Heathrow - airlive</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMixgFBVV95cUxOM1hyNTFBTFZnb0laYUVwNDhpZnFaemtDZHRERldQQlFfOGN4Vjk3ejRrc3lDcDhNZGFXUktJbW1Jamh4OENTR2VyYllKeTA3eXVfNVJWcEdBNFQ4TmVYMUtwZkpVYWotQ1dxNndhSTF6ZnRnSmxkZi03UjZzUFBrNndydUZWM18zOEJzTC1jd3dPSnRsZ19lVTV6cUVjUHctbHRIMmt2N0tSSkdXRHpER005ZTNxSEIwUVUzV3huYVNUNWNOUHc?oc=5" target="_blank"&gt;Emergency: United Boeing 767 to Newark dumped fuel before diversion to London Heathrow&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM1hyNTFBTFZnb0laYUVwNDhpZnFaemtDZHRERldQQlFfOGN4Vjk3ejRrc3lDcDhNZGFXUktJbW1Jamh4OENTR2VyYllKeTA3eXVfNVJWcEdBNFQ4TmVYMUtwZkpVYWotQ1dxNndhSTF6ZnRnSmxkZi03UjZzUFBrNndydUZWM18zOEJzTC1jd3dPSnRsZ19lVTV6cUVjUHctbHRIMmt2N0tSSkdXRHpER005ZTNxSEIwUVUzV3huYVNUNWNOUHc?oc=5</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O203"/>
+  <dimension ref="A1:O205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12919,7 +12919,6 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -12950,8 +12949,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
           <t>review</t>
@@ -12984,7 +12981,6 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -13015,8 +13011,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
           <t>review</t>
@@ -13028,6 +13022,136 @@
         </is>
       </c>
       <c r="O203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>auto-b7807f06b32e</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Dampf in Bordküche von Boeing 737 zwingt Eurowings-Flug zur Landung in Paris</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ein Flug von Eurowings von Köln nach Palma de Mallorca ist am Samstagabend (29. August) außerplanmäßig in Paris-Charles de Gaulle gelandet. Nach Angaben der Fluggesellschaft kam es in der hinteren Bordküche zu einer Dampfentwicklung, wie der TV-Sender RTL berichtet. Die Besatzung von Flug EW590 setzte daraufhin das Notsignal 7700 ab und entschied sich zur Landung in der französishen Haupstadt.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/dampf-in-bordkueche-von-boeing-737-zwingt-eurowings-flug-zur-landung-in-paris/dnx5sdc</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>auto-8e7c2ffd8edd</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Jet2 flight LS1473 made a U-turn over France after pilots declared an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMivgFBVV95cUxQREZDdER4STdyY2dSZk5IZ0NEeVJXelcxSjF1ZXJoYW52ZWx6UWxLYTN0cW5NUkIydHNHZGZUTFpCb0k1SGlWVU1LV0RaUk5pSnJsZWNnbmR4ekQ4YlV1UjdsVUh4SXhXcmxRNl95MUEzVUNZTUhsWWdXdms2aXlBVWMwLTZPTzNudVpxZkZGLUpaM1FoXzBXdF9FSXZyd0hwUS1jUkNlOW5FdXZZTTM3cEFfTzZDdXU2eTZvekZB?oc=5" target="_blank"&gt;Jet2 flight LS1473 made a U-turn over France after pilots declared an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQREZDdER4STdyY2dSZk5IZ0NEeVJXelcxSjF1ZXJoYW52ZWx6UWxLYTN0cW5NUkIydHNHZGZUTFpCb0k1SGlWVU1LV0RaUk5pSnJsZWNnbmR4ekQ4YlV1UjdsVUh4SXhXcmxRNl95MUEzVUNZTUhsWWdXdms2aXlBVWMwLTZPTzNudVpxZkZGLUpaM1FoXzBXdF9FSXZyd0hwUS1jUkNlOW5FdXZZTTM3cEFfTzZDdXU2eTZvekZB?oc=5</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O205"/>
+  <dimension ref="A1:O211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13043,7 +13043,6 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -13074,8 +13073,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
           <t>review</t>
@@ -13108,7 +13105,6 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13139,8 +13135,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
           <t>review</t>
@@ -13152,6 +13146,396 @@
         </is>
       </c>
       <c r="O205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>auto-f21970e068ea</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Lot übernimmt zwei Boeing 787-9 von Virgin Atlantic</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Lot Polish Airlines will zwei gebrauchte Boeing 787-9 von Virgin Atlantic übernehmen. Die beiden Dreamliner sollen in der ersten Hälfte des kommenden Jahres zur Flotte stoßen. Ihre Kabinen werden aufgefrischt, eine vollständige Neukonfiguration ist jedoch nicht vorgesehen, berichtet das Portal &lt;a href="https://www.pasazer.com/news/470681/lot,pozyska,dwa,dreamlinery,787,9,od,virgin,atlantic.html#google_vignette" id="05332972-fcb0-4fd4-ab5b-378cdb62b28f" data-link-role-code="target_blank"&gt;Pasazer&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lot-uebernimmt-zwei-boeing-787-9-von-virgin-atlantic/cnr0vys</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>auto-6c7b4f2d7406</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Flüge zwischen Linz und Frankfurt bleiben ziemlich leer</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Nach dem Rückzug von Austrian Airlines übernahm DAT Danish Air Transport die Strecke Linz - Frankfurt. Doch die erhoffte Auslastung von 60 Prozent erreicht die Fluggesellschaft bei weitem nicht, wie eine aktuelle Auswertung zeigt.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/fluege-zwischen-linz-und-frankfurt-bleiben-ziemlich-leer/ymv4c00</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>auto-eec7031d0c15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Condor-Chef rechnet mit weiter hohen Kerosinpreisen</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Flugpassagiere müssen sich auf weiter steigende Ticketpreise einrichten. "Fliegen wird für alle teurer", sagte Condor-Chef Peter Gerber bei einer Luftverkehrsveranstaltung in Frankfurt. Für das kommende Jahr rechne er wegen der weiterhin angespannten Lage am Persischen Golf nicht mit sinkenden Kerosinpreisen.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53496/Condor-Chef-rechnet-mit-weiter-hohen-Kerosinpreisen.html</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>auto-1afcd83ba91c</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TAP rutscht vor Teilprivatisierung tiefer in die roten Zahlen</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>LISSABON - TAP Air Portugal meldet vor der Teilprivatisierung an Lufthansa oder Air France-KLM einen Rekordumsatz. Gestiegene Treibstoffkosten setzen die portugiesische Fluggesellschaft aber unter Druck - TAP hat das erste Geschäftshalbjahr 2026 mit fast 100 Millionen Euro Verlust abgeschlossen.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53495/TAP-rutscht-vor-Teilprivatisierung-tiefer-in-die-roten-Zahlen.html</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>auto-03a4dfd362fe</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Boeing 787-9 von Lufthansa landet ungeplant in Baku</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Crew und Passagiere einer Boeing 787-9 von Lufthansa verbringen nach einer ungeplanten Landung einen Tag in Baku. Das ist passiert.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53492/Boeing-787-9-von-Lufthansa-landet-ungeplant-in-Baku.html</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>auto-e39566615727</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Air France flight AF566 to Beirut turned around and declared an emergency - airlive</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxQX2pSbEUxLVN3QUxrb1AyOVJrUmY3YW9QcjhpSnJiX3k2YUhmSFFkUVdIRjkzaEIxcTBvRFJtZFpaR2Zoa1l4SXlLQ0hXNTJNTHVjNFlwUU4za1NuVE9ydnBnRXdSVzRORWl4dVB5QzdmV3Y5N0U1V1QwN0oxcnNxS1gzTzkzNE1FZVpmeWxzV04xeDJmWlRQYTJWd1VFaF9ybnBfbGVSbHdXcWQ1eXQ2MW81YWxNdw?oc=5" target="_blank"&gt;Air France flight AF566 to Beirut turned around and declared an emergency&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQX2pSbEUxLVN3QUxrb1AyOVJrUmY3YW9QcjhpSnJiX3k2YUhmSFFkUVdIRjkzaEIxcTBvRFJtZFpaR2Zoa1l4SXlLQ0hXNTJNTHVjNFlwUU4za1NuVE9ydnBnRXdSVzRORWl4dVB5QzdmV3Y5N0U1V1QwN0oxcnNxS1gzTzkzNE1FZVpmeWxzV04xeDJmWlRQYTJWd1VFaF9ybnBfbGVSbHdXcWQ1eXQ2MW81YWxNdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O211"/>
+  <dimension ref="A1:O218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13167,7 +13167,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -13198,8 +13197,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
           <t>review</t>
@@ -13232,7 +13229,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13263,8 +13259,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
           <t>review</t>
@@ -13297,7 +13291,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13328,8 +13321,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
           <t>review</t>
@@ -13362,7 +13353,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13393,8 +13383,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
           <t>review</t>
@@ -13427,7 +13415,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13458,8 +13445,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
           <t>review</t>
@@ -13492,7 +13477,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13523,8 +13507,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
           <t>review</t>
@@ -13536,6 +13518,461 @@
         </is>
       </c>
       <c r="O211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>auto-443003dce4d1</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ANA All Nippon Airways und Lufthansa Group bieten wieder kostenlose Inlandsflüge in Japan an</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ANA All Nippon Airways und Lufthansa Group legen ihr Angebot für kostenlose Inlandsflüge in Japan neu auf. Reisende aus Deutschland, Österreich und anderen europäischen Ländern können bei Buchungen vom 1. bis 30. September 2026 bis zu zwei ANA-Inlandsflüge ohne zusätzliche Flugkosten zu ihrer Japan-Reise hinzufügen. Die Aktion gilt für Reisen vom 1. Dezember 2026 bis 28. Februar 2027.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/ana-all-nippon-airways-und-lufthansa-group-bieten-wieder-kostenlose-inlandsfluege-in/5hylww9</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>auto-9d611711de61</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Russische Frachtairline startet neuen Comeback-Versuch</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Nach jahrelanger Sanktionspause und einem gescheiterten Comeback mit betagten Antonov An-12 unternimmt die russische Frachtairline Atran Airlines einen neuen Anlauf. Noch in diesem Jahr will sie wieder abheben - mit Boeing 737.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/atran-airlines-plant-comeback-neustart-mit-boeing-737/q062jek</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>auto-400857ea6bbd</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Flugbranche warnt vor Chaos bei Schengen-Einreisen</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die Luftverkehrsbranche hat vor einem drohenden Chaos bei der Einreise in den Schengenraum gewarnt. Die zum 6. September auslaufenden Ausnahmeregeln der EU müssten dringend verlängert werden, verlangen Vertreter des Frankfurter Flughafens, der Airlines Lufthansa und Condor sowie des Flughafenverbands ADV.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53504/Flugbranche-warnt-vor-Chaos-bei-Schengen-Einreisen.html</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>auto-aab5657bf612</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Lufthansa hat wieder Chance auf DAX-Rückkehr</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa will seit Jahren zurück in die erste Börsenliga. Im September hat der Konzern eine neue Aufstiegschance vom MDAX in den DAX.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53502/Lufthansa-hat-wieder-Chance-auf-DAX-Rueckkehr.html</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>auto-47905953aead</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Srilankan Airlines legt Zusatzflug nach Frankfurt auf - airliners.de</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMigAFBVV95cUxOLTRhcXM2VnRvSkFoWnoyWFFqN2RKYjVDaEFhRzBkWXVkVlQzQ1ptdnpsY3pQNWpDTjNDelJBSlUzWDRSS1h3WUhBT01OOVZlV2NuYzQ2MTlGdkJ5ak9Uc01YNXVkMTlwMUY1eDhYbzAxaWtGZ1lKd0lTeHNBa0ZGMg?oc=5" target="_blank"&gt;Srilankan Airlines legt Zusatzflug nach Frankfurt auf&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airliners.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOLTRhcXM2VnRvSkFoWnoyWFFqN2RKYjVDaEFhRzBkWXVkVlQzQ1ptdnpsY3pQNWpDTjNDelJBSlUzWDRSS1h3WUhBT01OOVZlV2NuYzQ2MTlGdkJ5ak9Uc01YNXVkMTlwMUY1eDhYbzAxaWtGZ1lKd0lTeHNBa0ZGMg?oc=5</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>auto-5cb51d878cf2</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Medical issue forces Ryanair Dublin bound flight into emergency landing - Irish Mirror</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikAFBVV95cUxPbFNYeGFFSVZKYVVZTVEtMUlYT000Qzc5SGdUSUg3azY0cXQxZWRWdk9ZbGVpcjF2Z0pJbWdjWjRMYi1HX2dweTFGOVRMbjlfckJUZkdXMzRNOTVYTWpjOUdxNG8wWUNNUThPZ0phUk9fZnhsMnNSbXdEQ3hXMG92V2N3VjQwNUIxdW5lU1o2dnLSAZYBQVVfeXFMUDNzbXlTeFZVa2o1bFRUNHdQZWtZQnpDeTlOdjhCcUZEeWpPSHZKVk82OTVxZ0h4bXJnUWw0RXNqS250OHRFZ2RQMTNhVnR6ZFViZkFodUZFTWFidGhLZ3pkVlFkcG9aQnVVVDZxSEh6OFZud1F6V2hWVlhPNHlmczdVTHRqYVpUTjdxcS1QRloxWmZxY29R?oc=5" target="_blank"&gt;Medical issue forces Ryanair Dublin bound flight into emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Irish Mirror&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbFNYeGFFSVZKYVVZTVEtMUlYT000Qzc5SGdUSUg3azY0cXQxZWRWdk9ZbGVpcjF2Z0pJbWdjWjRMYi1HX2dweTFGOVRMbjlfckJUZkdXMzRNOTVYTWpjOUdxNG8wWUNNUThPZ0phUk9fZnhsMnNSbXdEQ3hXMG92V2N3VjQwNUIxdW5lU1o2dnLSAZYBQVVfeXFMUDNzbXlTeFZVa2o1bFRUNHdQZWtZQnpDeTlOdjhCcUZEeWpPSHZKVk82OTVxZ0h4bXJnUWw0RXNqS250OHRFZ2RQMTNhVnR6ZFViZkFodUZFTWFidGhLZ3pkVlFkcG9aQnVVVDZxSEh6OFZud1F6V2hWVlhPNHlmczdVTHRqYVpUTjdxcS1QRloxWmZxY29R?oc=5</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>auto-c59fd99aa8dc</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Help! Delta Deserted Us After an Emergency Landing in the Azores. (Published 2025) - The New York Times</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxNaWhLSEQ4NnFhTlVCU3hsb2xlMWdqV3gzSUYzSlhLLUw0aVRpN2hfTFVqTlh3UklLVm1tb3ZyTENMX0VrbUhaZWRtOWVKampPcUhobENKSlRCVnBYdVpCdHltZEVkMlpSdU9XTjRSUFBhUGdWejl3UjhjSGIzWGVvUy1CazhOR3kzaE1CQ2NHNzU5aHJrN3k0b2QzcGhNekFOcEE?oc=5" target="_blank"&gt;Help! Delta Deserted Us After an Emergency Landing in the Azores. (Published 2025)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The New York Times&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaWhLSEQ4NnFhTlVCU3hsb2xlMWdqV3gzSUYzSlhLLUw0aVRpN2hfTFVqTlh3UklLVm1tb3ZyTENMX0VrbUhaZWRtOWVKampPcUhobENKSlRCVnBYdVpCdHltZEVkMlpSdU9XTjRSUFBhUGdWejl3UjhjSGIzWGVvUy1CazhOR3kzaE1CQ2NHNzU5aHJrN3k0b2QzcGhNekFOcEE?oc=5</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O218"/>
+  <dimension ref="A1:O226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13539,7 +13539,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13570,8 +13569,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
           <t>review</t>
@@ -13604,7 +13601,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13635,8 +13631,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
           <t>review</t>
@@ -13669,7 +13663,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13700,8 +13693,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
           <t>review</t>
@@ -13734,7 +13725,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13765,8 +13755,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
           <t>review</t>
@@ -13799,7 +13787,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -13830,8 +13817,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
           <t>review</t>
@@ -13864,7 +13849,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -13895,8 +13879,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
           <t>review</t>
@@ -13929,7 +13911,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -13960,8 +13941,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
           <t>review</t>
@@ -13973,6 +13952,526 @@
         </is>
       </c>
       <c r="O218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>auto-a666348dbf1b</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Jetzt wählt Portugal zwischen Lufthansa Group und Air France-KLM</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Lufthansa Group und Air France-KLM wollen 44,9 Prozent von Tap Air Portugal übernehmen. Die staatliche Beteiligungsholding hat beide Angebote geprüft und ihre Einschätzung an die Regierung weitergeleitet. Nun steht in Lissabon die Entscheidung an.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/lufthansa-und-air-france-klm-jetzt-wird-es-ernst-beim-bieterkampf-um-tap-air-portugal/ltnnsr1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>auto-69aac600d07e</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Lufthansa schließt AirRail-Terminal</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa schließt das "AirRail-Terminal" am Frankfurter Flughafen. Das ändert sich für Passagiere mit Bahnanreise.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53518/Lufthansa-schliesst-AirRail-Terminal.html</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>auto-df7349042098</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Ab 31. März: Diese Airline fliegt bald zweimal wöchentlich nach Frankfurt - fnp.de</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipwFBVV95cUxOTlBDMWc3aGtKQ0ZKNjZIeS1vdVFiRGpTanJ6QXZ2VGNJTnBNWDF3VmxQdm4wMEREV0VqMk1Jdmx0N2RaMVFDaUoweXNWNVVNYkhVWXFhaGU0ZnFQLXVfWnViOVl1V3Z4MHVYLWQ2WjhUYVhSdUYySnVrTUoyWi1wb09jYlF4S203R2RxeTk2alhvSlczYU9JYUtzTFk3VmpEd0JEY0E4Zw?oc=5" target="_blank"&gt;Ab 31. März: Diese Airline fliegt bald zweimal wöchentlich nach Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOTlBDMWc3aGtKQ0ZKNjZIeS1vdVFiRGpTanJ6QXZ2VGNJTnBNWDF3VmxQdm4wMEREV0VqMk1Jdmx0N2RaMVFDaUoweXNWNVVNYkhVWXFhaGU0ZnFQLXVfWnViOVl1V3Z4MHVYLWQ2WjhUYVhSdUYySnVrTUoyWi1wb09jYlF4S203R2RxeTk2alhvSlczYU9JYUtzTFk3VmpEd0JEY0E4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>auto-19003a1a9ccc</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Frankfurt: Lufthansa Cargo launches Globecross for cross-border logistics - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitwFBVV95cUxQbS1NU3U0NDFvaXF5SzZBSnhvejJfN2VSOTZabEJDN1lkUUFXT096VVNpTExqSFhPOFQ3TC1PcUZHalRneWlTS0JIV2Y2alVaWFB5RkJrZ2xyYU9CaW1Iall4WGJaUmRUNWRhRTlTV1pQcElJblpIaGY0aDBsb3docW9IRF93NHY1emVKeWpFd0JaMVhkZzFOTzR3bkRiWk1EM040Y3kxY21tdElXeUtYUkVSek5NOGM?oc=5" target="_blank"&gt;Frankfurt: Lufthansa Cargo launches Globecross for cross-border logistics&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQbS1NU3U0NDFvaXF5SzZBSnhvejJfN2VSOTZabEJDN1lkUUFXT096VVNpTExqSFhPOFQ3TC1PcUZHalRneWlTS0JIV2Y2alVaWFB5RkJrZ2xyYU9CaW1Iall4WGJaUmRUNWRhRTlTV1pQcElJblpIaGY0aDBsb3docW9IRF93NHY1emVKeWpFd0JaMVhkZzFOTzR3bkRiWk1EM040Y3kxY21tdElXeUtYUkVSek5NOGM?oc=5</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>auto-8646dec215d6</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Air France fliegt seit 75 Jahren ab Frankfurt - Airportzentrale</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiwFBVV95cUxNczc4TEU2OXBuY0FjUFU4aXRUNm1BenlaRkRfcFFsSXlvYlBaT1JFNlBORlM2OGFhMmJ2RmZqT2o1d1hxcjZQenh3RnZONU1KRjdBWnlDYjZoWjJleTJaYjFnYjhwSU9UM1EtU2NoelZ2QnRtYlZGUk5lX0c0RFNJWXZ6dmpUUlpldWhz?oc=5" target="_blank"&gt;Air France fliegt seit 75 Jahren ab Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airportzentrale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNczc4TEU2OXBuY0FjUFU4aXRUNm1BenlaRkRfcFFsSXlvYlBaT1JFNlBORlM2OGFhMmJ2RmZqT2o1d1hxcjZQenh3RnZONU1KRjdBWnlDYjZoWjJleTJaYjFnYjhwSU9UM1EtU2NoelZ2QnRtYlZGUk5lX0c0RFNJWXZ6dmpUUlpldWhz?oc=5</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>auto-9311cebf67c5</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Mehr United Flüge ab Frankfurt - Fliegerweb</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbmdkcnh6SXAwSnZEMUMxZi15WU5lNm42bFRVd0puVkRubnR4dVRXU050LTFYQzhHVXliaWhLOWx0VklfNWpKOGpwS2xrUG5QNUFoTGRSQjlQbmhaaENlWnJ4aWFQRkFPdTVaam94aUV4QUNxOU5rbllCN0F3QmZseTR6R0RqT2tL?oc=5" target="_blank"&gt;Mehr United Flüge ab Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fliegerweb&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbmdkcnh6SXAwSnZEMUMxZi15WU5lNm42bFRVd0puVkRubnR4dVRXU050LTFYQzhHVXliaWhLOWx0VklfNWpKOGpwS2xrUG5QNUFoTGRSQjlQbmhaaENlWnJ4aWFQRkFPdTVaam94aUV4QUNxOU5rbllCN0F3QmZseTR6R0RqT2tL?oc=5</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>auto-9b881e80ad14</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>A flight from Japan was ordered to perform a go around at Frankfurt because it was arriving too early - airlive</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1AFBVV95cUxPYjVmTWdLUWJ6T2Qzc1d1RDhNSHJaWWJlbld2OHhwLUF3Vm1uVDgtbWVKS1pMaXlackVfZ2lfNlRuaC1GVFcyY0lIUmZXeHZKeXF1V3NfVGc3eDlFMjNuUVVoVXNIbXU3YVV2eHBiX2FQNkt4eU8wd2xDeTBCekdCNTFKZzJvVnVNM29MTkY5XzBIajJvV1IycW5NX0E3cERZUy1HZUNVTGtwN2xkQmlXeWdVZUZ1bTQtQ2dsc1kyYUt6eUt4eTdmeEJDUkFBUnFjY2JEXw?oc=5" target="_blank"&gt;A flight from Japan was ordered to perform a go around at Frankfurt because it was arriving too early&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airlive&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPYjVmTWdLUWJ6T2Qzc1d1RDhNSHJaWWJlbld2OHhwLUF3Vm1uVDgtbWVKS1pMaXlackVfZ2lfNlRuaC1GVFcyY0lIUmZXeHZKeXF1V3NfVGc3eDlFMjNuUVVoVXNIbXU3YVV2eHBiX2FQNkt4eU8wd2xDeTBCekdCNTFKZzJvVnVNM29MTkY5XzBIajJvV1IycW5NX0E3cERZUy1HZUNVTGtwN2xkQmlXeWdVZUZ1bTQtQ2dsc1kyYUt6eUt4eTdmeEJDUkFBUnFjY2JEXw?oc=5</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>auto-7d1d57b5ea19</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Mid-air chaos as Swiss Air flight forced into emergency landing after smoke fills cabin - express.co.uk</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxPSElnTnF2TG9xTWk5Qm9uU3NNNENNNEFrSEZabmZNZmhKYmtiN2NvM3Fwc2VyYVBoSWs2b2lIX0d0N0J1UkhmNE5lWVRhR05BaF9zb0ljV2FpMFRQNHFCOEFnZHlnSUxEVE5LNlE4YXdEV0g3N2g0V1ZtZERPZThHWDRCTkxtYjdCRzdlLTRXTEgzLXVxS21OU9IBngFBVV95cUxNdHQxdXM2SVNlMWFRRDItcEZQbWxOc2p3N0tZUFQ1MldBSjB2NEFPNDVqeGFFNGVnOEs5ckFuN3p3VjVwLVF5T0tXQWdhWTdZOU03d09leEhUQmFvYmFUTFpjdk56VG1xZTF1X2hPbzVCNDFrLWdrOW1aZEJNZFNhbTdKWnhxd3pBWlEtTS14bkRQcko5TzFHOTV2TVR6Zw?oc=5" target="_blank"&gt;Mid-air chaos as Swiss Air flight forced into emergency landing after smoke fills cabin&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;express.co.uk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSElnTnF2TG9xTWk5Qm9uU3NNNENNNEFrSEZabmZNZmhKYmtiN2NvM3Fwc2VyYVBoSWs2b2lIX0d0N0J1UkhmNE5lWVRhR05BaF9zb0ljV2FpMFRQNHFCOEFnZHlnSUxEVE5LNlE4YXdEV0g3N2g0V1ZtZERPZThHWDRCTkxtYjdCRzdlLTRXTEgzLXVxS21OU9IBngFBVV95cUxNdHQxdXM2SVNlMWFRRDItcEZQbWxOc2p3N0tZUFQ1MldBSjB2NEFPNDVqeGFFNGVnOEs5ckFuN3p3VjVwLVF5T0tXQWdhWTdZOU03d09leEhUQmFvYmFUTFpjdk56VG1xZTF1X2hPbzVCNDFrLWdrOW1aZEJNZFNhbTdKWnhxd3pBWlEtTS14bkRQcko5TzFHOTV2TVR6Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O226"/>
+  <dimension ref="A1:O246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13973,7 +13973,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14004,8 +14003,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
           <t>review</t>
@@ -14038,7 +14035,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14069,8 +14065,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
           <t>review</t>
@@ -14103,7 +14097,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14134,8 +14127,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>review</t>
@@ -14168,7 +14159,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14199,8 +14189,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>review</t>
@@ -14233,7 +14221,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14264,8 +14251,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>review</t>
@@ -14298,7 +14283,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14329,8 +14313,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>review</t>
@@ -14363,7 +14345,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14394,8 +14375,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>review</t>
@@ -14428,7 +14407,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -14459,8 +14437,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>review</t>
@@ -14472,6 +14448,1306 @@
         </is>
       </c>
       <c r="O226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>auto-7f2bbebcf134</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Brasiliens Luftfahrtbehörde groundet Total Linhas Aéreas</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Die brasilianische Luftfahrtbehörde Anac hat das Luftverkehrsbetreiberzeugnis von Total Linhas Aéreas vollständig suspendiert. Die vor allem im Fracht- und Posttransport tätige Fluggesellschaft darf damit bis auf Weiteres keine Flüge durchführen. Grund sind nach Angaben der Behörde erhebliche Defizite bei der Betriebssicherheit.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/brasiliens-luftfahrtbehoerde-groundet-total-linhas-aereas/yvdn941</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>auto-2ad8e088cbac</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Etihad baut Göteborg zur Ganzjahresdestination aus</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Etihad Airways wird ihre neue Verbindung zwischen Abu Dhabi und Göteborg ganzjährig anbieten. Ursprünglich war die Strecke saisonal geplant. Nach Angaben der Fluggesellschaft fiel die Nachfrage seit dem Buchungsstart jedoch höher aus als erwartet.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/etihad-baut-goeteborg-zur-ganzjahresdestination-aus/c0ekt78</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>auto-de207791033c</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>A330neo-Probleme bremsen Airbus-Auslieferungen</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Qualitätsmängel an Großraumjets vom Typ A330neo haben dem weltgrößten Flugzeugbauer Airbus im Sommer einen Rückschlag bei den Auslieferungen eingebrockt. Das Problem betreffe das Seitenleitwerk des Typs, teilte eine Airbus-Sprecherin am Donnerstag auf Nachfrage mit.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53531/A330neo-Probleme-bremsen-Airbus-Auslieferungen-.html</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>auto-86fc010a82b1</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Vorerst keine 35-Stunden-Woche bei EFW</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>DRESDEN - Den Elbe Flugzeugwerken (EFW) fehlen Aufträge in der Frachterumrüstung - Unternehmen und Gewerkschaft stellen Pläne für die Einführung einer 35-Stunden-Woche im Konzern jetzt um mindestens drei Jahre zurück. Ein Wartungsauftrag der Bundeswehr sichert bei EFW Beschäftigung.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53527/Vorerst-keine-35-Stunden-Woche-bei-EFW.html</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>auto-e14f48e07e16</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>DLR-Rover soll 2029 auf Marsmond aufsetzen</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>KÖLN - Wie kam der Mars zu seinen Monden? Aufklären helfen soll das ein Rover, der gerade mal so groß wie eine Getränkekiste ist. Das deutsch-französische Landefahrzeug "Idefix" soll den Mars 2027 erreichen - und 2029 als erster Rover überhaupt auf einem Marsmond aufsetzen.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53521/DLR-Rover-soll-Marsmond-erkunden.html</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>auto-0795b1919824</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>T’Way Air nimmt Flugverbindung zwischen Frankfurt und Seoul auf - aviation.direct</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMijwFBVV95cUxPN2w5Y0RYaUM1andWVHMzRVh0dkc0QmFKREdHM19LdzZxamsxbHdXTGVSc3pHTEpiNS1MbG9lbjdXZkRSeHBkcjI5SjJnSE1TZG5INVBtNndISGVFckJ2YzB2SDUxVEhpUGpFSzVnaUZIWUFaT3F6N29ueWR2TVJyLVcyYWVLVkZGT3k2Uy1lYw?oc=5" target="_blank"&gt;T’Way Air nimmt Flugverbindung zwischen Frankfurt und Seoul auf&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aviation.direct&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPN2w5Y0RYaUM1andWVHMzRVh0dkc0QmFKREdHM19LdzZxamsxbHdXTGVSc3pHTEpiNS1MbG9lbjdXZkRSeHBkcjI5SjJnSE1TZG5INVBtNndISGVFckJ2YzB2SDUxVEhpUGpFSzVnaUZIWUFaT3F6N29ueWR2TVJyLVcyYWVLVkZGT3k2Uy1lYw?oc=5</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>auto-74910c21b704</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt und das Nachtflugverbot - Maßnahme gegen Fluglärm - fnp.de</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipwFBVV95cUxQeDM4MHQ4dlAyYzhBaVRsdkdaQVlhNTloRHlQeGxISHhFaTAxTmJJMU1TdF9yZGo0bUxaNWlnamRJd0FveWZDRkhKY0kwT2hLNk9DeDFuc1l5LURTbWlsc1pZU0JSd0RJN1o5SXoxQXMzWkpZdnloc3FUU3JqRVRYekViRTV3cElJaXp0N0tpWERPWDhoZll6V2Jnck1sXzlGUEFqU0tPUQ?oc=5" target="_blank"&gt;Flughafen Frankfurt und das Nachtflugverbot - Maßnahme gegen Fluglärm&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fnp.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQeDM4MHQ4dlAyYzhBaVRsdkdaQVlhNTloRHlQeGxISHhFaTAxTmJJMU1TdF9yZGo0bUxaNWlnamRJd0FveWZDRkhKY0kwT2hLNk9DeDFuc1l5LURTbWlsc1pZU0JSd0RJN1o5SXoxQXMzWkpZdnloc3FUU3JqRVRYekViRTV3cElJaXp0N0tpWERPWDhoZll6V2Jnck1sXzlGUEFqU0tPUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>auto-f640e38dcd6c</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Air France eröffnet Schengen-Lounge im Frankfurter Terminal 3 - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiZEFVX3lxTE9JeW5ZaFNqODBQSm9DQVhjYkhfVXhXZVdCTkNXSGI0dVIxVWxLc05YVEIyUGkzQmx0bEtLeVZtMHJFTm5tOHlVdzhnMWM4cVJIdENVUFhNY2FPOWdKTGZTenlodHQ?oc=5" target="_blank"&gt;Air France eröffnet Schengen-Lounge im Frankfurter Terminal 3&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9JeW5ZaFNqODBQSm9DQVhjYkhfVXhXZVdCTkNXSGI0dVIxVWxLc05YVEIyUGkzQmx0bEtLeVZtMHJFTm5tOHlVdzhnMWM4cVJIdENVUFhNY2FPOWdKTGZTenlodHQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>auto-f83e5d420958</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Mit dem „Short Connection Pass“ schnell zum Anschluss-Flug - Airportzentrale</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitAFBVV95cUxOVWdiR21iSnBwN3lHclhJbW40UExJOFZPLWpqZEcyMWZWY1VjZUpJdWtpUnNVdl9GVklSWGNvRkZ1SmkyUlU1UHEyS2VPSi1OYTdmblhKOFd4Ri15eWQtbDFvZFJKYlpWR1IyNUtzZmZfZThSdlItQTkzUFF0Zkc2Nm9EamVfaWt2c2k3c3F3dUYzTUJhZDF3MUM3aGVDal9zUHU3UXJDRWVLYVNRRWx4NzktNkE?oc=5" target="_blank"&gt;Flughafen Frankfurt: Mit dem „Short Connection Pass“ schnell zum Anschluss-Flug&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airportzentrale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVWdiR21iSnBwN3lHclhJbW40UExJOFZPLWpqZEcyMWZWY1VjZUpJdWtpUnNVdl9GVklSWGNvRkZ1SmkyUlU1UHEyS2VPSi1OYTdmblhKOFd4Ri15eWQtbDFvZFJKYlpWR1IyNUtzZmZfZThSdlItQTkzUFF0Zkc2Nm9EamVfaWt2c2k3c3F3dUYzTUJhZDF3MUM3aGVDal9zUHU3UXJDRWVLYVNRRWx4NzktNkE?oc=5</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>auto-6768ad785c9d</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Korean Air setzt im Winter die beliebte Airbus A380 von Seoul nach Frankfurt ein - PointsMag</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMibkFVX3lxTE53M1VzbXczRHdtZ0Q0ZWJSbVlBYUVzMzY5TDB4MVZaX0lEdWJNNW9KOF94N01GZjVvcmhKN1BIcWhLVGpTM180N1pFaGNsWk9EZ3ItZ2VWazJ5czJReUt4YV9ZbnBIM1hnTmprdDJn?oc=5" target="_blank"&gt;Korean Air setzt im Winter die beliebte Airbus A380 von Seoul nach Frankfurt ein&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;PointsMag&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE53M1VzbXczRHdtZ0Q0ZWJSbVlBYUVzMzY5TDB4MVZaX0lEdWJNNW9KOF94N01GZjVvcmhKN1BIcWhLVGpTM180N1pFaGNsWk9EZ3ItZ2VWazJ5czJReUt4YV9ZbnBIM1hnTmprdDJn?oc=5</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>auto-5ed613f35ee5</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Flughafen Frankfurt: Air Astana kündigt Strecke nach Kostanai an - Airportzentrale</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxOenJNMnlvWnZyR3RkbllhLWhmV1kwSjYxNUxpeVYwOXFqYWMyb1VTVmlMVkdHeEt4VGJHS0JaOGlVOXRJYUlidDgteEVGZ3E0RHFBZllob25vcG5tY1NZdHZhQXh1N1FnYXozbVozdWp6QXVqU0FybGxkYmpZdmtJd0xjcTJUcF9URTRmM0NUci1qUS1Jc0Y0UWpid2JySzBEbHNPWA?oc=5" target="_blank"&gt;Flughafen Frankfurt: Air Astana kündigt Strecke nach Kostanai an&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Airportzentrale&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOenJNMnlvWnZyR3RkbllhLWhmV1kwSjYxNUxpeVYwOXFqYWMyb1VTVmlMVkdHeEt4VGJHS0JaOGlVOXRJYUlidDgteEVGZ3E0RHFBZllob25vcG5tY1NZdHZhQXh1N1FnYXozbVozdWp6QXVqU0FybGxkYmpZdmtJd0xjcTJUcF9URTRmM0NUci1qUS1Jc0Y0UWpid2JySzBEbHNPWA?oc=5</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>auto-3a3d46d8c47b</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Saudi Arabian Airlines fliegt seit 55 Jahren nach Frankfurt - aviation.direct</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiiwFBVV95cUxNRkVOUk42emNYR1ZXbXJONE9uckhZYzU2Q1hyTnItZWVld3ZKQkdUNjkzUThHZzZ2Mkh5TGdmSHdrQXZiMDVMYm9mMVBBWThpdjFYRUNldE9TRHRtUlRIdmlwQjhrSEFLcWUxTGNnd3lONElYV1RUQU1FMm1BT0M5WUtCbUMxdXplanNv?oc=5" target="_blank"&gt;Saudi Arabian Airlines fliegt seit 55 Jahren nach Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;aviation.direct&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNRkVOUk42emNYR1ZXbXJONE9uckhZYzU2Q1hyTnItZWVld3ZKQkdUNjkzUThHZzZ2Mkh5TGdmSHdrQXZiMDVMYm9mMVBBWThpdjFYRUNldE9TRHRtUlRIdmlwQjhrSEFLcWUxTGNnd3lONElYV1RUQU1FMm1BT0M5WUtCbUMxdXplanNv?oc=5</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>auto-350816dffd39</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Weltreisebausteine von Turkmenistan Airlines: Business Class Frankfurt ↔︎ Asien ab 757€ oneway - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMid0FVX3lxTE5YQ3V5UXQxWE9VdFRrT09jOHA4ZXRoUmtuMUw0dVRaRmFyMUpOSktpTUM5WW5zY1BYNWNIVlJRYk93bG9XeUlLdEcyVWxGN3FiZ3NJMGlka2xWWkZDQk1FUFNwVVh4MGpUNzNfMVVaNFpHd082d2tz?oc=5" target="_blank"&gt;Weltreisebausteine von Turkmenistan Airlines: Business Class Frankfurt ↔︎ Asien ab 757€ oneway&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5YQ3V5UXQxWE9VdFRrT09jOHA4ZXRoUmtuMUw0dVRaRmFyMUpOSktpTUM5WW5zY1BYNWNIVlJRYk93bG9XeUlLdEcyVWxGN3FiZ3NJMGlka2xWWkZDQk1FUFNwVVh4MGpUNzNfMVVaNFpHd082d2tz?oc=5</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>auto-b90e608c32d5</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>T'way Air erhöht die Zahl der Seoul-Frankfurt-Flüge und führt ab 2025 tägliche Verbindungen ein - PR Newswire</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi7wFBVV95cUxQYkk2enZzemdTS2tTQlhReDRROFNNVXVBYXB1Z0dYWmVST3A1dkFVNWNPcldZMWdZYnB1aWdMYXhpTDQ4ZjNCNEE1b0F1TnVneVYxRWhfOUo1OUdWMWRvNzRNWnROQThKcWU3ekNHbk0yV1RQQ2dWOUxoQ3lLVFdCQmhfSTg3QnkyZ1BjaEF2Rk5jUTN5S0U1bTZ2Z0RBVnhBSlpFc3plRXJFX2c2dGlIU2ZuS3duaWVKQ085ZXkyemtSTHBQdmc2YnYzTkplejRfTHRIaDNac2ZVSy1QdnVYOHhhTG9md3pCc0Zmd2w0WQ?oc=5" target="_blank"&gt;T'way Air erhöht die Zahl der Seoul-Frankfurt-Flüge und führt ab 2025 tägliche Verbindungen ein&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;PR Newswire&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQYkk2enZzemdTS2tTQlhReDRROFNNVXVBYXB1Z0dYWmVST3A1dkFVNWNPcldZMWdZYnB1aWdMYXhpTDQ4ZjNCNEE1b0F1TnVneVYxRWhfOUo1OUdWMWRvNzRNWnROQThKcWU3ekNHbk0yV1RQQ2dWOUxoQ3lLVFdCQmhfSTg3QnkyZ1BjaEF2Rk5jUTN5S0U1bTZ2Z0RBVnhBSlpFc3plRXJFX2c2dGlIU2ZuS3duaWVKQ085ZXkyemtSTHBQdmc2YnYzTkplejRfTHRIaDNac2ZVSy1QdnVYOHhhTG9md3pCc0Zmd2w0WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>auto-43cd82cf1b07</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Konkurrenz für Lufthansa? Condor startet Kairo-Flüge ab Frankfurt - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxNTUV2eHZzQzdzenhBMnIzdVRiTTkxeFdwTWhXNUExREJ5VmVmaVJDWXlRSzdCVHl4aV9BTzk5UHNZZHdBRzVtQy1HUUVlbDZzT3ZzVnhzbGMxMC1WNENVWFllQzhxSk5ORV9CdmtETi1hVTUyQnhJWnQyb25aV3dmaDRLYUtINnE4R2xSMFZhOXJ4Z1lDNGNBdA?oc=5" target="_blank"&gt;Konkurrenz für Lufthansa? Condor startet Kairo-Flüge ab Frankfurt&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTUV2eHZzQzdzenhBMnIzdVRiTTkxeFdwTWhXNUExREJ5VmVmaVJDWXlRSzdCVHl4aV9BTzk5UHNZZHdBRzVtQy1HUUVlbDZzT3ZzVnhzbGMxMC1WNENVWFllQzhxSk5ORV9CdmtETi1hVTUyQnhJWnQyb25aV3dmaDRLYUtINnE4R2xSMFZhOXJ4Z1lDNGNBdA?oc=5</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>auto-231d174b48dc</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Winterflugplan 2023/24: Vietnam Airlines baut Frankfurt-Angebot aus - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirgFBVV95cUxPendIbVhrYmN6TWh1NUxiQVFPOUtSbTh3aHp3alZpLWc4UjFpX2ZzUHQ4cUo5b0xIcVBDUGQzelp1UVd1QUdjZXpYSzVUMlZQcVJvSmNMakphNW5hVFVDbW1VcE01azFsQ21LX3lNTzEyekt1VU8yTjFmdzNMOThBT2NNZVhhTHVLd2I4SUhyOVFDbDJRT1o5OG1mOWJoMVFtR2xiRmNITEROMm9KTVE?oc=5" target="_blank"&gt;Winterflugplan 2023/24: Vietnam Airlines baut Frankfurt-Angebot aus&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPendIbVhrYmN6TWh1NUxiQVFPOUtSbTh3aHp3alZpLWc4UjFpX2ZzUHQ4cUo5b0xIcVBDUGQzelp1UVd1QUdjZXpYSzVUMlZQcVJvSmNMakphNW5hVFVDbW1VcE01azFsQ21LX3lNTzEyekt1VU8yTjFmdzNMOThBT2NNZVhhTHVLd2I4SUhyOVFDbDJRT1o5OG1mOWJoMVFtR2xiRmNITEROMm9KTVE?oc=5</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>auto-f61c0fff4901</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Turkish Airlines fliegt ab Januar vom neuen Istanbul Airport nach Deutschland - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiqgFBVV95cUxPRVFNWDRPVTlndC1TWkNWVmJLQWhmRFpNUnNBVjN1eHdVTW40RHp0S2tPUHNFYk1JQWJmbXV4dUFKZjJPZjBlN25KY1VQam5mbjZVQ2Z4WFF0b280QkRQU1lxMlItU0JPRUlRcFJ4TndhUndTc05jU1pfUGxod1I1SVpKRE9FN0otcFBkUkNiS05fZHM0TGxoN0hfVFlWS3JZRWJfM0xQeGxwQQ?oc=5" target="_blank"&gt;Turkish Airlines fliegt ab Januar vom neuen Istanbul Airport nach Deutschland&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPRVFNWDRPVTlndC1TWkNWVmJLQWhmRFpNUnNBVjN1eHdVTW40RHp0S2tPUHNFYk1JQWJmbXV4dUFKZjJPZjBlN25KY1VQam5mbjZVQ2Z4WFF0b280QkRQU1lxMlItU0JPRUlRcFJ4TndhUndTc05jU1pfUGxod1I1SVpKRE9FN0otcFBkUkNiS05fZHM0TGxoN0hfVFlWS3JZRWJfM0xQeGxwQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>auto-fc12e34872bd</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Review: American Airlines Admirals Club New York La Guardia Airport - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMimAFBVV95cUxOVk5SWnk1d1pKVVBaMDZoTTU0ZmliZzRNZ1k0TXo2QW1DOFRPQ3Z3UWNydldNZXpsZjdwUkF5SjFrbzRYZ2JDVmxLUFdzOEF2QUZTMzBRckJYcmNVNmpxa1NxYlBWNk5zeWF4R254RUpTWDJxRmwyUjJrT3ZfYjR3ZE5jcnZKMllmMWVncHNyYWdYLU9RdDZsRw?oc=5" target="_blank"&gt;Review: American Airlines Admirals Club New York La Guardia Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVk5SWnk1d1pKVVBaMDZoTTU0ZmliZzRNZ1k0TXo2QW1DOFRPQ3Z3UWNydldNZXpsZjdwUkF5SjFrbzRYZ2JDVmxLUFdzOEF2QUZTMzBRckJYcmNVNmpxa1NxYlBWNk5zeWF4R254RUpTWDJxRmwyUjJrT3ZfYjR3ZE5jcnZKMllmMWVncHNyYWdYLU9RdDZsRw?oc=5</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>auto-24d4aaebc578</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Singapore Airlines nimmt ab 2. November die beliebte Strecke Frankfurt - New York wieder auf - PointsMag</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMif0FVX3lxTE5tcVdfLWdSOHIwUzdsV3pCd2JKSjZmVjBYdG5JbnlDVmM3QWl6dzZLUlFHSmZDcUgzclNKRllaaWVhZTdYM1JqOWpnOXh5Rzd1Z0FGcWl6VEU4ZDdvR1lRcHJNelI4bWFTSHZFYW9lUHlwUWlOUmliMnVyRzlHaDA?oc=5" target="_blank"&gt;Singapore Airlines nimmt ab 2. November die beliebte Strecke Frankfurt - New York wieder auf&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;PointsMag&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5tcVdfLWdSOHIwUzdsV3pCd2JKSjZmVjBYdG5JbnlDVmM3QWl6dzZLUlFHSmZDcUgzclNKRllaaWVhZTdYM1JqOWpnOXh5Rzd1Z0FGcWl6VEU4ZDdvR1lRcHJNelI4bWFTSHZFYW9lUHlwUWlOUmliMnVyRzlHaDA?oc=5</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>auto-51a2a687adf4</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Review: Turkish Airlines Lounge Istanbul Airport - Frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMif0FVX3lxTE9hQk0yODUwRnl2aFQxaUp1NXNNdU5KZ3NLeGtWRk1WbWZxb0wwNlh0VHZILTJoY0tKaGxlLWtNcFRYQ1FMSTFzZjBPcDI2MnhGcDBiSzZPSE1BaFgtUXNQNVNvRm9IUjh0d0VHcUIySDFBaHg1SFE2MlZFaTlBYXM?oc=5" target="_blank"&gt;Review: Turkish Airlines Lounge Istanbul Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9hQk0yODUwRnl2aFQxaUp1NXNNdU5KZ3NLeGtWRk1WbWZxb0wwNlh0VHZILTJoY0tKaGxlLWtNcFRYQ1FMSTFzZjBPcDI2MnhGcDBiSzZPSE1BaFgtUXNQNVNvRm9IUjh0d0VHcUIySDFBaHg1SFE2MlZFaTlBYXM?oc=5</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O246"/>
+  <dimension ref="A1:O265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14469,7 +14469,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14500,8 +14499,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
           <t>review</t>
@@ -14534,7 +14531,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14565,8 +14561,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
           <t>review</t>
@@ -14599,7 +14593,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14630,8 +14623,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
           <t>review</t>
@@ -14664,7 +14655,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14695,8 +14685,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
           <t>review</t>
@@ -14729,7 +14717,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14760,8 +14747,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
           <t>review</t>
@@ -14794,7 +14779,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14825,8 +14809,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>review</t>
@@ -14859,7 +14841,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14890,8 +14871,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>review</t>
@@ -14924,7 +14903,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -14955,8 +14933,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>review</t>
@@ -14989,7 +14965,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15020,8 +14995,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>review</t>
@@ -15054,7 +15027,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15085,8 +15057,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
           <t>review</t>
@@ -15119,7 +15089,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15150,8 +15119,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
           <t>review</t>
@@ -15184,7 +15151,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15215,8 +15181,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
           <t>review</t>
@@ -15249,7 +15213,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15280,8 +15243,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
           <t>review</t>
@@ -15314,7 +15275,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15345,8 +15305,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
           <t>review</t>
@@ -15379,7 +15337,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15410,8 +15367,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
           <t>review</t>
@@ -15444,7 +15399,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15475,8 +15429,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
           <t>review</t>
@@ -15509,7 +15461,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15540,8 +15491,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
           <t>review</t>
@@ -15574,7 +15523,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15605,8 +15553,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
           <t>review</t>
@@ -15639,7 +15585,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15670,8 +15615,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
           <t>review</t>
@@ -15704,7 +15647,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15735,8 +15677,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
           <t>review</t>
@@ -15748,6 +15688,1241 @@
         </is>
       </c>
       <c r="O246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>auto-ce3ed19d4479</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Air China reduziert temporär Angebot nach Franfurt und Genf</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Air China reduziert im vierten Quartal 2026 die Frequenzen auf mehreren Europastrecken. Ab Peking werden unter anderem die Verbindungen nach Brüssel, Budapest und Venedig um jeweils einen wöchentlichen Flug gekürzt. Auch nach genf kürtzt die cheinesische Nationalairline von fünf auf vier Flüge pro Woche. Besonders deutlich fällt die Reduzierung nach Istanbul aus: Statt täglich fliegt Air China dort zeitweise nur noch vier Mal pro Woche.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/air-china-reduziert-temporaer-angebot-nach-franfurt-und-genf/r6s8qqg</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>auto-2e21fbb71538</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Flybondi verlagert Mitarbeitende zu neuer Frachtgesellschaft</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Flybondi hat damit begonnen, Teile ihrer Belegschaft zu OCA Air zu verlagern. Die mit dem Unternehmer Marcelo Scatturice verbundene Airline soll sich auf Fracht-, Post- und Logistikdienste konzentrieren und zunächst mit drei Flugzeugen starten. Gewerkschaftskreisen zufolge wurden bereits mehr als 200 Flybondi-Beschäftigte über den Wechsel informiert, wie argentinische Medien berichten.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flybondi-verlagert-mitarbeitende-zu-neuer-frachtgesellschaft/4j8j2fz</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>auto-6d4b90ca1c3b</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Gefahrstoffalarm: Terminal 1 am Flughafen Berlin musste evakuiert werden</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Am Flughafen Berlin Brandenburg ist am Donnerstagabend (3. September) das Terminal 1 vorübergehend evakuiert worden. Auslöser war ein Gefahrstoffalarm. Wie die B.Z. berichtet, hatte eine Frau an einem Servicepoint der Bundespolizei angegeben, einen gefährlichen Stoff bei sich zu haben.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/gefahrstoffalarm-terminal-1-am-flughafen-berlin-musste-evakuiert-werden/sj29d77</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>auto-df3366266d41</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Französische Elite-Flugstaffel erhält zweiten Pilatus PC-24</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Die Escadrille 57S der französischen Marine setzt künftig auf Schweizer Businessjets statt auf Dassault. Nun hat die Elitestaffel ihren zweiten Pilatus PC-24 übernommen.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flugzeuge/franzoesische-marine-setzt-auf-schweizer-pilatus-pc-24-statt-dassault/gqhs874</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>auto-f62b5857ea39</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Harald Gloy wird 2027 nächster Chef von Lufthansa Technik</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa regelt die Nachfolge intern: Harald Gloy wird zum 1. Februar 2027 neuer Vorstandschef der Lufthansa Technik. Der 54-jährige Manager folgt dann auf Sören Stark, der in den Ruhestand tritt. Gloy erhält zunächst einen Vertrag über fünf Jahre, teilte Lufthansa am Freitag mit.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53548/Harald-Gloy-wird-2027-naechster-Chef-von-Lufthansa-Technik.html</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>auto-4548e3d8d8aa</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Lufthansa darf wieder nicht zurück in den DAX</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa muss weiter auf eine Rückkehr in den DAX warten. Die Deutsche Börse ändert die Zusammensetzung im Leitindex nicht.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53545/Lufthansa-darf-wieder-nicht-zurueck-in-den-DAX.html</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>auto-ba8b549fd097</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ATR zieht größten Auftrag seit zehn Jahren an Land</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Der französisch-italienische Turboprop-Flugzeugbauer ATR hat den größten Auftrag seit zehn Jahren erhalten. Die indische Regionalfluggesellschaft Fly 91 aus Goa bestellte 40 Maschinen des Typs ATR 72-600, wie ATR am Donnerstag mitteilte. Der Auftrag hat den Angaben zufolge einen Wert von rund einer Milliarde US-Dollar.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53538/ATR-zieht-groessten-Auftrag-seit-zehn-Jahren-an-Land.html</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>auto-8caa3f668be8</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Polizei räumt Terminal 1 am BER</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>BERLIN - Eine Frau meldet am Flughafen BER einen möglicherweise gefährlichen Stoff. Die Polizei ließ das Terminal 1 teilweise räumen. Am späten Abend folgt die Entwarnung - nach einer mehrstündigen Sperrung. Der Flugbetrieb war durch den Zwischenfall im Terminal 1 eingeschränkt.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53536/Polizei-raeumt-Terminal-1-am-BER.html</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>auto-3cf3097fb5ae</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Putin: Russische Ölindustrie weiter intakt</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>WLADIWOSTOK - Kremlchef Wladimir Putin sieht trotz Milliardenschäden durch die ukrainischen Angriffe auf Ölraffinerien und andere kritische Infrastruktur weiter Ressourcen für eine Fortsetzung seines Krieges.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53535/Putin-Russische-Oelindustrie-weiter-intakt.html</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>auto-c29743c73a54</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Ufo und Lufthansa nehmen Verhandlungen wieder auf</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Die Kabinengewerkschaft Ufo und Lufthansa werden in der kommenden Woche wieder in Gespräche zu offenen Tarifthemen einsteigen.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53533/Ufo-und-Lufthansa-nehmen-Verhandlungen-wieder-auf.html</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>auto-0d2d2fb72787</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Im Terminal 3: Air France eröffnet neue Lounge am Frankfurt Airport - fvw|TravelTalk</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMisAFBVV95cUxOXzY0bGN0bmRGZkVWbjZ4bjYxaVcxNHBBaFZOTkZnaGlQS2tUdElHaVotSkR2UzhyTWU2bm9Pa3Q0LWNIanhiWndaSmplb0NmaE1wZHk5a0NFS1FUYmw1M3UxamNNYlQ1SFlhYktRS0dVa1A4MEEwTmxzeGpYNjNtZThTQi1pcWJ0ZVJqZ1k1ZDYwQ0lLMjRmLXBmREQ4MVFPZmZkZWp6TUs3Q2t5Qkpvbw?oc=5" target="_blank"&gt;Im Terminal 3: Air France eröffnet neue Lounge am Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;fvw|TravelTalk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOXzY0bGN0bmRGZkVWbjZ4bjYxaVcxNHBBaFZOTkZnaGlQS2tUdElHaVotSkR2UzhyTWU2bm9Pa3Q0LWNIanhiWndaSmplb0NmaE1wZHk5a0NFS1FUYmw1M3UxamNNYlQ1SFlhYktRS0dVa1A4MEEwTmxzeGpYNjNtZThTQi1pcWJ0ZVJqZ1k1ZDYwQ0lLMjRmLXBmREQ4MVFPZmZkZWp6TUs3Q2t5Qkpvbw?oc=5</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>auto-c3b50c48b2de</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Air France eröffnet neue Lounge im Terminal 3 am Frankfurter Flughafen - airliners.de</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMikwFBVV95cUxOSklORTNDM2UwNC0tdlFubTZnRlpPMUd2WlVNcDhLS1BvZTE1eHhvVUFubFh2NklLY1NNSGE1NGlQcW4ta3JPdGpBSXdXYm1ZSko1US1xNEhEQnduUUVkV1E3c3BxNEtCS01aU09jTzI3SHhDMXByeHdyX0pkZWx0NWtYZzNYelllRHk3ODgyWFdaQXM?oc=5" target="_blank"&gt;Air France eröffnet neue Lounge im Terminal 3 am Frankfurter Flughafen&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;airliners.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOSklORTNDM2UwNC0tdlFubTZnRlpPMUd2WlVNcDhLS1BvZTE1eHhvVUFubFh2NklLY1NNSGE1NGlQcW4ta3JPdGpBSXdXYm1ZSko1US1xNEhEQnduUUVkV1E3c3BxNEtCS01aU09jTzI3SHhDMXByeHdyX0pkZWx0NWtYZzNYelllRHk3ODgyWFdaQXM?oc=5</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>auto-930634570e07</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Discover Airlines führt ab München wieder Flüge im eigenen Namen durch - frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxOczdOSm4yV3RmWjR3a3Y1MmVNRkZ2ZHJEMS1xQWctRHVsUzBEenRIdGNnNXVrR2RsOWd0Q0VVa01IMWZDOVFod2lZME51TXlYRkhDUlAtTzVaZTFtcklTRVQ1TVRIa1IzOG50VUx6NV90MDhuZXpDMGJ4TGVWdEdQQTh3SmV4c0Y0NlBWVHVPMlE4NDB5ZXdtME5TYXgzTVdZSFE?oc=5" target="_blank"&gt;Discover Airlines führt ab München wieder Flüge im eigenen Namen durch&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOczdOSm4yV3RmWjR3a3Y1MmVNRkZ2ZHJEMS1xQWctRHVsUzBEenRIdGNnNXVrR2RsOWd0Q0VVa01IMWZDOVFod2lZME51TXlYRkhDUlAtTzVaZTFtcklTRVQ1TVRIa1IzOG50VUx6NV90MDhuZXpDMGJ4TGVWdEdQQTh3SmV4c0Y0NlBWVHVPMlE4NDB5ZXdtME5TYXgzTVdZSFE?oc=5</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>auto-e0ea3954d6ad</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Bangkok: Business Class von Frankfurt ab 1.197€ mit Turkmenistan Airlines - Travel-Dealz</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMihAFBVV95cUxNY0tIWERFM1VJUjh0bU1OTGZGSmJlX0dvb2I4YjZBWXB4RzdrR3ZGSmhFMmtuVTI5TlFOelhFUFpKbGNJQWVSOTFYV0dRTGFkVDFWRXphZFE0Zk8xLW9QUUtfVzFPYjJ0Y2lGZFp2aFdtM19hdXRRVHNISHNIX3N1ZFVWTEg?oc=5" target="_blank"&gt;Bangkok: Business Class von Frankfurt ab 1.197€ mit Turkmenistan Airlines&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Travel-Dealz&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNY0tIWERFM1VJUjh0bU1OTGZGSmJlX0dvb2I4YjZBWXB4RzdrR3ZGSmhFMmtuVTI5TlFOelhFUFpKbGNJQWVSOTFYV0dRTGFkVDFWRXphZFE0Zk8xLW9QUUtfVzFPYjJ0Y2lGZFp2aFdtM19hdXRRVHNISHNIX3N1ZFVWTEg?oc=5</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>auto-60a1ba4959fe</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Die günstigsten Discover Airlines Business Class Prämienflüge ab Frankfurt/München - meilenoptimieren</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMirAFBVV95cUxQZ2FrUUlsWlM3STEwQmZLNDhnbmx6cHNEX2toRW1KdkhJY1RQUHEzN2U5SzRKRWhpT1hOQkRBcGVxaXIwWTZZQThDNERScXkwV1BlQnJBNFdCMHMzWWp2aXdLRGRPSTdVU0lpaE9kSGRITmdaUkh0N1FVM24zSUJrcElJM1UwdVBSdGY5VW1QR2FjY1daM1NNTWhOSHZWVjkxeDFuNF9fMGRocHZG?oc=5" target="_blank"&gt;Die günstigsten Discover Airlines Business Class Prämienflüge ab Frankfurt/München&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQZ2FrUUlsWlM3STEwQmZLNDhnbmx6cHNEX2toRW1KdkhJY1RQUHEzN2U5SzRKRWhpT1hOQkRBcGVxaXIwWTZZQThDNERScXkwV1BlQnJBNFdCMHMzWWp2aXdLRGRPSTdVU0lpaE9kSGRITmdaUkh0N1FVM24zSUJrcElJM1UwdVBSdGY5VW1QR2FjY1daM1NNTWhOSHZWVjkxeDFuNF9fMGRocHZG?oc=5</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>auto-ade6cf26494f</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Review: Gulf Air Falcon Gold (Business Class) Bahrain nach Frankfurt – GF17 (A321) - frankfurtflyer.de</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMioAFBVV95cUxOQnVnSkFBbDk2QzljNGlvaVBsQzE2WndQZ0p1cmZTQnE4UkgtQi1UX3oyTUY5cTVmSDM1Qy1ZQklSWnFBOXlOSlMzUF9CMkJ0dk5GLVd2WHVHSlJIZmNEdURHMGgtWjBVSkRvMjhFVGpEbVF5clJmV1hQdHo5dUpqelhkZHlWQlNDTFo3ODhnQ0tGQVQxUjZRUzQwMmI2VDd5?oc=5" target="_blank"&gt;Review: Gulf Air Falcon Gold (Business Class) Bahrain nach Frankfurt – GF17 (A321)&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;frankfurtflyer.de&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOQnVnSkFBbDk2QzljNGlvaVBsQzE2WndQZ0p1cmZTQnE4UkgtQi1UX3oyTUY5cTVmSDM1Qy1ZQklSWnFBOXlOSlMzUF9CMkJ0dk5GLVd2WHVHSlJIZmNEdURHMGgtWjBVSkRvMjhFVGpEbVF5clJmV1hQdHo5dUpqelhkZHlWQlNDTFo3ODhnQ0tGQVQxUjZRUzQwMmI2VDd5?oc=5</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>auto-de02828a81b2</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Harrowing Ryanair flight on Boeing jet forces emergency landing - The Seattle Times</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiwAFBVV95cUxOLTFKb01zM0ZmdWRGUkRnVHlkZGVWWXFvMm9sVTNpUWpuUE5sR19HUlVpZ05hV2FXRWRoRUxuVG9wRzBMZ3lHUXFIaERkZWY4NzhtN3VKaTVDaWQ4SHkxY2RTRGczVjJMWWljcmRQTGRldzFXRU5CZXRpVXdrYm4zUjkzeE1JVUpVaVAxdlRzeFBxdnVpcDBUbEJ2ZWZnOHo0c291T3dyWmxVcG9HSjg5WV9HUDlOZWVKaVZ0Y3FuZ2o?oc=5" target="_blank"&gt;Harrowing Ryanair flight on Boeing jet forces emergency landing&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Seattle Times&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOLTFKb01zM0ZmdWRGUkRnVHlkZGVWWXFvMm9sVTNpUWpuUE5sR19HUlVpZ05hV2FXRWRoRUxuVG9wRzBMZ3lHUXFIaERkZWY4NzhtN3VKaTVDaWQ4SHkxY2RTRGczVjJMWWljcmRQTGRldzFXRU5CZXRpVXdrYm4zUjkzeE1JVUpVaVAxdlRzeFBxdnVpcDBUbEJ2ZWZnOHo0c291T3dyWmxVcG9HSjg5WV9HUDlOZWVKaVZ0Y3FuZ2o?oc=5</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>auto-4a6cd22c98a7</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Bird slams into plane nose: Cabin filled with smoke mid-air; panic on Paris-bound flight — watch - The Times of India</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi-wFBVV95cUxNT29qQV9jYjRhZUFXT1VhaVVPRWlJUUtwRlVON241WXVIZHVKOWZoZzE2UkRBM0tiVGhXM09DaURnYno1cktha1NkS3lFei1xOHNYM2IwMXBjUlhTU0NVNUFET19vTS1CemFucUMtVUJvaWUtaE1hVmswWWxTblY5WEJSZ1RrT3A0NnRoSnlGN1V6WG9qMWtGTllhTjl1RGNDNmZUUHVGeVFkNDBtWHJSbTFZX0ZpWkNnamtFLTJNRFpDUFRWMzZNbF9yZTRoNm1CNEdUeEVzTTR0MFZ4ZmFpRDkzR3NOSDJSLUwtYmhYQm1acTZQelJUWHZPMNIBgAJBVV95cUxOSUgwMHFfWk02aVpkelp4bE42WjZ1TE1WRU1aYXVOM196SlVMNmhMXzMxQ2M3T091V1pQbDRIYU5IRVU4YkFTbzdYMjVYWmZWaTJjN3dLYzJXOUtjSWNrMjZjLURvb2JpR3kyV1RwUjFrN3lESmJEaHl3OXdXV0F1c3pQQjROeEVpQk9sb2RBVXAtOUVwMkVvY1VBRlo3ZnFseFRpa2hsWGhsSHkyZjNwcWpUV290QUg0dXg3OHdnUGV3UE82Szk2eUtkTFhieUVZbEo4NW5uemJNYVpOSk1qNnU5MWJ0ek4za1BBVHEyWVNfYWlJVTBaRUVQcGZvaHpH?oc=5" target="_blank"&gt;Bird slams into plane nose: Cabin filled with smoke mid-air; panic on Paris-bound flight — watch&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Times of India&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNT29qQV9jYjRhZUFXT1VhaVVPRWlJUUtwRlVON241WXVIZHVKOWZoZzE2UkRBM0tiVGhXM09DaURnYno1cktha1NkS3lFei1xOHNYM2IwMXBjUlhTU0NVNUFET19vTS1CemFucUMtVUJvaWUtaE1hVmswWWxTblY5WEJSZ1RrT3A0NnRoSnlGN1V6WG9qMWtGTllhTjl1RGNDNmZUUHVGeVFkNDBtWHJSbTFZX0ZpWkNnamtFLTJNRFpDUFRWMzZNbF9yZTRoNm1CNEdUeEVzTTR0MFZ4ZmFpRDkzR3NOSDJSLUwtYmhYQm1acTZQelJUWHZPMNIBgAJBVV95cUxOSUgwMHFfWk02aVpkelp4bE42WjZ1TE1WRU1aYXVOM196SlVMNmhMXzMxQ2M3T091V1pQbDRIYU5IRVU4YkFTbzdYMjVYWmZWaTJjN3dLYzJXOUtjSWNrMjZjLURvb2JpR3kyV1RwUjFrN3lESmJEaHl3OXdXV0F1c3pQQjROeEVpQk9sb2RBVXAtOUVwMkVvY1VBRlo3ZnFseFRpa2hsWGhsSHkyZjNwcWpUV290QUg0dXg3OHdnUGV3UE82Szk2eUtkTFhieUVZbEo4NW5uemJNYVpOSk1qNnU5MWJ0ek4za1BBVHEyWVNfYWlJVTBaRUVQcGZvaHpH?oc=5</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>auto-5118b6117bf3</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Emirates Flight Diverts to Edinburgh After Mid-Air Emergency Near Newcastle, Signals ‘7700’ Code - The Sunday Guardian</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi1AFBVV95cUxNNFZKMzU3Tk1aYmZOWVBuV3J0WWNvZi1lZjBLeFdDX3dMWXZLb0UzcGF6YmNBa3Uzdnd2LWRXaFNMS1VnUkc0ek8wM2NYSFpUb2dYMlBHVWV5TUtOWnJyTmp3TnlRcFk1MXp0Z1NtUzZLZVptejI0LXk3NHVBWVFWbTdFVTN0eklJUFBabzRlTGdLa29yNDVFU2gzMF9zZF9iclBRWnA4c19EempJellhUXhEYUJjVGtPLXF6eThpVFp6WDB5TkNZdks2OHVHem9IcDZzadIB2gFBVV95cUxQT1Qyc05RdWw3dnY4M1E0bzFsT2ZZSG92SUZIVVVpb0FhWWt6NHV3SFAzVTRYRFY0Z0ZLQnZhcGdUOEU3NE9naWJqVnk1QTMzbDFLaEVYZU1kMGt1TkhzajYtQmJ4Q2ZjUWw5VC1QQ2VDSjdwNGJFXy1EblJpbE9xWDV3My1xMGhfcEliNm5taXQ3aWV3SlcwQTViWkdKVHJqc2lBSl9lbUxSZGdRU0J2djZ1X0ltMGRDdUNPWGFESWJxS1gycWNXaFJGejlfMXhQT2pFRkkwZTNYQQ?oc=5" target="_blank"&gt;Emirates Flight Diverts to Edinburgh After Mid-Air Emergency Near Newcastle, Signals ‘7700’ Code&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Sunday Guardian&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNNFZKMzU3Tk1aYmZOWVBuV3J0WWNvZi1lZjBLeFdDX3dMWXZLb0UzcGF6YmNBa3Uzdnd2LWRXaFNMS1VnUkc0ek8wM2NYSFpUb2dYMlBHVWV5TUtOWnJyTmp3TnlRcFk1MXp0Z1NtUzZLZVptejI0LXk3NHVBWVFWbTdFVTN0eklJUFBabzRlTGdLa29yNDVFU2gzMF9zZF9iclBRWnA4c19EempJellhUXhEYUJjVGtPLXF6eThpVFp6WDB5TkNZdks2OHVHem9IcDZzadIB2gFBVV95cUxQT1Qyc05RdWw3dnY4M1E0bzFsT2ZZSG92SUZIVVVpb0FhWWt6NHV3SFAzVTRYRFY0Z0ZLQnZhcGdUOEU3NE9naWJqVnk1QTMzbDFLaEVYZU1kMGt1TkhzajYtQmJ4Q2ZjUWw5VC1QQ2VDSjdwNGJFXy1EblJpbE9xWDV3My1xMGhfcEliNm5taXQ3aWV3SlcwQTViWkdKVHJqc2lBSl9lbUxSZGdRU0J2djZ1X0ltMGRDdUNPWGFESWJxS1gycWNXaFJGejlfMXhQT2pFRkkwZTNYQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O265"/>
+  <dimension ref="A1:O270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15709,7 +15709,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15740,8 +15739,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
           <t>review</t>
@@ -15774,7 +15771,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15805,8 +15801,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
           <t>review</t>
@@ -15839,7 +15833,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15870,8 +15863,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
           <t>review</t>
@@ -15904,7 +15895,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -15935,8 +15925,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
           <t>review</t>
@@ -15969,7 +15957,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16000,8 +15987,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
           <t>review</t>
@@ -16034,7 +16019,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16065,8 +16049,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
           <t>review</t>
@@ -16099,7 +16081,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16130,8 +16111,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
           <t>review</t>
@@ -16164,7 +16143,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -16195,8 +16173,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
           <t>review</t>
@@ -16229,7 +16205,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16260,8 +16235,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
           <t>review</t>
@@ -16294,7 +16267,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16325,8 +16297,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
           <t>review</t>
@@ -16359,7 +16329,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16390,8 +16359,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr">
         <is>
           <t>review</t>
@@ -16424,7 +16391,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16455,8 +16421,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
           <t>review</t>
@@ -16489,7 +16453,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16520,8 +16483,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
           <t>review</t>
@@ -16554,7 +16515,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16585,8 +16545,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
           <t>review</t>
@@ -16619,7 +16577,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16650,8 +16607,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>review</t>
@@ -16684,7 +16639,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16715,8 +16669,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
           <t>review</t>
@@ -16749,7 +16701,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -16780,8 +16731,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
           <t>review</t>
@@ -16814,7 +16763,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -16845,8 +16793,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
           <t>review</t>
@@ -16879,7 +16825,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -16910,8 +16855,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr">
         <is>
           <t>review</t>
@@ -16923,6 +16866,331 @@
         </is>
       </c>
       <c r="O265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>auto-f01e1d78b5c9</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lufthansa kürzt Winterangebot zwischen Frankfurt und New York</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Pro Tag nur ein Flug statt der bisher geplanten zwei Flüge: Die deutsche Fluggesellschaft halbiert für den Winterflugplan 2026/27 ihre Frequenz zwischen Frankfurt und New York-JFK, wie das Portal &lt;a href="https://www.aero.de/news-53553/Lufthansa-halbiert-A350-Frequenz-zwischen-Frankfurt-und-New-York.html" id="ad2729cf-1cb8-4065-9637-94501534eb5e"&gt;Aero&lt;/a&gt; berichtet. Wie schon im vergangenen Winter werde man «keinen zweiten täglichen Flug von Frankfurt nach New York (JFK) anbieten», bestätigte ein Airline-Sprecher.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-kuerzt-winterangebot-zwischen-frankfurt-und-new-york/q7yv2nk</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>auto-08bd2488b3e4</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Thüringer Luft- und Raumfahrttag</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Der Thüringer Luft- und Raumfahrttag gibt Einblicke in die aktuellen Entwicklungen und zukünftigen Herausforderungen der Branche. Im Mittelpunkt steht die Frage, wie sich Luft- und Raumfahrt technologisch und wirtschaftlich weiterentwickeln und dabei souverän sowie wettbewerbsfähig bleiben können. Fachvorträge, Diskussionen und Unternehmensbesuche bieten dabei spannende Einblicke und Raum für den Austausch zwischen Industrie, Forschung und Politik.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ads/thueringer-luft-und-raumfahrttag/6mbpl46</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>auto-68db12a45dc7</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lufthansa reduziert Frequenz zwischen Frankfurt und New York</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa nimmt Flugangebot auf einer zentralen Nordamerikalinie raus. Auf der Verbindung Frankfurt-New York JFK beschränkt sich Lufthansa im Winter 2026/2027 auf einen täglichen A350-Umlauf. Auswirkungen auf die Frankfurter A350-Exilflotte hat die Entscheidung nicht.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53553/Lufthansa-halbiert-A350-Frequenz-zwischen-Frankfurt-und-New-York.html</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>auto-591bae2d6a33</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Lufthansa und Piloten starten Schlichtung und Mediation</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Flankiert von Schlichtern starten Lufthansa und die Vereinigung Cockpit in einen Verhandlungsmarathon. Das Pilotenlager schickt Bodo Ramelow in den Ring, Lufthansa Roland Koch. Die Ex-Ministerpräsidenten gehen harte Tarifthemen an - mit der Schlichtung spannen Lufthansa und Piloten ein Auffangnetz.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53551/Lufthansa-und-Piloten-starten-Schlichtung-und-Mediation.html</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>auto-3c88535ecd03</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Vietnam Airlines flight makes emergency landing in Munich after technical issue - The Star</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZm50WmZaOU95YnczYXhRVzY0bmhhRkRyc2xBaldhektHaHNLQ1dvMG5WM3lhcFdNUlY4cEJHUllFaERPRUQya1B2Z0ZnOUdraHc3VDA2bDRHbTBUbzNWempMT1VtWGJPb0ZqY2VWdTRWSXVRY29aTzZoUmFVR3ZQME4tUGl1N3pzbXhxUDFCQkdYNzQtUVctS05CdXYtb1hGbWFLSjd0NEdZZGwxMjFQQ2Z4XzZqekZhUkpBQkp6RklScld0N0hPRzN3TDRuWmdlSVpEcHNza1RYdw?oc=5" target="_blank"&gt;Vietnam Airlines flight makes emergency landing in Munich after technical issue&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The Star&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZm50WmZaOU95YnczYXhRVzY0bmhhRkRyc2xBaldhektHaHNLQ1dvMG5WM3lhcFdNUlY4cEJHUllFaERPRUQya1B2Z0ZnOUdraHc3VDA2bDRHbTBUbzNWempMT1VtWGJPb0ZqY2VWdTRWSXVRY29aTzZoUmFVR3ZQME4tUGl1N3pzbXhxUDFCQkdYNzQtUVctS05CdXYtb1hGbWFLSjd0NEdZZGwxMjFQQ2Z4XzZqekZhUkpBQkp6RklScld0N0hPRzN3TDRuWmdlSVpEcHNza1RYdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -16887,7 +16887,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16918,8 +16917,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
           <t>review</t>
@@ -16952,7 +16949,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -16983,8 +16979,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
           <t>review</t>
@@ -17017,7 +17011,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17048,8 +17041,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
           <t>review</t>
@@ -17082,7 +17073,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17113,8 +17103,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
           <t>review</t>
@@ -17147,7 +17135,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -17178,8 +17165,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
           <t>review</t>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O270"/>
+  <dimension ref="A1:O281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17181,6 +17181,721 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>auto-879b71726ccd</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Discover Airlines fliegt neu nach Alghero und Genua</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Discover Airlines baut im Sommer 2027 das Italien-Angebot aus und nimmt zwei neue Strecken auf. Ab Juni fliegt der Ferienflieger zweimal wöchentlich von München nach Alghero auf Sardinien, jeweils montags und freitags. Bereits ab Ende März geht es samstags und sonntags von Frankfurt nach Genua. Auf beiden Strecken gibt es derzeit keine anderen Direktverbindungen. Die Genua-Flüge sind Teil einer Kooperation mit Costa Cruises, die einen festen Anteil der Sitze für Kreuzfahrtgäste abnimmt. Zugleich erhöht Discover die Frequenz nach Brindisi. Zusammen mit Bari umfasst das Italien-Programm damit vier Ziele und bis zu zehn Flüge pro Woche. Auf allen Strecken kommen Airbus A320 zum Einsatz.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/discover-airlines-fliegt-neu-nach-alghero-und-genua/kvm9gjz</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>auto-6b3ff1bc2014</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>La Compagnie kommt erstmals nach Deutschland und fliegt von Düsseldorf nach New York</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Die französische Business-Class-Airline steuert erstmals einen deutschen Flughafen an. Ab April 2027 verbindet La Compagnie Düsseldorf mit Newark bei New York.</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/flughaefen/la-compagnie-fliegt-von-duesseldorf-nach-new-york-business-class-airline-mit/cnw8nkb</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>auto-c11a6db10d6d</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lufthansa und Air France-KLM müssen bei Tap nachlegen</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Portugal wollte das Rennen um Tap eigentlich auf einen Bewerber reduzieren. Doch Lufthansa und Air France-KLM liegen mit ihren Angeboten so dicht beieinander, dass beide nachbessern dürfen.</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/lufthansa-und-air-france-klm-muessen-bei-angebot-fuer-tap-nachlegen-portugal/j2ffvxf</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>auto-d6d19778fe53</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Was bisher über die Bruchlandung der Boeing 767 von Amazon in Miami bekannt ist</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Fünf Tote, mehrere Verletzte und eine Boeing 767 außerhalb des Flughafengeländes: Der Unfall eines für Amazon fliegenden Frachters von 21 Air hat schwere Folgen. Aufnahmen des Anflugs liefern erste Hinweise auf einen ungewöhnlichen Ablauf. Das ist über Flug 2I7598, die N1997A und die laufenden Ermittlungen bekannt.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/sicherheit/was-bisher-ueber-die-bruchlandung-der-boeing-767-von-amazon-in-miami-bekannt-ist/2d65x20</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>auto-33fd220e006d</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Brasilianischer Flughafen muss nach Kollision eines Flugzeugs mit einem Wasserschwein Schadenersatz zahlen</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Acht Jahre nach der Kollision eines Schulungsflugzeugs mit einem Wasserschwein am Flughafen Campo Grande muss der damalige Betreiber Infraero Schadenersatz zahlen. Ein brasilianisches Gericht bestätigte Zahlungen von insgesamt rund 181.000 Real (rund 29.000 Euro) für Reparatur, Abstellkosten und weitere Ausgaben. Hinzu kommen Entschädigungen für entgangene Einnahmen.</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/brasilianischer-flughafen-muss-nach-kollision-eines-flugzeugs-mit-einem-wasserschwein/n0wlvxs</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>auto-bfbe41c21147</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Medsky Airways plant Direktflüge zwischen Libyen und Frankreich</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Libyen steht vor der Wiederaufnahme direkter Flugverbindungen mit Frankreich nach einer Unterbrechung von mehr als zehn Jahren. Die libysche Fluggesellschaft Medsky Airways plant entsprechende Flüge.</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/medsky-airways-plant-direktfluege-zwischen-libyen-und-frankreich/e7qthj4</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>auto-28d1added29c</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>My Freighter schließt Interline-Abkommen mit Oman Air</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Die usbekische Frachtfluggesellschaft My Freighter hat ein Interline-Abkommen mit Oman Air geschlossen. Dadurch kann My Freighter das Streckennetz der omanischen Fluggesellschaft über deren Drehkreuz Maskat für Frachtverbindungen nutzen, berichtet das Portal Central Asia + Aero.</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/my-freighter-schliesst-interline-abkommen-mit-oman-air/0m1nkcn</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>auto-d04e14a3d453</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Portugal treibt Preis für TAP Air Portugal hoch</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LISSABON - Lufthansa und Air France-KLM bieten für ein Stück TAP Air Portugal. Ende Juli hinterlegte Beteiligungsofferten der Flugkonzern stuft die portugiesische Regierung nach einer ersten Bewertung als "im Großen und Ganzen gleichwertig" ein. Lissabon fordert die Interessenten nun zu Nachbesserungen auf.</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53564/Portugal-treibt-Preis-fuer-TAP-Air-Portugal-hoch.html</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>auto-3b4851427461</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Schwerer Unfall überschattet Luftsport-Sommerfest</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>VIERNHEIM - Ein Sommerfest wird von einer Tragödie überschattet: Ein Kleinflugzeug stürzt ab, zwei Männer sterben. Eine Frau und ein Kleinkind kommen mit schwersten Verletzungen ins Krankenhaus.</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53561/Schwerer-Unfall-ueberschattet-Luftsport-Sommerfest.html</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>auto-a85b79126537</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport: "LogiSpace" near CargoCity North – Areas available for rent - TRANSPORT - die Zeitung für den Güterverkehr</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaklLTmE0Y014SXRqYWV1MGdrOUp6U2dJRkpVQTZFX3pOTXRreWJMLU91eDI2cXFROUNQXzNGTHpxVS10TUNxUEhtTHNEREtoaGxWUGtHOVpoUTZ0VVpIekFxejRUelZzOFJpb2JxUjdpdnlPTGV6SWRkWlFLU1N3ZGJ5dDV0dGdZamppMUg0SGpJMm43YmpHMFg5RDlpWU5ObDlxUHlrZEhYQjhJS1BFS0J3b1RmbDBY?oc=5" target="_blank"&gt;Frankfurt Airport: "LogiSpace" near CargoCity North – Areas available for rent&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;TRANSPORT - die Zeitung für den Güterverkehr&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOaklLTmE0Y014SXRqYWV1MGdrOUp6U2dJRkpVQTZFX3pOTXRreWJMLU91eDI2cXFROUNQXzNGTHpxVS10TUNxUEhtTHNEREtoaGxWUGtHOVpoUTZ0VVpIekFxejRUelZzOFJpb2JxUjdpdnlPTGV6SWRkWlFLU1N3ZGJ5dDV0dGdZamppMUg0SGpJMm43YmpHMFg5RDlpWU5ObDlxUHlrZEhYQjhJS1BFS0J3b1RmbDBY?oc=5</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>auto-4f99e9b515da</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Delta flight from Copenhagen to JFK makes emergency landing in Paris - theaviationhub.co.uk</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiswFBVV95cUxNTHIwQlhHNEliSG1JSjBhTTRsSkJSaVJyRVJ6SDZIUVVCb1poQ1UzTm11M1V5WklaWkVDdG9ueHRFVGRYdFZUQ1RBRGphSy0ya0NRY0Ixc3BFSk1JYWtZYW5MSXpNZjZxSldjRGloc21kVXJKaFVMVU9femMtYkpvdHpWNjBoLW4yTTlzSEZfQXJGeERJbHZQZ0I0QVhtbUtaVWtlbHgweUZEZFlpM2dwdkJJUQ?oc=5" target="_blank"&gt;Delta flight from Copenhagen to JFK makes emergency landing in Paris&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;theaviationhub.co.uk&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Google News Europa Movements</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNTHIwQlhHNEliSG1JSjBhTTRsSkJSaVJyRVJ6SDZIUVVCb1poQ1UzTm11M1V5WklaWkVDdG9ueHRFVGRYdFZUQ1RBRGphSy0ya0NRY0Ixc3BFSk1JYWtZYW5MSXpNZjZxSldjRGloc21kVXJKaFVMVU9femMtYkpvdHpWNjBoLW4yTTlzSEZfQXJGeERJbHZQZ0I0QVhtbUtaVWtlbHgweUZEZFlpM2dwdkJJUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O281"/>
+  <dimension ref="A1:O289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17197,7 +17197,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17228,8 +17227,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
           <t>review</t>
@@ -17262,7 +17259,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17293,8 +17289,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
           <t>review</t>
@@ -17327,7 +17321,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17358,8 +17351,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
           <t>review</t>
@@ -17392,7 +17383,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17423,8 +17413,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
           <t>review</t>
@@ -17457,7 +17445,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17488,8 +17475,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
           <t>review</t>
@@ -17522,7 +17507,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17553,8 +17537,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
           <t>review</t>
@@ -17587,7 +17569,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17618,8 +17599,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
           <t>review</t>
@@ -17652,7 +17631,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17683,8 +17661,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
           <t>review</t>
@@ -17717,7 +17693,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17748,8 +17723,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
           <t>review</t>
@@ -17782,7 +17755,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17813,8 +17785,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
           <t>review</t>
@@ -17847,7 +17817,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -17878,8 +17847,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
           <t>review</t>
@@ -17891,6 +17858,526 @@
         </is>
       </c>
       <c r="O281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>auto-2fd89dd73466</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Turkish Airlines wird neuer Trikotsponsor des FC Liverpool</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Turkish Airlines wird ab dem 1. Juni 2027 neuer Hauptsponsor des FC Liverpool. Ab der Saison 2027/28 erscheint das Logo der Fluggesellschaft auf der Vorderseite der Trikots der Männer-, Frauen- und Nachwuchsmannschaften.</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/turkish-airlines-wird-neuer-trikotsponsor-des-fc-liverpool/58cqr4d</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>auto-a26ed3c3a0e2</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>«Hier waren wir zu optimistisch»: Swiss zieht nach monatelanger Kritik aus Ekel-Hotel in Miami aus</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Seit dem vergangenen Winter steht das Crewhotel von Swiss in Miami in der Kritik. Trotz Beschwerden über Schmutz, Infrastruktur und Sicherheitsmängel hielt die Airline zunächst an der Unterkunft fest und setzte auf Verbesserungen. Diese blieben offenbar aus. Jetzt zieht Swiss die Reissleine – und entschuldigt sich bei den Crews.</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/swiss-zieht-nach-monatelanger-kritik-aus-ekel-hotel-in-miami-aus/q6pvr8z</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>auto-d8bb8122315e</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Verkauf von Airwork an ASL Airlines Australia geplatzt</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Die geplante Übernahme der neuseeländischen Frachtfluggesellschaft Airwork durch ASL Airlines Australia ist gescheitert. Nach Angaben der Insolvenzverwalter wurde die bereits geschlossene bedingte Verkaufsvereinbarung nicht vollzogen. Nun soll Airwork bis Ende des ersten Quartals 2027 an einen anderen 'Käufer verkauft werden, berichtet das Portal Aero South Pacific.</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/verkauf-von-airwork-an-asl-airlines-australia-geplatzt/sz1rzbd</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>auto-7249bfdecc72</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Royal Air will ab Dezember von den Komoren nach Mayotte fliegen</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Die komorische Fluggesellschaft Royal Air will ihr internationales Streckennetz um Mayotte erweitern. Nach Angaben der Airline sollen die Flüge auf die französische Insel am 15. Dezember 2026 starten. Die Verbindung war bereits seit der Gründung von Royal Air im Jahr 2024 geplant, berichtet der Tv-Sender TF1.</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/royal-air-will-ab-dezember-von-den-komoren-nach-mayotte-fliegen/v2sgnxh</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>auto-9729ff41d67b</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lufthansa will in der Flotte mehr Premiumsitze einbauen</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa will 2030 mit acht bis zehn Prozent Marge fliegen. Das neue Lufthansa-Interkontprodukt Allegris ist der Schlüssel zum Renditeziel, die Premiumtickets verkaufen sich gut. Nach einem Medienbericht überdenkt Lufthansa die Kabinenaufteilung neuer Interkontflugzeuge.</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53575/Lufthansa-will-in-der-Flotte-mehr-Premiumsitze-einbauen.html</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>auto-90da3e32fee3</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>A330neo-Problem hemmt Airbus-Auslieferungen</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>TOULOUSE - Airbus muss einen Rückgang der Auslieferungen hinnehmen. Nur 57 Flugzeuge fanden im August 2026 den Weg zu den Kunden. Der neue Frachter A350F und chinesische Großkunden sorgen unterdessen für weitere Aufträge.</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53574/A330neo-Problem-hemmt-Airbus-Auslieferungen.html</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>auto-11fc379dcbde</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SPD-Fraktionsvize gegen zusätzliche Flugrechte für Emirates</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>BERLIN - SPD-Fraktionsvize Armand Zorn sieht eine mögliche Ausweitung von Start- und Landemöglichkeiten für die Fluggesellschaft Emirates an deutschen Flughäfen kritisch.</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53573/SPD-Fraktionsvize-gegen-zusaetzliche-Flugrechte-fuer-Emirates.html</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>auto-124dc145c13d</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Traf Rakete 1968 Air-France-Flug?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>NIZZA - Zeugen sprechen von Vertuschung und verschwundenen Dokumenten: Findet die Justiz jetzt Beweise für einen Raketenabschuss der Air-France-Caravelle durch Frankreichs Armee?</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53570/Traf-Rakete-1968-Air-France-Flug.html</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O289"/>
+  <dimension ref="A1:O297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17879,7 +17879,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17910,8 +17909,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
           <t>review</t>
@@ -17944,7 +17941,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -17975,8 +17971,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
           <t>review</t>
@@ -18009,7 +18003,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18040,8 +18033,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
           <t>review</t>
@@ -18074,7 +18065,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18105,8 +18095,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
           <t>review</t>
@@ -18139,7 +18127,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18170,8 +18157,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
           <t>review</t>
@@ -18204,7 +18189,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18235,8 +18219,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
           <t>review</t>
@@ -18269,7 +18251,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18300,8 +18281,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
           <t>review</t>
@@ -18334,7 +18313,6 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18365,8 +18343,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
           <t>review</t>
@@ -18378,6 +18354,526 @@
         </is>
       </c>
       <c r="O289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>auto-0ce458985bdf</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Hungary Airlines gibt einen Airbus A330 F ab</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Hungary Airlines stellt ihre Frachtflotte neu auf. Der Airbus A330-200 P2F mit dem Kennzeichen HA-ZTO wird die Flotte verlassen, da der Eigentümer das Flugzeug zum Verkauf anbietet. Die Fluggesellschaft prüft Leasing- und Expansionsmöglichkeiten, um wieder mehrere Flugzeuge zu betreiben, berichtet das Portal Airline Economics.</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/hungary-airlines-gibt-einen-airbus-a330-f-ab/bfz5bbt</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>auto-b2049720b447</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Lufthansa, Swiss, Eurowings und Austrian Airlines fliegen ab Ende Oktober wieder nach Dubai</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Die Airlines der Lufthansa Group nehmen ihre Verbindungen nach Dubai ab Ende Oktober schrittweise wieder auf. Lufthansa startet am 25. Oktober ab München mit fünf wöchentlichen Flügen und einen Tag später ab Frankfurt zunächst mit vier, ab 9. November fünf Flügen pro Woche. Swiss fliegt ab 27. Oktober täglich ab Zürich.</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-swiss-eurowings-und-austrian-airlines-fliegen-ab-ende-oktober-wieder-nach/yl8fdk5</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>auto-fb39173f9fda</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TAB Cargo: Staatliche Frachtairline Boliviens nimmt Flugbetrieb wieder auf - mit McDonnell Douglas DC-10 F</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Die staatliche bolivianische Frachtfluggesellschaft Transportes Aéreos Bolivianos oder kurz TAB Cargo hat am 5. September ihren regulären Flugbetrieb wieder aufgenommen. Der Neustart erfolgt im Zuge einer Restrukturierung und der neuen Open-Skies-Politik Boliviens. Sie war seit Novmeber 2025 am Boden gewesen.</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/tab-cargo-staatliche-frachtairline-boliviens-nimmt-flugbetrieb-wieder-auf-mit/wd1y7cm</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>auto-6d52ed05feb4</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Pilotinnen und Piloten von Easyjet in Frankreich kündigen Streik an</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Die französischen Pilotinnen und Piloten von Easyjet sind für den 13. und 14. September zum Streik aufgerufen. Die Gewerkschaft SNPL hat nach mehreren Monaten erfolgloser Gespräche mit der Fluggesellschaft eine entsprechende Streikankündigung eingereicht.</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/pilotinnen-und-piloten-von-easyjet-in-frankreich-kuendigen-streik-an/940skxw</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>auto-1f4758d888ac</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Hessen will Strafrecht verschärfen</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>WIESBADEN - Angesichts der jüngsten Sabotageakte macht sich Hessens Justizminister Christian Heinz (CDU) für eine Verschärfung des Strafrechts stark, um kritische Infrastruktur in Deutschland besser zu schützen.</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53594/Hessen-will-Strafrecht-verschaerfen.html</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>auto-97d6b7dc682b</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lufthansa wettet auf Rückkehr der Dubai-Nachfrage</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Bis zu 36 wöchentliche Verbindungen: Lufthansa nimmt im Winter 26/27 die im Iran-Krieg ausgesetzten Konzernlinien nach Dubai wieder auf. Allein aus Deutschland wird Lufthansa das Ziel am Persischen Golf von fünf Flughäfen aus anfliegen. Zwei Konzernairlines fliegen täglich nach Dubai.</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53587/Lufthansa-wettet-auf-Rueckkehr-der-Dubai-Nachfrage.html</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>auto-d32f8d526f20</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Frachtjet-Unfall: Alle Todesopfer saßen in Fahrzeug</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>MIAMI - Alle fünf Todesopfer bei dem Amazon-Frachtflugzeug-Unfall am Flughafen Miami haben in einem Wagen gesessen, mit dem der Jet zusammengestoßen ist.</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53583/Frachtjet-Unfall-Alle-Todesopfer-sassen-in-Fahrzeug.html</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>auto-c1b1a5aa9560</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Lufthansa Cargo übernimmt Abfertiger in Frankfurt</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Lufthansa Cargo übernimmt den Frankfurter Luftfrachtabfertiger LUG Aircargo Handling. Mit der Übernahme erhält Lufthansa Cargo kurzfristig Zugriff auf zusätzliche Abfertigungskapazitäten am Heimatdrehkrehkreuz.</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53578/Lufthansa-Cargo-uebernimmt-Abfertiger-in-Frankfurt.html</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O297"/>
+  <dimension ref="A1:O299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18375,7 +18375,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18406,8 +18405,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
           <t>review</t>
@@ -18440,7 +18437,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18471,8 +18467,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>review</t>
@@ -18505,7 +18499,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18536,8 +18529,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
           <t>review</t>
@@ -18570,7 +18561,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18601,8 +18591,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
           <t>review</t>
@@ -18635,7 +18623,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18666,8 +18653,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
           <t>review</t>
@@ -18700,7 +18685,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18731,8 +18715,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
           <t>review</t>
@@ -18765,7 +18747,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18796,8 +18777,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>review</t>
@@ -18830,7 +18809,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18861,8 +18839,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
           <t>review</t>
@@ -18874,6 +18850,136 @@
         </is>
       </c>
       <c r="O297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>auto-d43254e66928</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Flugzeug von Selenskyj beinahe von Drohne getroffen</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Special Movement Europa</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>OSLO - Auch der ukrainische Präsident reiste nach Oslo, um König Harald V. die letzte Ehre zu erweisen. Auf dem Weg soll es laut dem norwegischen Regierungschef allerdings einen Zwischenfall gegeben haben.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53598/Flugzeug-von-Selenskyj-beinahe-von-Drohne-getroffen.html</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>auto-72e1cc1e4fb9</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Frankfurt Style Award und Airlebnistag Fashion on Air – Frankfurt Airport - Fashionstreet-Berlin</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMitgFBVV95cUxQbEc0QUY5THpVVjQ5NGplVUEwcDNxdE54cV8yVW14bGpVQ1pzMG1BMmhld3NENkxyWmZDdktCTUM3dklNRHBKTFRmVWVXS0NsczV4S1JtemphSkZQc1ZqNVBrdUh1bERDQWpsMFBqZUtHdl9BNjhzNTdWZ1dBV1dVYnhLSjlyV2M5NWVaZFhnSG93OVZ5M3BJd3VrUlpDcHN0TXNaNGtUZmhjNzdMT0d5R2NDVUJQdw?oc=5" target="_blank"&gt;Frankfurt Style Award und Airlebnistag Fashion on Air – Frankfurt Airport&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Fashionstreet-Berlin&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbEc0QUY5THpVVjQ5NGplVUEwcDNxdE54cV8yVW14bGpVQ1pzMG1BMmhld3NENkxyWmZDdktCTUM3dklNRHBKTFRmVWVXS0NsczV4S1JtemphSkZQc1ZqNVBrdUh1bERDQWpsMFBqZUtHdl9BNjhzNTdWZ1dBV1dVYnhLSjlyV2M5NWVaZFhnSG93OVZ5M3BJd3VrUlpDcHN0TXNaNGtUZmhjNzdMT0d5R2NDVUJQdw?oc=5</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O299"/>
+  <dimension ref="A1:O306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18871,7 +18871,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>Special Movement Europa</t>
@@ -18902,8 +18901,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
           <t>review</t>
@@ -18936,7 +18933,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -18967,8 +18963,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
           <t>review</t>
@@ -18980,6 +18974,461 @@
         </is>
       </c>
       <c r="O299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>auto-fdaa100847a2</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>General Atomics stellt neue günstigere Militärdrohne Wildfire vor</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>General Atomics Aeronautical Systems hat mit Wildfire eine neue unbemannte Drohne vorgestellt. Sie ist als kostengünstigere und in großen Stückzahlen einsetzbare Ergänzung zu Systemen wie der MQ-9B gedacht. Vorgesehen sind vor allem Aufklärungs- und Angriffsmissionen, daneben nennt der Hersteller auch zivile und kommerzielle Anwendungen wie Frachttransporte.</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker-verteidigung/general-atomics-stellt-neue-guenstigere-militaerdrohne-wildfire-vor/2v350nf</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>auto-69d1db85bccd</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Lufthansa Group und Air France-KLM begrüssen weitere Gespräche über Tap</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Air France-KLM und Lufthansa wollen ihre Angebote für einen Einstieg bei Tap Air Portugal im Rahmen der neuen Verhandlungsrunde weiterverfolgen. Air France-KLM sieht die zusätzlichen Gespräche als Gelegenheit, das eigene Konzept zu stärken. Der Konzern zeigte sich zuversichtlich, innerhalb der von der portugiesischen Regierung gesetzten Frist von drei Wochen ein endgültiges und verbessertes verbindliches Angebot vorlegen zu können, berichtet die Nachrichtenagentur Lusa. Zu möglichen finanziellen Nachbesserungen äußerte er sich nicht.</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/lufthansa-group-und-air-france-klm-begruessen-weitere-gespraeche-ueber-tap/5070rwe</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>auto-5fb36011e6bb</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Die wichtigsten Fragen und Antworten zu den neuen Verkehrsrechten für die Emirate</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Eine Airline aus den Vereinigten Arabischen Emiraten darf einen fünften deutschen Flughafen ansteuern. Damit ist der Weg für Emirates-Flüge nach Berlin frei. Aber wie wird dies nun umgesetzt? Und welche Konkurrenten sind betroffen? Die wichtigsten Fragen und Antworten.</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/airlines/die-wichtigsten-fragen-und-antworten-zu-den-neuen-verkehrsrechten-fuer-die-emirate/d1fn49f</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>auto-2dd78b6186e7</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Auch im August weniger Flüge in Frankfurt</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Im August flogen rund 6,3 Millionen Passagiere über den Flughafen Frankfurt. Das waren 0,3 Prozent weniger als im Vorjahresmonat.</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53611/Auch-im-August-weniger-Fluege-in-Frankfurt.html</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>auto-6091922fea33</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Wie realistisch ist ein deutscher GCAP-Einstieg?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Special Movement</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Deutschland braucht nach dem FCAS-Ende eine neue Fighter-Strategie. Das britisch-italienisch-japanische Projekt ist zwar weit fortgeschritten, laut Leonardo-Cchef Lorenzo Mariani aber offen für Nachrücker. Eine deutsche GCAP-Beteiligung - noch möglich, aber auch sinnvoll? Airbus denkt in eine andere Richtung.</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53586/Wie-realistisch-ist-ein-deutscher-GCAP-Einstieg.html</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>auto-5daa589f383f</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Hessen lehnt erweiterte Emirates-Flugrechte ab</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>FRANKFURT - Der hessische Wirtschaftsminister Kaweh Mansoori (SPD) lehnt erweiterte Verkehrsrechte für Emirates ab.</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>aero.de</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>https://www.aero.de/news-53607/Hessen-lehnt-erweiterte-Emirates-Flugrechte-ab.html</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>auto-3912963d9518</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Discover Airlines Business Class Hin/Rückflüge Frankfurt – Punta Cana ab 1.895€ - PointsMag</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMie0FVX3lxTE1iSU10aGRTT0Rkb2dtZXJqTmQyWlBNV1ZDdy03OTlmRkN5ckNma0RGTkdzT0NCS3dvTWd0UldvUS1tWExBRkR4X19Fekl2YUU3Q2J6RXVVQjFndG1ZSEFZdnFPUXBPaXIzTzhuVXJFRjktRklQOWZQUkxMUQ?oc=5" target="_blank"&gt;Discover Airlines Business Class Hin/Rückflüge Frankfurt – Punta Cana ab 1.895€&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;PointsMag&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1iSU10aGRTT0Rkb2dtZXJqTmQyWlBNV1ZDdy03OTlmRkN5ckNma0RGTkdzT0NCS3dvTWd0UldvUS1tWExBRkR4X19Fekl2YUU3Q2J6RXVVQjFndG1ZSEFZdnFPUXBPaXIzTzhuVXJFRjktRklQOWZQUkxMUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/content/news.xlsx
+++ b/content/news.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O306"/>
+  <dimension ref="A1:O309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18995,7 +18995,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19026,8 +19025,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
           <t>review</t>
@@ -19060,7 +19057,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19091,8 +19087,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
           <t>review</t>
@@ -19125,7 +19119,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19156,8 +19149,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
           <t>review</t>
@@ -19190,7 +19181,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19221,8 +19211,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
           <t>review</t>
@@ -19255,7 +19243,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>Special Movement</t>
@@ -19286,8 +19273,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
           <t>review</t>
@@ -19320,7 +19305,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19351,8 +19335,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr">
         <is>
           <t>review</t>
@@ -19385,7 +19367,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>Frankfurt Airport</t>
@@ -19416,8 +19397,6 @@
           <t>review</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
           <t>review</t>
@@ -19429,6 +19408,201 @@
         </is>
       </c>
       <c r="O306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>auto-2aefeb94d398</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Emirates bringt Premium Economy im Airbus A380 nach Paris</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Emirates setzt ab dem 25. Oktober täglich einen umgerüsteten Airbus A380 zwischen Dubai und Paris ein. Auf den Flügen EK071 und EK072 steht damit erstmals die Premium Economy der Airline auf dieser Strecke zur Verfügung. Nach Lyon und Nizza bietet Emirates die Reiseklasse damit an allen drei französischen Zielen an.</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/emirates-bringt-premium-economy-im-airbus-a380-nach-paris/kn03zjp</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>auto-4ae1f2c34d8e</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Flydubai steigt mit drei Boeing 737-800 in das Frachteschäft ein</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Flydubai startet am 1. Oktober 2026 mit eigenen Frachterverbindungen. Dafür übernimmt die Airline drei Boeing 737-800-Frachter im Wet-Lease von Solitair. Jedes Flugzeug bietet eine Nutzlast von 23.000 Kilogramm. Als Frachtdrehkreuz dient der Flughafen Dubai World Central.</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>aeroTELEGRAPH</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>https://www.aerotelegraph.com/ticker/flydubai-steigt-mit-drei-boeing-737-800-in-das-frachteschaeft-ein/fr0myjs</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>auto-6bb95f7f7f80</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Neue Air France Lounge in Frankfurt jetzt bei Priority Pass - meilenoptimieren.com</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Frankfurt Airport</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Automatisch gefundener Kandidat. Fakten, FRA-Bezug und Quelle vor Veröffentlichung prüfen.</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://news.google.com/rss/articles/CBMiZ0FVX3lxTE14eHY0MWdaUm5WYjVOMWRJSU5TZzkwdFZMN240QXplYUtySml4THNTaW9rSGNoRDhUV3RZeU9qMnlRM1dhZlVvclV6Nlo3ekFleE1uczNUdDhfU1A4emF2LWk2a3E2dDA?oc=5" target="_blank"&gt;Neue Air France Lounge in Frankfurt jetzt bei Priority Pass&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;meilenoptimieren.com&lt;/font&gt;</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Google News FRA</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE14eHY0MWdaUm5WYjVOMWRJSU5TZzkwdFZMN240QXplYUtySml4THNTaW9rSGNoRDhUV3RZeU9qMnlRM1dhZlVvclV6Nlo3ekFleE1uczNUdDhfU1A4emF2LWk2a3E2dDA?oc=5</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
         <is>
           <t>no</t>
         </is>
